--- a/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-HV-DTS-002 REV1.xlsx
+++ b/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-HV-DTS-002 REV1.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -133,28 +133,87 @@
       <sz val="16"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <i val="1"/>
       <color rgb="00404040"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color theme="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="FF00B050"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -342,7 +401,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -460,6 +519,14 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -470,36 +537,77 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1073,96 +1181,96 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A1" s="29" t="n"/>
-      <c r="B1" s="44" t="n"/>
-      <c r="C1" s="44" t="n"/>
-      <c r="D1" s="44" t="n"/>
-      <c r="E1" s="44" t="n"/>
-      <c r="F1" s="44" t="n"/>
-      <c r="G1" s="44" t="n"/>
-      <c r="H1" s="44" t="n"/>
-      <c r="I1" s="44" t="n"/>
-      <c r="J1" s="44" t="n"/>
-      <c r="K1" s="44" t="n"/>
-      <c r="L1" s="44" t="n"/>
-      <c r="M1" s="45" t="n"/>
-      <c r="N1" s="30" t="n"/>
-      <c r="O1" s="44" t="n"/>
-      <c r="P1" s="44" t="n"/>
-      <c r="Q1" s="44" t="n"/>
-      <c r="R1" s="44" t="n"/>
-      <c r="S1" s="44" t="n"/>
-      <c r="T1" s="44" t="n"/>
-      <c r="U1" s="44" t="n"/>
-      <c r="V1" s="44" t="n"/>
-      <c r="W1" s="44" t="n"/>
-      <c r="X1" s="44" t="n"/>
-      <c r="Y1" s="45" t="n"/>
+      <c r="A1" s="44" t="n"/>
+      <c r="B1" s="45" t="n"/>
+      <c r="C1" s="45" t="n"/>
+      <c r="D1" s="45" t="n"/>
+      <c r="E1" s="45" t="n"/>
+      <c r="F1" s="45" t="n"/>
+      <c r="G1" s="45" t="n"/>
+      <c r="H1" s="45" t="n"/>
+      <c r="I1" s="45" t="n"/>
+      <c r="J1" s="45" t="n"/>
+      <c r="K1" s="45" t="n"/>
+      <c r="L1" s="45" t="n"/>
+      <c r="M1" s="46" t="n"/>
+      <c r="N1" s="47" t="n"/>
+      <c r="O1" s="45" t="n"/>
+      <c r="P1" s="48" t="n"/>
+      <c r="Q1" s="48" t="n"/>
+      <c r="R1" s="48" t="n"/>
+      <c r="S1" s="48" t="n"/>
+      <c r="T1" s="48" t="n"/>
+      <c r="U1" s="48" t="n"/>
+      <c r="V1" s="48" t="n"/>
+      <c r="W1" s="48" t="n"/>
+      <c r="X1" s="48" t="n"/>
+      <c r="Y1" s="49" t="n"/>
       <c r="Z1" s="27" t="inlineStr">
         <is>
           <t>DISEÑO DE INGENIERÍA</t>
         </is>
       </c>
-      <c r="AA1" s="44" t="n"/>
-      <c r="AB1" s="44" t="n"/>
-      <c r="AC1" s="44" t="n"/>
-      <c r="AD1" s="44" t="n"/>
-      <c r="AE1" s="44" t="n"/>
-      <c r="AF1" s="44" t="n"/>
-      <c r="AG1" s="44" t="n"/>
-      <c r="AH1" s="44" t="n"/>
-      <c r="AI1" s="44" t="n"/>
-      <c r="AJ1" s="44" t="n"/>
-      <c r="AK1" s="44" t="n"/>
-      <c r="AL1" s="44" t="n"/>
-      <c r="AM1" s="44" t="n"/>
-      <c r="AN1" s="44" t="n"/>
-      <c r="AO1" s="44" t="n"/>
-      <c r="AP1" s="44" t="n"/>
-      <c r="AQ1" s="44" t="n"/>
-      <c r="AR1" s="44" t="n"/>
-      <c r="AS1" s="44" t="n"/>
-      <c r="AT1" s="44" t="n"/>
-      <c r="AU1" s="44" t="n"/>
-      <c r="AV1" s="44" t="n"/>
-      <c r="AW1" s="44" t="n"/>
-      <c r="AX1" s="44" t="n"/>
-      <c r="AY1" s="44" t="n"/>
-      <c r="AZ1" s="44" t="n"/>
-      <c r="BA1" s="44" t="n"/>
-      <c r="BB1" s="45" t="n"/>
+      <c r="AA1" s="48" t="n"/>
+      <c r="AB1" s="48" t="n"/>
+      <c r="AC1" s="48" t="n"/>
+      <c r="AD1" s="48" t="n"/>
+      <c r="AE1" s="48" t="n"/>
+      <c r="AF1" s="48" t="n"/>
+      <c r="AG1" s="48" t="n"/>
+      <c r="AH1" s="48" t="n"/>
+      <c r="AI1" s="48" t="n"/>
+      <c r="AJ1" s="48" t="n"/>
+      <c r="AK1" s="48" t="n"/>
+      <c r="AL1" s="48" t="n"/>
+      <c r="AM1" s="48" t="n"/>
+      <c r="AN1" s="48" t="n"/>
+      <c r="AO1" s="48" t="n"/>
+      <c r="AP1" s="48" t="n"/>
+      <c r="AQ1" s="48" t="n"/>
+      <c r="AR1" s="48" t="n"/>
+      <c r="AS1" s="48" t="n"/>
+      <c r="AT1" s="48" t="n"/>
+      <c r="AU1" s="48" t="n"/>
+      <c r="AV1" s="48" t="n"/>
+      <c r="AW1" s="48" t="n"/>
+      <c r="AX1" s="48" t="n"/>
+      <c r="AY1" s="48" t="n"/>
+      <c r="AZ1" s="48" t="n"/>
+      <c r="BA1" s="48" t="n"/>
+      <c r="BB1" s="49" t="n"/>
       <c r="BC1" s="26" t="inlineStr">
         <is>
           <t>CODIGO:</t>
         </is>
       </c>
-      <c r="BD1" s="46" t="n"/>
-      <c r="BE1" s="46" t="n"/>
-      <c r="BF1" s="46" t="n"/>
-      <c r="BG1" s="46" t="n"/>
-      <c r="BH1" s="46" t="n"/>
-      <c r="BI1" s="46" t="n"/>
-      <c r="BJ1" s="46" t="n"/>
-      <c r="BK1" s="46" t="n"/>
-      <c r="BL1" s="46" t="n"/>
-      <c r="BM1" s="46" t="n"/>
-      <c r="BN1" s="47" t="n"/>
+      <c r="BD1" s="50" t="n"/>
+      <c r="BE1" s="50" t="n"/>
+      <c r="BF1" s="50" t="n"/>
+      <c r="BG1" s="50" t="n"/>
+      <c r="BH1" s="50" t="n"/>
+      <c r="BI1" s="50" t="n"/>
+      <c r="BJ1" s="50" t="n"/>
+      <c r="BK1" s="50" t="n"/>
+      <c r="BL1" s="50" t="n"/>
+      <c r="BM1" s="50" t="n"/>
+      <c r="BN1" s="51" t="n"/>
       <c r="BO1" s="25" t="inlineStr">
         <is>
           <t>P2437-HV-DTS-002</t>
         </is>
       </c>
-      <c r="BP1" s="48" t="n"/>
-      <c r="BQ1" s="48" t="n"/>
-      <c r="BR1" s="48" t="n"/>
-      <c r="BS1" s="48" t="n"/>
-      <c r="BT1" s="48" t="n"/>
-      <c r="BU1" s="48" t="n"/>
-      <c r="BV1" s="48" t="n"/>
-      <c r="BW1" s="48" t="n"/>
-      <c r="BX1" s="48" t="n"/>
-      <c r="BY1" s="48" t="n"/>
-      <c r="BZ1" s="49" t="n"/>
+      <c r="BP1" s="52" t="n"/>
+      <c r="BQ1" s="52" t="n"/>
+      <c r="BR1" s="52" t="n"/>
+      <c r="BS1" s="52" t="n"/>
+      <c r="BT1" s="52" t="n"/>
+      <c r="BU1" s="52" t="n"/>
+      <c r="BV1" s="52" t="n"/>
+      <c r="BW1" s="52" t="n"/>
+      <c r="BX1" s="52" t="n"/>
+      <c r="BY1" s="52" t="n"/>
+      <c r="BZ1" s="53" t="n"/>
       <c r="CB1" s="15" t="inlineStr">
         <is>
           <t>REVIZADO</t>
@@ -1175,71 +1283,83 @@
       </c>
     </row>
     <row r="2" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="50" t="n"/>
-      <c r="M2" s="51" t="n"/>
-      <c r="N2" s="50" t="n"/>
-      <c r="Y2" s="51" t="n"/>
-      <c r="Z2" s="52" t="n"/>
-      <c r="AA2" s="53" t="n"/>
-      <c r="AB2" s="53" t="n"/>
-      <c r="AC2" s="53" t="n"/>
-      <c r="AD2" s="53" t="n"/>
-      <c r="AE2" s="53" t="n"/>
-      <c r="AF2" s="53" t="n"/>
-      <c r="AG2" s="53" t="n"/>
-      <c r="AH2" s="53" t="n"/>
-      <c r="AI2" s="53" t="n"/>
-      <c r="AJ2" s="53" t="n"/>
-      <c r="AK2" s="53" t="n"/>
-      <c r="AL2" s="53" t="n"/>
-      <c r="AM2" s="53" t="n"/>
-      <c r="AN2" s="53" t="n"/>
-      <c r="AO2" s="53" t="n"/>
-      <c r="AP2" s="53" t="n"/>
-      <c r="AQ2" s="53" t="n"/>
-      <c r="AR2" s="53" t="n"/>
-      <c r="AS2" s="53" t="n"/>
-      <c r="AT2" s="53" t="n"/>
-      <c r="AU2" s="53" t="n"/>
-      <c r="AV2" s="53" t="n"/>
-      <c r="AW2" s="53" t="n"/>
-      <c r="AX2" s="53" t="n"/>
-      <c r="AY2" s="53" t="n"/>
-      <c r="AZ2" s="53" t="n"/>
-      <c r="BA2" s="53" t="n"/>
-      <c r="BB2" s="54" t="n"/>
+      <c r="A2" s="54" t="n"/>
+      <c r="B2" s="55" t="n"/>
+      <c r="C2" s="55" t="n"/>
+      <c r="D2" s="55" t="n"/>
+      <c r="E2" s="55" t="n"/>
+      <c r="F2" s="55" t="n"/>
+      <c r="G2" s="55" t="n"/>
+      <c r="H2" s="55" t="n"/>
+      <c r="I2" s="55" t="n"/>
+      <c r="J2" s="55" t="n"/>
+      <c r="K2" s="55" t="n"/>
+      <c r="L2" s="55" t="n"/>
+      <c r="M2" s="56" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="O2" s="55" t="n"/>
+      <c r="Y2" s="57" t="n"/>
+      <c r="Z2" s="58" t="n"/>
+      <c r="AA2" s="59" t="n"/>
+      <c r="AB2" s="59" t="n"/>
+      <c r="AC2" s="59" t="n"/>
+      <c r="AD2" s="59" t="n"/>
+      <c r="AE2" s="59" t="n"/>
+      <c r="AF2" s="59" t="n"/>
+      <c r="AG2" s="59" t="n"/>
+      <c r="AH2" s="59" t="n"/>
+      <c r="AI2" s="59" t="n"/>
+      <c r="AJ2" s="59" t="n"/>
+      <c r="AK2" s="59" t="n"/>
+      <c r="AL2" s="59" t="n"/>
+      <c r="AM2" s="59" t="n"/>
+      <c r="AN2" s="59" t="n"/>
+      <c r="AO2" s="59" t="n"/>
+      <c r="AP2" s="59" t="n"/>
+      <c r="AQ2" s="59" t="n"/>
+      <c r="AR2" s="59" t="n"/>
+      <c r="AS2" s="59" t="n"/>
+      <c r="AT2" s="59" t="n"/>
+      <c r="AU2" s="59" t="n"/>
+      <c r="AV2" s="59" t="n"/>
+      <c r="AW2" s="59" t="n"/>
+      <c r="AX2" s="59" t="n"/>
+      <c r="AY2" s="59" t="n"/>
+      <c r="AZ2" s="59" t="n"/>
+      <c r="BA2" s="59" t="n"/>
+      <c r="BB2" s="60" t="n"/>
       <c r="BC2" s="26" t="inlineStr">
         <is>
           <t>REVISION:</t>
         </is>
       </c>
-      <c r="BD2" s="46" t="n"/>
-      <c r="BE2" s="46" t="n"/>
-      <c r="BF2" s="46" t="n"/>
-      <c r="BG2" s="46" t="n"/>
-      <c r="BH2" s="46" t="n"/>
-      <c r="BI2" s="46" t="n"/>
-      <c r="BJ2" s="46" t="n"/>
-      <c r="BK2" s="46" t="n"/>
-      <c r="BL2" s="46" t="n"/>
-      <c r="BM2" s="46" t="n"/>
-      <c r="BN2" s="47" t="n"/>
+      <c r="BD2" s="50" t="n"/>
+      <c r="BE2" s="50" t="n"/>
+      <c r="BF2" s="50" t="n"/>
+      <c r="BG2" s="50" t="n"/>
+      <c r="BH2" s="50" t="n"/>
+      <c r="BI2" s="50" t="n"/>
+      <c r="BJ2" s="50" t="n"/>
+      <c r="BK2" s="50" t="n"/>
+      <c r="BL2" s="50" t="n"/>
+      <c r="BM2" s="50" t="n"/>
+      <c r="BN2" s="51" t="n"/>
       <c r="BO2" s="25" t="inlineStr">
         <is>
           <t>CERO (0)</t>
         </is>
       </c>
-      <c r="BP2" s="48" t="n"/>
-      <c r="BQ2" s="48" t="n"/>
-      <c r="BR2" s="48" t="n"/>
-      <c r="BS2" s="48" t="n"/>
-      <c r="BT2" s="48" t="n"/>
-      <c r="BU2" s="48" t="n"/>
-      <c r="BV2" s="48" t="n"/>
-      <c r="BW2" s="48" t="n"/>
-      <c r="BX2" s="48" t="n"/>
-      <c r="BY2" s="48" t="n"/>
-      <c r="BZ2" s="49" t="n"/>
+      <c r="BP2" s="52" t="n"/>
+      <c r="BQ2" s="52" t="n"/>
+      <c r="BR2" s="52" t="n"/>
+      <c r="BS2" s="52" t="n"/>
+      <c r="BT2" s="52" t="n"/>
+      <c r="BU2" s="52" t="n"/>
+      <c r="BV2" s="52" t="n"/>
+      <c r="BW2" s="52" t="n"/>
+      <c r="BX2" s="52" t="n"/>
+      <c r="BY2" s="52" t="n"/>
+      <c r="BZ2" s="53" t="n"/>
       <c r="CB2" s="15" t="inlineStr">
         <is>
           <t>APROBADO</t>
@@ -1252,341 +1372,371 @@
       </c>
     </row>
     <row r="3" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A3" s="50" t="n"/>
-      <c r="M3" s="51" t="n"/>
-      <c r="N3" s="50" t="n"/>
-      <c r="Y3" s="51" t="n"/>
+      <c r="A3" s="54" t="n"/>
+      <c r="B3" s="55" t="n"/>
+      <c r="C3" s="55" t="n"/>
+      <c r="D3" s="55" t="n"/>
+      <c r="E3" s="55" t="n"/>
+      <c r="F3" s="55" t="n"/>
+      <c r="G3" s="55" t="n"/>
+      <c r="H3" s="55" t="n"/>
+      <c r="I3" s="55" t="n"/>
+      <c r="J3" s="55" t="n"/>
+      <c r="K3" s="55" t="n"/>
+      <c r="L3" s="55" t="n"/>
+      <c r="M3" s="56" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="55" t="n"/>
+      <c r="Y3" s="57" t="n"/>
       <c r="Z3" s="27" t="inlineStr">
         <is>
           <t>SISTEMA HVAC LABORATORIO BRINSA</t>
         </is>
       </c>
-      <c r="AA3" s="44" t="n"/>
-      <c r="AB3" s="44" t="n"/>
-      <c r="AC3" s="44" t="n"/>
-      <c r="AD3" s="44" t="n"/>
-      <c r="AE3" s="44" t="n"/>
-      <c r="AF3" s="44" t="n"/>
-      <c r="AG3" s="44" t="n"/>
-      <c r="AH3" s="44" t="n"/>
-      <c r="AI3" s="44" t="n"/>
-      <c r="AJ3" s="44" t="n"/>
-      <c r="AK3" s="44" t="n"/>
-      <c r="AL3" s="44" t="n"/>
-      <c r="AM3" s="44" t="n"/>
-      <c r="AN3" s="44" t="n"/>
-      <c r="AO3" s="44" t="n"/>
-      <c r="AP3" s="44" t="n"/>
-      <c r="AQ3" s="44" t="n"/>
-      <c r="AR3" s="44" t="n"/>
-      <c r="AS3" s="44" t="n"/>
-      <c r="AT3" s="44" t="n"/>
-      <c r="AU3" s="44" t="n"/>
-      <c r="AV3" s="44" t="n"/>
-      <c r="AW3" s="44" t="n"/>
-      <c r="AX3" s="44" t="n"/>
-      <c r="AY3" s="44" t="n"/>
-      <c r="AZ3" s="44" t="n"/>
-      <c r="BA3" s="44" t="n"/>
-      <c r="BB3" s="45" t="n"/>
+      <c r="AA3" s="48" t="n"/>
+      <c r="AB3" s="48" t="n"/>
+      <c r="AC3" s="48" t="n"/>
+      <c r="AD3" s="48" t="n"/>
+      <c r="AE3" s="48" t="n"/>
+      <c r="AF3" s="48" t="n"/>
+      <c r="AG3" s="48" t="n"/>
+      <c r="AH3" s="48" t="n"/>
+      <c r="AI3" s="48" t="n"/>
+      <c r="AJ3" s="48" t="n"/>
+      <c r="AK3" s="48" t="n"/>
+      <c r="AL3" s="48" t="n"/>
+      <c r="AM3" s="48" t="n"/>
+      <c r="AN3" s="48" t="n"/>
+      <c r="AO3" s="48" t="n"/>
+      <c r="AP3" s="48" t="n"/>
+      <c r="AQ3" s="48" t="n"/>
+      <c r="AR3" s="48" t="n"/>
+      <c r="AS3" s="48" t="n"/>
+      <c r="AT3" s="48" t="n"/>
+      <c r="AU3" s="48" t="n"/>
+      <c r="AV3" s="48" t="n"/>
+      <c r="AW3" s="48" t="n"/>
+      <c r="AX3" s="48" t="n"/>
+      <c r="AY3" s="48" t="n"/>
+      <c r="AZ3" s="48" t="n"/>
+      <c r="BA3" s="48" t="n"/>
+      <c r="BB3" s="49" t="n"/>
       <c r="BC3" s="26" t="inlineStr">
         <is>
           <t>FECHA:</t>
         </is>
       </c>
-      <c r="BD3" s="46" t="n"/>
-      <c r="BE3" s="46" t="n"/>
-      <c r="BF3" s="46" t="n"/>
-      <c r="BG3" s="46" t="n"/>
-      <c r="BH3" s="46" t="n"/>
-      <c r="BI3" s="46" t="n"/>
-      <c r="BJ3" s="46" t="n"/>
-      <c r="BK3" s="46" t="n"/>
-      <c r="BL3" s="46" t="n"/>
-      <c r="BM3" s="46" t="n"/>
-      <c r="BN3" s="47" t="n"/>
+      <c r="BD3" s="50" t="n"/>
+      <c r="BE3" s="50" t="n"/>
+      <c r="BF3" s="50" t="n"/>
+      <c r="BG3" s="50" t="n"/>
+      <c r="BH3" s="50" t="n"/>
+      <c r="BI3" s="50" t="n"/>
+      <c r="BJ3" s="50" t="n"/>
+      <c r="BK3" s="50" t="n"/>
+      <c r="BL3" s="50" t="n"/>
+      <c r="BM3" s="50" t="n"/>
+      <c r="BN3" s="51" t="n"/>
       <c r="BO3" s="25" t="inlineStr">
         <is>
           <t>JULIO 23 DEL 2026</t>
         </is>
       </c>
-      <c r="BP3" s="48" t="n"/>
-      <c r="BQ3" s="48" t="n"/>
-      <c r="BR3" s="48" t="n"/>
-      <c r="BS3" s="48" t="n"/>
-      <c r="BT3" s="48" t="n"/>
-      <c r="BU3" s="48" t="n"/>
-      <c r="BV3" s="48" t="n"/>
-      <c r="BW3" s="48" t="n"/>
-      <c r="BX3" s="48" t="n"/>
-      <c r="BY3" s="48" t="n"/>
-      <c r="BZ3" s="49" t="n"/>
+      <c r="BP3" s="52" t="n"/>
+      <c r="BQ3" s="52" t="n"/>
+      <c r="BR3" s="52" t="n"/>
+      <c r="BS3" s="52" t="n"/>
+      <c r="BT3" s="52" t="n"/>
+      <c r="BU3" s="52" t="n"/>
+      <c r="BV3" s="52" t="n"/>
+      <c r="BW3" s="52" t="n"/>
+      <c r="BX3" s="52" t="n"/>
+      <c r="BY3" s="52" t="n"/>
+      <c r="BZ3" s="53" t="n"/>
     </row>
     <row r="4" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A4" s="50" t="n"/>
-      <c r="M4" s="51" t="n"/>
-      <c r="N4" s="50" t="n"/>
-      <c r="Y4" s="51" t="n"/>
-      <c r="Z4" s="52" t="n"/>
-      <c r="AA4" s="53" t="n"/>
-      <c r="AB4" s="53" t="n"/>
-      <c r="AC4" s="53" t="n"/>
-      <c r="AD4" s="53" t="n"/>
-      <c r="AE4" s="53" t="n"/>
-      <c r="AF4" s="53" t="n"/>
-      <c r="AG4" s="53" t="n"/>
-      <c r="AH4" s="53" t="n"/>
-      <c r="AI4" s="53" t="n"/>
-      <c r="AJ4" s="53" t="n"/>
-      <c r="AK4" s="53" t="n"/>
-      <c r="AL4" s="53" t="n"/>
-      <c r="AM4" s="53" t="n"/>
-      <c r="AN4" s="53" t="n"/>
-      <c r="AO4" s="53" t="n"/>
-      <c r="AP4" s="53" t="n"/>
-      <c r="AQ4" s="53" t="n"/>
-      <c r="AR4" s="53" t="n"/>
-      <c r="AS4" s="53" t="n"/>
-      <c r="AT4" s="53" t="n"/>
-      <c r="AU4" s="53" t="n"/>
-      <c r="AV4" s="53" t="n"/>
-      <c r="AW4" s="53" t="n"/>
-      <c r="AX4" s="53" t="n"/>
-      <c r="AY4" s="53" t="n"/>
-      <c r="AZ4" s="53" t="n"/>
-      <c r="BA4" s="53" t="n"/>
-      <c r="BB4" s="54" t="n"/>
+      <c r="A4" s="54" t="n"/>
+      <c r="B4" s="55" t="n"/>
+      <c r="C4" s="55" t="n"/>
+      <c r="D4" s="55" t="n"/>
+      <c r="E4" s="55" t="n"/>
+      <c r="F4" s="55" t="n"/>
+      <c r="G4" s="55" t="n"/>
+      <c r="H4" s="55" t="n"/>
+      <c r="I4" s="55" t="n"/>
+      <c r="J4" s="55" t="n"/>
+      <c r="K4" s="55" t="n"/>
+      <c r="L4" s="55" t="n"/>
+      <c r="M4" s="56" t="n"/>
+      <c r="N4" s="54" t="n"/>
+      <c r="O4" s="55" t="n"/>
+      <c r="Y4" s="57" t="n"/>
+      <c r="Z4" s="58" t="n"/>
+      <c r="AA4" s="59" t="n"/>
+      <c r="AB4" s="59" t="n"/>
+      <c r="AC4" s="59" t="n"/>
+      <c r="AD4" s="59" t="n"/>
+      <c r="AE4" s="59" t="n"/>
+      <c r="AF4" s="59" t="n"/>
+      <c r="AG4" s="59" t="n"/>
+      <c r="AH4" s="59" t="n"/>
+      <c r="AI4" s="59" t="n"/>
+      <c r="AJ4" s="59" t="n"/>
+      <c r="AK4" s="59" t="n"/>
+      <c r="AL4" s="59" t="n"/>
+      <c r="AM4" s="59" t="n"/>
+      <c r="AN4" s="59" t="n"/>
+      <c r="AO4" s="59" t="n"/>
+      <c r="AP4" s="59" t="n"/>
+      <c r="AQ4" s="59" t="n"/>
+      <c r="AR4" s="59" t="n"/>
+      <c r="AS4" s="59" t="n"/>
+      <c r="AT4" s="59" t="n"/>
+      <c r="AU4" s="59" t="n"/>
+      <c r="AV4" s="59" t="n"/>
+      <c r="AW4" s="59" t="n"/>
+      <c r="AX4" s="59" t="n"/>
+      <c r="AY4" s="59" t="n"/>
+      <c r="AZ4" s="59" t="n"/>
+      <c r="BA4" s="59" t="n"/>
+      <c r="BB4" s="60" t="n"/>
       <c r="BC4" s="26" t="inlineStr">
         <is>
           <t>ELABORO:</t>
         </is>
       </c>
-      <c r="BD4" s="46" t="n"/>
-      <c r="BE4" s="46" t="n"/>
-      <c r="BF4" s="46" t="n"/>
-      <c r="BG4" s="46" t="n"/>
-      <c r="BH4" s="46" t="n"/>
-      <c r="BI4" s="46" t="n"/>
-      <c r="BJ4" s="46" t="n"/>
-      <c r="BK4" s="46" t="n"/>
-      <c r="BL4" s="46" t="n"/>
-      <c r="BM4" s="46" t="n"/>
-      <c r="BN4" s="47" t="n"/>
+      <c r="BD4" s="50" t="n"/>
+      <c r="BE4" s="50" t="n"/>
+      <c r="BF4" s="50" t="n"/>
+      <c r="BG4" s="50" t="n"/>
+      <c r="BH4" s="50" t="n"/>
+      <c r="BI4" s="50" t="n"/>
+      <c r="BJ4" s="50" t="n"/>
+      <c r="BK4" s="50" t="n"/>
+      <c r="BL4" s="50" t="n"/>
+      <c r="BM4" s="50" t="n"/>
+      <c r="BN4" s="51" t="n"/>
       <c r="BO4" s="25" t="inlineStr">
         <is>
           <t>J.ARBOLEDA</t>
         </is>
       </c>
-      <c r="BP4" s="48" t="n"/>
-      <c r="BQ4" s="48" t="n"/>
-      <c r="BR4" s="48" t="n"/>
-      <c r="BS4" s="48" t="n"/>
-      <c r="BT4" s="48" t="n"/>
-      <c r="BU4" s="48" t="n"/>
-      <c r="BV4" s="48" t="n"/>
-      <c r="BW4" s="48" t="n"/>
-      <c r="BX4" s="48" t="n"/>
-      <c r="BY4" s="48" t="n"/>
-      <c r="BZ4" s="49" t="n"/>
+      <c r="BP4" s="52" t="n"/>
+      <c r="BQ4" s="52" t="n"/>
+      <c r="BR4" s="52" t="n"/>
+      <c r="BS4" s="52" t="n"/>
+      <c r="BT4" s="52" t="n"/>
+      <c r="BU4" s="52" t="n"/>
+      <c r="BV4" s="52" t="n"/>
+      <c r="BW4" s="52" t="n"/>
+      <c r="BX4" s="52" t="n"/>
+      <c r="BY4" s="52" t="n"/>
+      <c r="BZ4" s="53" t="n"/>
     </row>
     <row r="5" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A5" s="52" t="n"/>
-      <c r="B5" s="53" t="n"/>
-      <c r="C5" s="53" t="n"/>
-      <c r="D5" s="53" t="n"/>
-      <c r="E5" s="53" t="n"/>
-      <c r="F5" s="53" t="n"/>
-      <c r="G5" s="53" t="n"/>
-      <c r="H5" s="53" t="n"/>
-      <c r="I5" s="53" t="n"/>
-      <c r="J5" s="53" t="n"/>
-      <c r="K5" s="53" t="n"/>
-      <c r="L5" s="53" t="n"/>
-      <c r="M5" s="54" t="n"/>
-      <c r="N5" s="52" t="n"/>
-      <c r="O5" s="53" t="n"/>
-      <c r="P5" s="53" t="n"/>
-      <c r="Q5" s="53" t="n"/>
-      <c r="R5" s="53" t="n"/>
-      <c r="S5" s="53" t="n"/>
-      <c r="T5" s="53" t="n"/>
-      <c r="U5" s="53" t="n"/>
-      <c r="V5" s="53" t="n"/>
-      <c r="W5" s="53" t="n"/>
-      <c r="X5" s="53" t="n"/>
-      <c r="Y5" s="54" t="n"/>
+      <c r="A5" s="61" t="n"/>
+      <c r="B5" s="62" t="n"/>
+      <c r="C5" s="62" t="n"/>
+      <c r="D5" s="62" t="n"/>
+      <c r="E5" s="62" t="n"/>
+      <c r="F5" s="62" t="n"/>
+      <c r="G5" s="62" t="n"/>
+      <c r="H5" s="62" t="n"/>
+      <c r="I5" s="62" t="n"/>
+      <c r="J5" s="62" t="n"/>
+      <c r="K5" s="62" t="n"/>
+      <c r="L5" s="62" t="n"/>
+      <c r="M5" s="63" t="n"/>
+      <c r="N5" s="61" t="n"/>
+      <c r="O5" s="62" t="n"/>
+      <c r="P5" s="59" t="n"/>
+      <c r="Q5" s="59" t="n"/>
+      <c r="R5" s="59" t="n"/>
+      <c r="S5" s="59" t="n"/>
+      <c r="T5" s="59" t="n"/>
+      <c r="U5" s="59" t="n"/>
+      <c r="V5" s="59" t="n"/>
+      <c r="W5" s="59" t="n"/>
+      <c r="X5" s="59" t="n"/>
+      <c r="Y5" s="60" t="n"/>
       <c r="Z5" s="31" t="inlineStr">
         <is>
           <t>HOJA DE DATOS Y ESPECIFICACIONES TÉCNICAS DEL SISTEMA DE FILTRACIÓN MERV 13-14</t>
         </is>
       </c>
-      <c r="AA5" s="44" t="n"/>
-      <c r="AB5" s="44" t="n"/>
-      <c r="AC5" s="44" t="n"/>
-      <c r="AD5" s="44" t="n"/>
-      <c r="AE5" s="44" t="n"/>
-      <c r="AF5" s="44" t="n"/>
-      <c r="AG5" s="44" t="n"/>
-      <c r="AH5" s="44" t="n"/>
-      <c r="AI5" s="44" t="n"/>
-      <c r="AJ5" s="44" t="n"/>
-      <c r="AK5" s="44" t="n"/>
-      <c r="AL5" s="44" t="n"/>
-      <c r="AM5" s="44" t="n"/>
-      <c r="AN5" s="44" t="n"/>
-      <c r="AO5" s="44" t="n"/>
-      <c r="AP5" s="44" t="n"/>
-      <c r="AQ5" s="44" t="n"/>
-      <c r="AR5" s="44" t="n"/>
-      <c r="AS5" s="44" t="n"/>
-      <c r="AT5" s="44" t="n"/>
-      <c r="AU5" s="44" t="n"/>
-      <c r="AV5" s="44" t="n"/>
-      <c r="AW5" s="44" t="n"/>
-      <c r="AX5" s="44" t="n"/>
-      <c r="AY5" s="44" t="n"/>
-      <c r="AZ5" s="44" t="n"/>
-      <c r="BA5" s="44" t="n"/>
-      <c r="BB5" s="45" t="n"/>
+      <c r="AA5" s="48" t="n"/>
+      <c r="AB5" s="48" t="n"/>
+      <c r="AC5" s="48" t="n"/>
+      <c r="AD5" s="48" t="n"/>
+      <c r="AE5" s="48" t="n"/>
+      <c r="AF5" s="48" t="n"/>
+      <c r="AG5" s="48" t="n"/>
+      <c r="AH5" s="48" t="n"/>
+      <c r="AI5" s="48" t="n"/>
+      <c r="AJ5" s="48" t="n"/>
+      <c r="AK5" s="48" t="n"/>
+      <c r="AL5" s="48" t="n"/>
+      <c r="AM5" s="48" t="n"/>
+      <c r="AN5" s="48" t="n"/>
+      <c r="AO5" s="48" t="n"/>
+      <c r="AP5" s="48" t="n"/>
+      <c r="AQ5" s="48" t="n"/>
+      <c r="AR5" s="48" t="n"/>
+      <c r="AS5" s="48" t="n"/>
+      <c r="AT5" s="48" t="n"/>
+      <c r="AU5" s="48" t="n"/>
+      <c r="AV5" s="48" t="n"/>
+      <c r="AW5" s="48" t="n"/>
+      <c r="AX5" s="48" t="n"/>
+      <c r="AY5" s="48" t="n"/>
+      <c r="AZ5" s="48" t="n"/>
+      <c r="BA5" s="48" t="n"/>
+      <c r="BB5" s="49" t="n"/>
       <c r="BC5" s="26" t="inlineStr">
         <is>
           <t>REVISO:</t>
         </is>
       </c>
-      <c r="BD5" s="46" t="n"/>
-      <c r="BE5" s="46" t="n"/>
-      <c r="BF5" s="46" t="n"/>
-      <c r="BG5" s="46" t="n"/>
-      <c r="BH5" s="46" t="n"/>
-      <c r="BI5" s="46" t="n"/>
-      <c r="BJ5" s="46" t="n"/>
-      <c r="BK5" s="46" t="n"/>
-      <c r="BL5" s="46" t="n"/>
-      <c r="BM5" s="46" t="n"/>
-      <c r="BN5" s="47" t="n"/>
+      <c r="BD5" s="50" t="n"/>
+      <c r="BE5" s="50" t="n"/>
+      <c r="BF5" s="50" t="n"/>
+      <c r="BG5" s="50" t="n"/>
+      <c r="BH5" s="50" t="n"/>
+      <c r="BI5" s="50" t="n"/>
+      <c r="BJ5" s="50" t="n"/>
+      <c r="BK5" s="50" t="n"/>
+      <c r="BL5" s="50" t="n"/>
+      <c r="BM5" s="50" t="n"/>
+      <c r="BN5" s="51" t="n"/>
       <c r="BO5" s="25" t="inlineStr">
         <is>
           <t>F.NAVIA</t>
         </is>
       </c>
-      <c r="BP5" s="48" t="n"/>
-      <c r="BQ5" s="48" t="n"/>
-      <c r="BR5" s="48" t="n"/>
-      <c r="BS5" s="48" t="n"/>
-      <c r="BT5" s="48" t="n"/>
-      <c r="BU5" s="48" t="n"/>
-      <c r="BV5" s="48" t="n"/>
-      <c r="BW5" s="48" t="n"/>
-      <c r="BX5" s="48" t="n"/>
-      <c r="BY5" s="48" t="n"/>
-      <c r="BZ5" s="49" t="n"/>
+      <c r="BP5" s="52" t="n"/>
+      <c r="BQ5" s="52" t="n"/>
+      <c r="BR5" s="52" t="n"/>
+      <c r="BS5" s="52" t="n"/>
+      <c r="BT5" s="52" t="n"/>
+      <c r="BU5" s="52" t="n"/>
+      <c r="BV5" s="52" t="n"/>
+      <c r="BW5" s="52" t="n"/>
+      <c r="BX5" s="52" t="n"/>
+      <c r="BY5" s="52" t="n"/>
+      <c r="BZ5" s="53" t="n"/>
     </row>
     <row r="6" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>PROYECTO</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n"/>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="46" t="n"/>
-      <c r="E6" s="46" t="n"/>
-      <c r="F6" s="46" t="n"/>
-      <c r="G6" s="46" t="n"/>
-      <c r="H6" s="46" t="n"/>
-      <c r="I6" s="46" t="n"/>
-      <c r="J6" s="46" t="n"/>
-      <c r="K6" s="46" t="n"/>
-      <c r="L6" s="46" t="n"/>
-      <c r="M6" s="47" t="n"/>
-      <c r="N6" s="28" t="inlineStr">
+      <c r="B6" s="65" t="n"/>
+      <c r="C6" s="65" t="n"/>
+      <c r="D6" s="65" t="n"/>
+      <c r="E6" s="65" t="n"/>
+      <c r="F6" s="65" t="n"/>
+      <c r="G6" s="65" t="n"/>
+      <c r="H6" s="65" t="n"/>
+      <c r="I6" s="65" t="n"/>
+      <c r="J6" s="65" t="n"/>
+      <c r="K6" s="65" t="n"/>
+      <c r="L6" s="65" t="n"/>
+      <c r="M6" s="66" t="n"/>
+      <c r="N6" s="64" t="inlineStr">
         <is>
           <t>P2437</t>
         </is>
       </c>
-      <c r="O6" s="46" t="n"/>
-      <c r="P6" s="46" t="n"/>
-      <c r="Q6" s="46" t="n"/>
-      <c r="R6" s="46" t="n"/>
-      <c r="S6" s="46" t="n"/>
-      <c r="T6" s="46" t="n"/>
-      <c r="U6" s="46" t="n"/>
-      <c r="V6" s="46" t="n"/>
-      <c r="W6" s="46" t="n"/>
-      <c r="X6" s="46" t="n"/>
-      <c r="Y6" s="47" t="n"/>
-      <c r="Z6" s="52" t="n"/>
-      <c r="AA6" s="53" t="n"/>
-      <c r="AB6" s="53" t="n"/>
-      <c r="AC6" s="53" t="n"/>
-      <c r="AD6" s="53" t="n"/>
-      <c r="AE6" s="53" t="n"/>
-      <c r="AF6" s="53" t="n"/>
-      <c r="AG6" s="53" t="n"/>
-      <c r="AH6" s="53" t="n"/>
-      <c r="AI6" s="53" t="n"/>
-      <c r="AJ6" s="53" t="n"/>
-      <c r="AK6" s="53" t="n"/>
-      <c r="AL6" s="53" t="n"/>
-      <c r="AM6" s="53" t="n"/>
-      <c r="AN6" s="53" t="n"/>
-      <c r="AO6" s="53" t="n"/>
-      <c r="AP6" s="53" t="n"/>
-      <c r="AQ6" s="53" t="n"/>
-      <c r="AR6" s="53" t="n"/>
-      <c r="AS6" s="53" t="n"/>
-      <c r="AT6" s="53" t="n"/>
-      <c r="AU6" s="53" t="n"/>
-      <c r="AV6" s="53" t="n"/>
-      <c r="AW6" s="53" t="n"/>
-      <c r="AX6" s="53" t="n"/>
-      <c r="AY6" s="53" t="n"/>
-      <c r="AZ6" s="53" t="n"/>
-      <c r="BA6" s="53" t="n"/>
-      <c r="BB6" s="54" t="n"/>
+      <c r="O6" s="65" t="n"/>
+      <c r="P6" s="50" t="n"/>
+      <c r="Q6" s="50" t="n"/>
+      <c r="R6" s="50" t="n"/>
+      <c r="S6" s="50" t="n"/>
+      <c r="T6" s="50" t="n"/>
+      <c r="U6" s="50" t="n"/>
+      <c r="V6" s="50" t="n"/>
+      <c r="W6" s="50" t="n"/>
+      <c r="X6" s="50" t="n"/>
+      <c r="Y6" s="51" t="n"/>
+      <c r="Z6" s="58" t="n"/>
+      <c r="AA6" s="59" t="n"/>
+      <c r="AB6" s="59" t="n"/>
+      <c r="AC6" s="59" t="n"/>
+      <c r="AD6" s="59" t="n"/>
+      <c r="AE6" s="59" t="n"/>
+      <c r="AF6" s="59" t="n"/>
+      <c r="AG6" s="59" t="n"/>
+      <c r="AH6" s="59" t="n"/>
+      <c r="AI6" s="59" t="n"/>
+      <c r="AJ6" s="59" t="n"/>
+      <c r="AK6" s="59" t="n"/>
+      <c r="AL6" s="59" t="n"/>
+      <c r="AM6" s="59" t="n"/>
+      <c r="AN6" s="59" t="n"/>
+      <c r="AO6" s="59" t="n"/>
+      <c r="AP6" s="59" t="n"/>
+      <c r="AQ6" s="59" t="n"/>
+      <c r="AR6" s="59" t="n"/>
+      <c r="AS6" s="59" t="n"/>
+      <c r="AT6" s="59" t="n"/>
+      <c r="AU6" s="59" t="n"/>
+      <c r="AV6" s="59" t="n"/>
+      <c r="AW6" s="59" t="n"/>
+      <c r="AX6" s="59" t="n"/>
+      <c r="AY6" s="59" t="n"/>
+      <c r="AZ6" s="59" t="n"/>
+      <c r="BA6" s="59" t="n"/>
+      <c r="BB6" s="60" t="n"/>
       <c r="BC6" s="26" t="inlineStr">
         <is>
           <t>APROBO:</t>
         </is>
       </c>
-      <c r="BD6" s="46" t="n"/>
-      <c r="BE6" s="46" t="n"/>
-      <c r="BF6" s="46" t="n"/>
-      <c r="BG6" s="46" t="n"/>
-      <c r="BH6" s="46" t="n"/>
-      <c r="BI6" s="46" t="n"/>
-      <c r="BJ6" s="46" t="n"/>
-      <c r="BK6" s="46" t="n"/>
-      <c r="BL6" s="46" t="n"/>
-      <c r="BM6" s="46" t="n"/>
-      <c r="BN6" s="47" t="n"/>
+      <c r="BD6" s="50" t="n"/>
+      <c r="BE6" s="50" t="n"/>
+      <c r="BF6" s="50" t="n"/>
+      <c r="BG6" s="50" t="n"/>
+      <c r="BH6" s="50" t="n"/>
+      <c r="BI6" s="50" t="n"/>
+      <c r="BJ6" s="50" t="n"/>
+      <c r="BK6" s="50" t="n"/>
+      <c r="BL6" s="50" t="n"/>
+      <c r="BM6" s="50" t="n"/>
+      <c r="BN6" s="51" t="n"/>
       <c r="BO6" s="25" t="inlineStr">
         <is>
           <t>H.ROSERO</t>
         </is>
       </c>
-      <c r="BP6" s="48" t="n"/>
-      <c r="BQ6" s="48" t="n"/>
-      <c r="BR6" s="48" t="n"/>
-      <c r="BS6" s="48" t="n"/>
-      <c r="BT6" s="48" t="n"/>
-      <c r="BU6" s="48" t="n"/>
-      <c r="BV6" s="48" t="n"/>
-      <c r="BW6" s="48" t="n"/>
-      <c r="BX6" s="48" t="n"/>
-      <c r="BY6" s="48" t="n"/>
-      <c r="BZ6" s="49" t="n"/>
+      <c r="BP6" s="52" t="n"/>
+      <c r="BQ6" s="52" t="n"/>
+      <c r="BR6" s="52" t="n"/>
+      <c r="BS6" s="52" t="n"/>
+      <c r="BT6" s="52" t="n"/>
+      <c r="BU6" s="52" t="n"/>
+      <c r="BV6" s="52" t="n"/>
+      <c r="BW6" s="52" t="n"/>
+      <c r="BX6" s="52" t="n"/>
+      <c r="BY6" s="52" t="n"/>
+      <c r="BZ6" s="53" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="21" t="n"/>
+      <c r="A7" s="55" t="n"/>
+      <c r="B7" s="55" t="n"/>
+      <c r="C7" s="55" t="n"/>
+      <c r="D7" s="55" t="n"/>
+      <c r="E7" s="55" t="n"/>
+      <c r="F7" s="55" t="n"/>
+      <c r="G7" s="67" t="n"/>
+      <c r="H7" s="67" t="n"/>
+      <c r="I7" s="67" t="n"/>
+      <c r="J7" s="67" t="n"/>
+      <c r="K7" s="67" t="n"/>
+      <c r="L7" s="67" t="n"/>
+      <c r="M7" s="67" t="n"/>
+      <c r="N7" s="67" t="n"/>
+      <c r="O7" s="67" t="n"/>
       <c r="P7" s="21" t="n"/>
       <c r="Q7" s="21" t="n"/>
       <c r="R7" s="21" t="n"/>
@@ -1607,15 +1757,21 @@
       <c r="CD7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="G8" s="21" t="n"/>
-      <c r="H8" s="21" t="n"/>
-      <c r="I8" s="21" t="n"/>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="21" t="n"/>
+      <c r="A8" s="55" t="n"/>
+      <c r="B8" s="55" t="n"/>
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="55" t="n"/>
+      <c r="E8" s="55" t="n"/>
+      <c r="F8" s="55" t="n"/>
+      <c r="G8" s="67" t="n"/>
+      <c r="H8" s="67" t="n"/>
+      <c r="I8" s="67" t="n"/>
+      <c r="J8" s="67" t="n"/>
+      <c r="K8" s="67" t="n"/>
+      <c r="L8" s="67" t="n"/>
+      <c r="M8" s="67" t="n"/>
+      <c r="N8" s="67" t="n"/>
+      <c r="O8" s="67" t="n"/>
       <c r="P8" s="21" t="n"/>
       <c r="Q8" s="21" t="n"/>
       <c r="R8" s="21" t="n"/>
@@ -1636,15 +1792,21 @@
       <c r="CD8" s="7" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="21" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="21" t="n"/>
+      <c r="A9" s="55" t="n"/>
+      <c r="B9" s="55" t="n"/>
+      <c r="C9" s="55" t="n"/>
+      <c r="D9" s="55" t="n"/>
+      <c r="E9" s="55" t="n"/>
+      <c r="F9" s="55" t="n"/>
+      <c r="G9" s="67" t="n"/>
+      <c r="H9" s="67" t="n"/>
+      <c r="I9" s="67" t="n"/>
+      <c r="J9" s="67" t="n"/>
+      <c r="K9" s="67" t="n"/>
+      <c r="L9" s="67" t="n"/>
+      <c r="M9" s="67" t="n"/>
+      <c r="N9" s="67" t="n"/>
+      <c r="O9" s="67" t="n"/>
       <c r="P9" s="21" t="n"/>
       <c r="Q9" s="21" t="n"/>
       <c r="R9" s="21" t="n"/>
@@ -1665,15 +1827,21 @@
       <c r="CD9" s="7" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="21" t="n"/>
-      <c r="J10" s="21" t="n"/>
-      <c r="K10" s="21" t="n"/>
-      <c r="L10" s="21" t="n"/>
-      <c r="M10" s="21" t="n"/>
-      <c r="N10" s="21" t="n"/>
-      <c r="O10" s="21" t="n"/>
+      <c r="A10" s="55" t="n"/>
+      <c r="B10" s="55" t="n"/>
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="55" t="n"/>
+      <c r="E10" s="55" t="n"/>
+      <c r="F10" s="55" t="n"/>
+      <c r="G10" s="67" t="n"/>
+      <c r="H10" s="67" t="n"/>
+      <c r="I10" s="67" t="n"/>
+      <c r="J10" s="67" t="n"/>
+      <c r="K10" s="67" t="n"/>
+      <c r="L10" s="67" t="n"/>
+      <c r="M10" s="67" t="n"/>
+      <c r="N10" s="67" t="n"/>
+      <c r="O10" s="67" t="n"/>
       <c r="P10" s="21" t="n"/>
       <c r="Q10" s="21" t="n"/>
       <c r="R10" s="21" t="n"/>
@@ -1694,15 +1862,21 @@
       <c r="CD10" s="7" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="21" t="n"/>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="21" t="n"/>
+      <c r="A11" s="55" t="n"/>
+      <c r="B11" s="55" t="n"/>
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="55" t="n"/>
+      <c r="E11" s="55" t="n"/>
+      <c r="F11" s="55" t="n"/>
+      <c r="G11" s="67" t="n"/>
+      <c r="H11" s="67" t="n"/>
+      <c r="I11" s="67" t="n"/>
+      <c r="J11" s="67" t="n"/>
+      <c r="K11" s="67" t="n"/>
+      <c r="L11" s="67" t="n"/>
+      <c r="M11" s="67" t="n"/>
+      <c r="N11" s="67" t="n"/>
+      <c r="O11" s="67" t="n"/>
       <c r="P11" s="21" t="n"/>
       <c r="Q11" s="21" t="n"/>
       <c r="R11" s="21" t="n"/>
@@ -1723,15 +1897,21 @@
       <c r="CD11" s="7" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
-      <c r="J12" s="21" t="n"/>
-      <c r="K12" s="21" t="n"/>
-      <c r="L12" s="21" t="n"/>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="21" t="n"/>
+      <c r="A12" s="55" t="n"/>
+      <c r="B12" s="55" t="n"/>
+      <c r="C12" s="55" t="n"/>
+      <c r="D12" s="55" t="n"/>
+      <c r="E12" s="55" t="n"/>
+      <c r="F12" s="55" t="n"/>
+      <c r="G12" s="67" t="n"/>
+      <c r="H12" s="67" t="n"/>
+      <c r="I12" s="67" t="n"/>
+      <c r="J12" s="67" t="n"/>
+      <c r="K12" s="67" t="n"/>
+      <c r="L12" s="67" t="n"/>
+      <c r="M12" s="67" t="n"/>
+      <c r="N12" s="67" t="n"/>
+      <c r="O12" s="67" t="n"/>
       <c r="P12" s="21" t="n"/>
       <c r="Q12" s="21" t="n"/>
       <c r="R12" s="21" t="n"/>
@@ -1752,15 +1932,21 @@
       <c r="CD12" s="7" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="21" t="n"/>
-      <c r="J13" s="21" t="n"/>
-      <c r="K13" s="21" t="n"/>
-      <c r="L13" s="21" t="n"/>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="21" t="n"/>
-      <c r="O13" s="21" t="n"/>
+      <c r="A13" s="55" t="n"/>
+      <c r="B13" s="55" t="n"/>
+      <c r="C13" s="55" t="n"/>
+      <c r="D13" s="55" t="n"/>
+      <c r="E13" s="55" t="n"/>
+      <c r="F13" s="55" t="n"/>
+      <c r="G13" s="67" t="n"/>
+      <c r="H13" s="67" t="n"/>
+      <c r="I13" s="67" t="n"/>
+      <c r="J13" s="67" t="n"/>
+      <c r="K13" s="67" t="n"/>
+      <c r="L13" s="67" t="n"/>
+      <c r="M13" s="67" t="n"/>
+      <c r="N13" s="67" t="n"/>
+      <c r="O13" s="67" t="n"/>
       <c r="P13" s="21" t="n"/>
       <c r="Q13" s="21" t="n"/>
       <c r="R13" s="21" t="n"/>
@@ -1781,15 +1967,21 @@
       <c r="CD13" s="7" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="21" t="n"/>
+      <c r="A14" s="55" t="n"/>
+      <c r="B14" s="55" t="n"/>
+      <c r="C14" s="55" t="n"/>
+      <c r="D14" s="55" t="n"/>
+      <c r="E14" s="55" t="n"/>
+      <c r="F14" s="55" t="n"/>
+      <c r="G14" s="67" t="n"/>
+      <c r="H14" s="67" t="n"/>
+      <c r="I14" s="67" t="n"/>
+      <c r="J14" s="67" t="n"/>
+      <c r="K14" s="67" t="n"/>
+      <c r="L14" s="67" t="n"/>
+      <c r="M14" s="67" t="n"/>
+      <c r="N14" s="67" t="n"/>
+      <c r="O14" s="67" t="n"/>
       <c r="P14" s="21" t="n"/>
       <c r="Q14" s="21" t="n"/>
       <c r="R14" s="21" t="n"/>
@@ -1810,15 +2002,21 @@
       <c r="CD14" s="7" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="21" t="n"/>
+      <c r="A15" s="55" t="n"/>
+      <c r="B15" s="55" t="n"/>
+      <c r="C15" s="55" t="n"/>
+      <c r="D15" s="55" t="n"/>
+      <c r="E15" s="55" t="n"/>
+      <c r="F15" s="55" t="n"/>
+      <c r="G15" s="67" t="n"/>
+      <c r="H15" s="67" t="n"/>
+      <c r="I15" s="67" t="n"/>
+      <c r="J15" s="67" t="n"/>
+      <c r="K15" s="67" t="n"/>
+      <c r="L15" s="67" t="n"/>
+      <c r="M15" s="67" t="n"/>
+      <c r="N15" s="67" t="n"/>
+      <c r="O15" s="67" t="n"/>
       <c r="P15" s="21" t="n"/>
       <c r="Q15" s="21" t="n"/>
       <c r="R15" s="21" t="n"/>
@@ -1839,15 +2037,21 @@
       <c r="CD15" s="7" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="21" t="n"/>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
+      <c r="A16" s="55" t="n"/>
+      <c r="B16" s="55" t="n"/>
+      <c r="C16" s="55" t="n"/>
+      <c r="D16" s="55" t="n"/>
+      <c r="E16" s="55" t="n"/>
+      <c r="F16" s="55" t="n"/>
+      <c r="G16" s="67" t="n"/>
+      <c r="H16" s="67" t="n"/>
+      <c r="I16" s="67" t="n"/>
+      <c r="J16" s="67" t="n"/>
+      <c r="K16" s="67" t="n"/>
+      <c r="L16" s="67" t="n"/>
+      <c r="M16" s="67" t="n"/>
+      <c r="N16" s="67" t="n"/>
+      <c r="O16" s="67" t="n"/>
       <c r="P16" s="21" t="n"/>
       <c r="Q16" s="21" t="n"/>
       <c r="R16" s="21" t="n"/>
@@ -1868,15 +2072,21 @@
       <c r="CD16" s="7" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
+      <c r="A17" s="55" t="n"/>
+      <c r="B17" s="55" t="n"/>
+      <c r="C17" s="55" t="n"/>
+      <c r="D17" s="55" t="n"/>
+      <c r="E17" s="55" t="n"/>
+      <c r="F17" s="55" t="n"/>
+      <c r="G17" s="67" t="n"/>
+      <c r="H17" s="67" t="n"/>
+      <c r="I17" s="67" t="n"/>
+      <c r="J17" s="67" t="n"/>
+      <c r="K17" s="67" t="n"/>
+      <c r="L17" s="67" t="n"/>
+      <c r="M17" s="67" t="n"/>
+      <c r="N17" s="67" t="n"/>
+      <c r="O17" s="67" t="n"/>
       <c r="P17" s="21" t="n"/>
       <c r="Q17" s="21" t="n"/>
       <c r="R17" s="21" t="n"/>
@@ -1897,15 +2107,21 @@
       <c r="CD17" s="7" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
+      <c r="A18" s="55" t="n"/>
+      <c r="B18" s="55" t="n"/>
+      <c r="C18" s="55" t="n"/>
+      <c r="D18" s="55" t="n"/>
+      <c r="E18" s="55" t="n"/>
+      <c r="F18" s="55" t="n"/>
+      <c r="G18" s="67" t="n"/>
+      <c r="H18" s="67" t="n"/>
+      <c r="I18" s="67" t="n"/>
+      <c r="J18" s="67" t="n"/>
+      <c r="K18" s="67" t="n"/>
+      <c r="L18" s="67" t="n"/>
+      <c r="M18" s="67" t="n"/>
+      <c r="N18" s="67" t="n"/>
+      <c r="O18" s="67" t="n"/>
       <c r="P18" s="21" t="n"/>
       <c r="Q18" s="21" t="n"/>
       <c r="R18" s="21" t="n"/>
@@ -1926,15 +2142,21 @@
       <c r="CD18" s="7" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="21" t="n"/>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n"/>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
+      <c r="A19" s="55" t="n"/>
+      <c r="B19" s="55" t="n"/>
+      <c r="C19" s="55" t="n"/>
+      <c r="D19" s="55" t="n"/>
+      <c r="E19" s="55" t="n"/>
+      <c r="F19" s="55" t="n"/>
+      <c r="G19" s="67" t="n"/>
+      <c r="H19" s="67" t="n"/>
+      <c r="I19" s="67" t="n"/>
+      <c r="J19" s="67" t="n"/>
+      <c r="K19" s="67" t="n"/>
+      <c r="L19" s="67" t="n"/>
+      <c r="M19" s="67" t="n"/>
+      <c r="N19" s="67" t="n"/>
+      <c r="O19" s="67" t="n"/>
       <c r="P19" s="21" t="n"/>
       <c r="Q19" s="21" t="n"/>
       <c r="R19" s="21" t="n"/>
@@ -1955,15 +2177,21 @@
       <c r="CD19" s="7" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
+      <c r="A20" s="55" t="n"/>
+      <c r="B20" s="55" t="n"/>
+      <c r="C20" s="55" t="n"/>
+      <c r="D20" s="55" t="n"/>
+      <c r="E20" s="55" t="n"/>
+      <c r="F20" s="55" t="n"/>
+      <c r="G20" s="67" t="n"/>
+      <c r="H20" s="67" t="n"/>
+      <c r="I20" s="67" t="n"/>
+      <c r="J20" s="67" t="n"/>
+      <c r="K20" s="67" t="n"/>
+      <c r="L20" s="67" t="n"/>
+      <c r="M20" s="67" t="n"/>
+      <c r="N20" s="67" t="n"/>
+      <c r="O20" s="67" t="n"/>
       <c r="P20" s="21" t="n"/>
       <c r="Q20" s="21" t="n"/>
       <c r="R20" s="21" t="n"/>
@@ -1984,15 +2212,21 @@
       <c r="CD20" s="7" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="G21" s="21" t="n"/>
-      <c r="H21" s="21" t="n"/>
-      <c r="I21" s="21" t="n"/>
-      <c r="J21" s="21" t="n"/>
-      <c r="K21" s="21" t="n"/>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="21" t="n"/>
-      <c r="N21" s="21" t="n"/>
-      <c r="O21" s="21" t="n"/>
+      <c r="A21" s="55" t="n"/>
+      <c r="B21" s="55" t="n"/>
+      <c r="C21" s="55" t="n"/>
+      <c r="D21" s="55" t="n"/>
+      <c r="E21" s="55" t="n"/>
+      <c r="F21" s="55" t="n"/>
+      <c r="G21" s="67" t="n"/>
+      <c r="H21" s="67" t="n"/>
+      <c r="I21" s="67" t="n"/>
+      <c r="J21" s="67" t="n"/>
+      <c r="K21" s="67" t="n"/>
+      <c r="L21" s="67" t="n"/>
+      <c r="M21" s="67" t="n"/>
+      <c r="N21" s="67" t="n"/>
+      <c r="O21" s="67" t="n"/>
       <c r="P21" s="21" t="n"/>
       <c r="Q21" s="21" t="n"/>
       <c r="R21" s="41" t="inlineStr">
@@ -2000,140 +2234,158 @@
           <t>Elaborado por:</t>
         </is>
       </c>
-      <c r="S21" s="44" t="n"/>
-      <c r="T21" s="44" t="n"/>
-      <c r="U21" s="44" t="n"/>
-      <c r="V21" s="44" t="n"/>
-      <c r="W21" s="44" t="n"/>
-      <c r="X21" s="44" t="n"/>
-      <c r="Y21" s="44" t="n"/>
-      <c r="Z21" s="44" t="n"/>
-      <c r="AA21" s="44" t="n"/>
-      <c r="AB21" s="44" t="n"/>
-      <c r="AC21" s="44" t="n"/>
-      <c r="AD21" s="44" t="n"/>
-      <c r="AE21" s="45" t="n"/>
+      <c r="S21" s="48" t="n"/>
+      <c r="T21" s="48" t="n"/>
+      <c r="U21" s="48" t="n"/>
+      <c r="V21" s="48" t="n"/>
+      <c r="W21" s="48" t="n"/>
+      <c r="X21" s="48" t="n"/>
+      <c r="Y21" s="48" t="n"/>
+      <c r="Z21" s="48" t="n"/>
+      <c r="AA21" s="48" t="n"/>
+      <c r="AB21" s="48" t="n"/>
+      <c r="AC21" s="48" t="n"/>
+      <c r="AD21" s="48" t="n"/>
+      <c r="AE21" s="49" t="n"/>
       <c r="AF21" s="41" t="inlineStr">
         <is>
           <t>Revisado por:</t>
         </is>
       </c>
-      <c r="AG21" s="44" t="n"/>
-      <c r="AH21" s="44" t="n"/>
-      <c r="AI21" s="44" t="n"/>
-      <c r="AJ21" s="44" t="n"/>
-      <c r="AK21" s="44" t="n"/>
-      <c r="AL21" s="44" t="n"/>
-      <c r="AM21" s="44" t="n"/>
-      <c r="AN21" s="44" t="n"/>
-      <c r="AO21" s="44" t="n"/>
-      <c r="AP21" s="44" t="n"/>
-      <c r="AQ21" s="44" t="n"/>
-      <c r="AR21" s="44" t="n"/>
-      <c r="AS21" s="45" t="n"/>
+      <c r="AG21" s="48" t="n"/>
+      <c r="AH21" s="48" t="n"/>
+      <c r="AI21" s="48" t="n"/>
+      <c r="AJ21" s="48" t="n"/>
+      <c r="AK21" s="48" t="n"/>
+      <c r="AL21" s="48" t="n"/>
+      <c r="AM21" s="48" t="n"/>
+      <c r="AN21" s="48" t="n"/>
+      <c r="AO21" s="48" t="n"/>
+      <c r="AP21" s="48" t="n"/>
+      <c r="AQ21" s="48" t="n"/>
+      <c r="AR21" s="48" t="n"/>
+      <c r="AS21" s="49" t="n"/>
       <c r="AT21" s="41" t="inlineStr">
         <is>
           <t>Aprobado por:</t>
         </is>
       </c>
-      <c r="AU21" s="44" t="n"/>
-      <c r="AV21" s="44" t="n"/>
-      <c r="AW21" s="44" t="n"/>
-      <c r="AX21" s="44" t="n"/>
-      <c r="AY21" s="44" t="n"/>
-      <c r="AZ21" s="44" t="n"/>
-      <c r="BA21" s="44" t="n"/>
-      <c r="BB21" s="44" t="n"/>
-      <c r="BC21" s="44" t="n"/>
-      <c r="BD21" s="44" t="n"/>
-      <c r="BE21" s="44" t="n"/>
-      <c r="BF21" s="44" t="n"/>
-      <c r="BG21" s="45" t="n"/>
+      <c r="AU21" s="48" t="n"/>
+      <c r="AV21" s="48" t="n"/>
+      <c r="AW21" s="48" t="n"/>
+      <c r="AX21" s="48" t="n"/>
+      <c r="AY21" s="48" t="n"/>
+      <c r="AZ21" s="48" t="n"/>
+      <c r="BA21" s="48" t="n"/>
+      <c r="BB21" s="48" t="n"/>
+      <c r="BC21" s="48" t="n"/>
+      <c r="BD21" s="48" t="n"/>
+      <c r="BE21" s="48" t="n"/>
+      <c r="BF21" s="48" t="n"/>
+      <c r="BG21" s="49" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="G22" s="21" t="n"/>
-      <c r="H22" s="21" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="21" t="n"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
+      <c r="A22" s="55" t="n"/>
+      <c r="B22" s="55" t="n"/>
+      <c r="C22" s="55" t="n"/>
+      <c r="D22" s="55" t="n"/>
+      <c r="E22" s="55" t="n"/>
+      <c r="F22" s="55" t="n"/>
+      <c r="G22" s="67" t="n"/>
+      <c r="H22" s="67" t="n"/>
+      <c r="I22" s="67" t="n"/>
+      <c r="J22" s="67" t="n"/>
+      <c r="K22" s="67" t="n"/>
+      <c r="L22" s="67" t="n"/>
+      <c r="M22" s="67" t="n"/>
+      <c r="N22" s="67" t="n"/>
+      <c r="O22" s="67" t="n"/>
       <c r="P22" s="21" t="n"/>
       <c r="Q22" s="21" t="n"/>
-      <c r="R22" s="50" t="n"/>
-      <c r="AE22" s="51" t="n"/>
-      <c r="AF22" s="50" t="n"/>
-      <c r="AS22" s="51" t="n"/>
-      <c r="AT22" s="50" t="n"/>
-      <c r="BG22" s="51" t="n"/>
+      <c r="R22" s="68" t="n"/>
+      <c r="AE22" s="57" t="n"/>
+      <c r="AF22" s="68" t="n"/>
+      <c r="AS22" s="57" t="n"/>
+      <c r="AT22" s="68" t="n"/>
+      <c r="BG22" s="57" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="G23" s="21" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="21" t="n"/>
-      <c r="K23" s="21" t="n"/>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="21" t="n"/>
-      <c r="N23" s="21" t="n"/>
-      <c r="O23" s="21" t="n"/>
+      <c r="A23" s="55" t="n"/>
+      <c r="B23" s="55" t="n"/>
+      <c r="C23" s="55" t="n"/>
+      <c r="D23" s="55" t="n"/>
+      <c r="E23" s="55" t="n"/>
+      <c r="F23" s="55" t="n"/>
+      <c r="G23" s="67" t="n"/>
+      <c r="H23" s="67" t="n"/>
+      <c r="I23" s="67" t="n"/>
+      <c r="J23" s="67" t="n"/>
+      <c r="K23" s="67" t="n"/>
+      <c r="L23" s="67" t="n"/>
+      <c r="M23" s="67" t="n"/>
+      <c r="N23" s="67" t="n"/>
+      <c r="O23" s="67" t="n"/>
       <c r="P23" s="21" t="n"/>
       <c r="Q23" s="21" t="n"/>
-      <c r="R23" s="52" t="n"/>
-      <c r="S23" s="53" t="n"/>
-      <c r="T23" s="53" t="n"/>
-      <c r="U23" s="53" t="n"/>
-      <c r="V23" s="53" t="n"/>
-      <c r="W23" s="53" t="n"/>
-      <c r="X23" s="53" t="n"/>
-      <c r="Y23" s="53" t="n"/>
-      <c r="Z23" s="53" t="n"/>
-      <c r="AA23" s="53" t="n"/>
-      <c r="AB23" s="53" t="n"/>
-      <c r="AC23" s="53" t="n"/>
-      <c r="AD23" s="53" t="n"/>
-      <c r="AE23" s="54" t="n"/>
-      <c r="AF23" s="52" t="n"/>
-      <c r="AG23" s="53" t="n"/>
-      <c r="AH23" s="53" t="n"/>
-      <c r="AI23" s="53" t="n"/>
-      <c r="AJ23" s="53" t="n"/>
-      <c r="AK23" s="53" t="n"/>
-      <c r="AL23" s="53" t="n"/>
-      <c r="AM23" s="53" t="n"/>
-      <c r="AN23" s="53" t="n"/>
-      <c r="AO23" s="53" t="n"/>
-      <c r="AP23" s="53" t="n"/>
-      <c r="AQ23" s="53" t="n"/>
-      <c r="AR23" s="53" t="n"/>
-      <c r="AS23" s="54" t="n"/>
-      <c r="AT23" s="52" t="n"/>
-      <c r="AU23" s="53" t="n"/>
-      <c r="AV23" s="53" t="n"/>
-      <c r="AW23" s="53" t="n"/>
-      <c r="AX23" s="53" t="n"/>
-      <c r="AY23" s="53" t="n"/>
-      <c r="AZ23" s="53" t="n"/>
-      <c r="BA23" s="53" t="n"/>
-      <c r="BB23" s="53" t="n"/>
-      <c r="BC23" s="53" t="n"/>
-      <c r="BD23" s="53" t="n"/>
-      <c r="BE23" s="53" t="n"/>
-      <c r="BF23" s="53" t="n"/>
-      <c r="BG23" s="54" t="n"/>
+      <c r="R23" s="58" t="n"/>
+      <c r="S23" s="59" t="n"/>
+      <c r="T23" s="59" t="n"/>
+      <c r="U23" s="59" t="n"/>
+      <c r="V23" s="59" t="n"/>
+      <c r="W23" s="59" t="n"/>
+      <c r="X23" s="59" t="n"/>
+      <c r="Y23" s="59" t="n"/>
+      <c r="Z23" s="59" t="n"/>
+      <c r="AA23" s="59" t="n"/>
+      <c r="AB23" s="59" t="n"/>
+      <c r="AC23" s="59" t="n"/>
+      <c r="AD23" s="59" t="n"/>
+      <c r="AE23" s="60" t="n"/>
+      <c r="AF23" s="58" t="n"/>
+      <c r="AG23" s="59" t="n"/>
+      <c r="AH23" s="59" t="n"/>
+      <c r="AI23" s="59" t="n"/>
+      <c r="AJ23" s="59" t="n"/>
+      <c r="AK23" s="59" t="n"/>
+      <c r="AL23" s="59" t="n"/>
+      <c r="AM23" s="59" t="n"/>
+      <c r="AN23" s="59" t="n"/>
+      <c r="AO23" s="59" t="n"/>
+      <c r="AP23" s="59" t="n"/>
+      <c r="AQ23" s="59" t="n"/>
+      <c r="AR23" s="59" t="n"/>
+      <c r="AS23" s="60" t="n"/>
+      <c r="AT23" s="58" t="n"/>
+      <c r="AU23" s="59" t="n"/>
+      <c r="AV23" s="59" t="n"/>
+      <c r="AW23" s="59" t="n"/>
+      <c r="AX23" s="59" t="n"/>
+      <c r="AY23" s="59" t="n"/>
+      <c r="AZ23" s="59" t="n"/>
+      <c r="BA23" s="59" t="n"/>
+      <c r="BB23" s="59" t="n"/>
+      <c r="BC23" s="59" t="n"/>
+      <c r="BD23" s="59" t="n"/>
+      <c r="BE23" s="59" t="n"/>
+      <c r="BF23" s="59" t="n"/>
+      <c r="BG23" s="60" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
+      <c r="A24" s="55" t="n"/>
+      <c r="B24" s="55" t="n"/>
+      <c r="C24" s="55" t="n"/>
+      <c r="D24" s="55" t="n"/>
+      <c r="E24" s="55" t="n"/>
+      <c r="F24" s="55" t="n"/>
+      <c r="G24" s="67" t="n"/>
+      <c r="H24" s="67" t="n"/>
+      <c r="I24" s="67" t="n"/>
+      <c r="J24" s="67" t="n"/>
+      <c r="K24" s="67" t="n"/>
+      <c r="L24" s="67" t="n"/>
+      <c r="M24" s="67" t="n"/>
+      <c r="N24" s="67" t="n"/>
+      <c r="O24" s="67" t="n"/>
       <c r="P24" s="21" t="n"/>
       <c r="Q24" s="21" t="n"/>
       <c r="R24" s="23" t="inlineStr">
@@ -2141,270 +2393,306 @@
           <t>J.ARBOLEDA</t>
         </is>
       </c>
-      <c r="S24" s="44" t="n"/>
-      <c r="T24" s="44" t="n"/>
-      <c r="U24" s="44" t="n"/>
-      <c r="V24" s="44" t="n"/>
-      <c r="W24" s="44" t="n"/>
-      <c r="X24" s="44" t="n"/>
-      <c r="Y24" s="44" t="n"/>
-      <c r="Z24" s="44" t="n"/>
-      <c r="AA24" s="44" t="n"/>
-      <c r="AB24" s="44" t="n"/>
-      <c r="AC24" s="44" t="n"/>
-      <c r="AD24" s="44" t="n"/>
-      <c r="AE24" s="45" t="n"/>
+      <c r="S24" s="48" t="n"/>
+      <c r="T24" s="48" t="n"/>
+      <c r="U24" s="48" t="n"/>
+      <c r="V24" s="48" t="n"/>
+      <c r="W24" s="48" t="n"/>
+      <c r="X24" s="48" t="n"/>
+      <c r="Y24" s="48" t="n"/>
+      <c r="Z24" s="48" t="n"/>
+      <c r="AA24" s="48" t="n"/>
+      <c r="AB24" s="48" t="n"/>
+      <c r="AC24" s="48" t="n"/>
+      <c r="AD24" s="48" t="n"/>
+      <c r="AE24" s="49" t="n"/>
       <c r="AF24" s="24" t="n"/>
-      <c r="AG24" s="44" t="n"/>
-      <c r="AH24" s="44" t="n"/>
-      <c r="AI24" s="44" t="n"/>
-      <c r="AJ24" s="44" t="n"/>
-      <c r="AK24" s="44" t="n"/>
-      <c r="AL24" s="44" t="n"/>
-      <c r="AM24" s="44" t="n"/>
-      <c r="AN24" s="44" t="n"/>
-      <c r="AO24" s="44" t="n"/>
-      <c r="AP24" s="44" t="n"/>
-      <c r="AQ24" s="44" t="n"/>
-      <c r="AR24" s="44" t="n"/>
-      <c r="AS24" s="45" t="n"/>
+      <c r="AG24" s="48" t="n"/>
+      <c r="AH24" s="48" t="n"/>
+      <c r="AI24" s="48" t="n"/>
+      <c r="AJ24" s="48" t="n"/>
+      <c r="AK24" s="48" t="n"/>
+      <c r="AL24" s="48" t="n"/>
+      <c r="AM24" s="48" t="n"/>
+      <c r="AN24" s="48" t="n"/>
+      <c r="AO24" s="48" t="n"/>
+      <c r="AP24" s="48" t="n"/>
+      <c r="AQ24" s="48" t="n"/>
+      <c r="AR24" s="48" t="n"/>
+      <c r="AS24" s="49" t="n"/>
       <c r="AT24" s="24" t="n"/>
-      <c r="AU24" s="44" t="n"/>
-      <c r="AV24" s="44" t="n"/>
-      <c r="AW24" s="44" t="n"/>
-      <c r="AX24" s="44" t="n"/>
-      <c r="AY24" s="44" t="n"/>
-      <c r="AZ24" s="44" t="n"/>
-      <c r="BA24" s="44" t="n"/>
-      <c r="BB24" s="44" t="n"/>
-      <c r="BC24" s="44" t="n"/>
-      <c r="BD24" s="44" t="n"/>
-      <c r="BE24" s="44" t="n"/>
-      <c r="BF24" s="44" t="n"/>
-      <c r="BG24" s="45" t="n"/>
+      <c r="AU24" s="48" t="n"/>
+      <c r="AV24" s="48" t="n"/>
+      <c r="AW24" s="48" t="n"/>
+      <c r="AX24" s="48" t="n"/>
+      <c r="AY24" s="48" t="n"/>
+      <c r="AZ24" s="48" t="n"/>
+      <c r="BA24" s="48" t="n"/>
+      <c r="BB24" s="48" t="n"/>
+      <c r="BC24" s="48" t="n"/>
+      <c r="BD24" s="48" t="n"/>
+      <c r="BE24" s="48" t="n"/>
+      <c r="BF24" s="48" t="n"/>
+      <c r="BG24" s="49" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="21" t="n"/>
-      <c r="J25" s="21" t="n"/>
-      <c r="K25" s="21" t="n"/>
-      <c r="L25" s="21" t="n"/>
-      <c r="M25" s="21" t="n"/>
-      <c r="N25" s="21" t="n"/>
-      <c r="O25" s="21" t="n"/>
+      <c r="A25" s="55" t="n"/>
+      <c r="B25" s="55" t="n"/>
+      <c r="C25" s="55" t="n"/>
+      <c r="D25" s="55" t="n"/>
+      <c r="E25" s="55" t="n"/>
+      <c r="F25" s="55" t="n"/>
+      <c r="G25" s="67" t="n"/>
+      <c r="H25" s="67" t="n"/>
+      <c r="I25" s="67" t="n"/>
+      <c r="J25" s="67" t="n"/>
+      <c r="K25" s="67" t="n"/>
+      <c r="L25" s="67" t="n"/>
+      <c r="M25" s="67" t="n"/>
+      <c r="N25" s="67" t="n"/>
+      <c r="O25" s="67" t="n"/>
       <c r="P25" s="21" t="n"/>
       <c r="Q25" s="21" t="n"/>
-      <c r="R25" s="50" t="n"/>
-      <c r="AE25" s="51" t="n"/>
-      <c r="AF25" s="50" t="n"/>
-      <c r="AS25" s="51" t="n"/>
-      <c r="AT25" s="50" t="n"/>
-      <c r="BG25" s="51" t="n"/>
+      <c r="R25" s="68" t="n"/>
+      <c r="AE25" s="57" t="n"/>
+      <c r="AF25" s="68" t="n"/>
+      <c r="AS25" s="57" t="n"/>
+      <c r="AT25" s="68" t="n"/>
+      <c r="BG25" s="57" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="21" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="21" t="n"/>
-      <c r="K26" s="21" t="n"/>
-      <c r="L26" s="21" t="n"/>
-      <c r="M26" s="21" t="n"/>
-      <c r="N26" s="21" t="n"/>
-      <c r="O26" s="21" t="n"/>
+      <c r="A26" s="55" t="n"/>
+      <c r="B26" s="55" t="n"/>
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="55" t="n"/>
+      <c r="E26" s="55" t="n"/>
+      <c r="F26" s="55" t="n"/>
+      <c r="G26" s="67" t="n"/>
+      <c r="H26" s="67" t="n"/>
+      <c r="I26" s="67" t="n"/>
+      <c r="J26" s="67" t="n"/>
+      <c r="K26" s="67" t="n"/>
+      <c r="L26" s="67" t="n"/>
+      <c r="M26" s="67" t="n"/>
+      <c r="N26" s="67" t="n"/>
+      <c r="O26" s="67" t="n"/>
       <c r="P26" s="21" t="n"/>
       <c r="Q26" s="21" t="n"/>
-      <c r="R26" s="52" t="n"/>
-      <c r="S26" s="53" t="n"/>
-      <c r="T26" s="53" t="n"/>
-      <c r="U26" s="53" t="n"/>
-      <c r="V26" s="53" t="n"/>
-      <c r="W26" s="53" t="n"/>
-      <c r="X26" s="53" t="n"/>
-      <c r="Y26" s="53" t="n"/>
-      <c r="Z26" s="53" t="n"/>
-      <c r="AA26" s="53" t="n"/>
-      <c r="AB26" s="53" t="n"/>
-      <c r="AC26" s="53" t="n"/>
-      <c r="AD26" s="53" t="n"/>
-      <c r="AE26" s="54" t="n"/>
-      <c r="AF26" s="52" t="n"/>
-      <c r="AG26" s="53" t="n"/>
-      <c r="AH26" s="53" t="n"/>
-      <c r="AI26" s="53" t="n"/>
-      <c r="AJ26" s="53" t="n"/>
-      <c r="AK26" s="53" t="n"/>
-      <c r="AL26" s="53" t="n"/>
-      <c r="AM26" s="53" t="n"/>
-      <c r="AN26" s="53" t="n"/>
-      <c r="AO26" s="53" t="n"/>
-      <c r="AP26" s="53" t="n"/>
-      <c r="AQ26" s="53" t="n"/>
-      <c r="AR26" s="53" t="n"/>
-      <c r="AS26" s="54" t="n"/>
-      <c r="AT26" s="52" t="n"/>
-      <c r="AU26" s="53" t="n"/>
-      <c r="AV26" s="53" t="n"/>
-      <c r="AW26" s="53" t="n"/>
-      <c r="AX26" s="53" t="n"/>
-      <c r="AY26" s="53" t="n"/>
-      <c r="AZ26" s="53" t="n"/>
-      <c r="BA26" s="53" t="n"/>
-      <c r="BB26" s="53" t="n"/>
-      <c r="BC26" s="53" t="n"/>
-      <c r="BD26" s="53" t="n"/>
-      <c r="BE26" s="53" t="n"/>
-      <c r="BF26" s="53" t="n"/>
-      <c r="BG26" s="54" t="n"/>
+      <c r="R26" s="58" t="n"/>
+      <c r="S26" s="59" t="n"/>
+      <c r="T26" s="59" t="n"/>
+      <c r="U26" s="59" t="n"/>
+      <c r="V26" s="59" t="n"/>
+      <c r="W26" s="59" t="n"/>
+      <c r="X26" s="59" t="n"/>
+      <c r="Y26" s="59" t="n"/>
+      <c r="Z26" s="59" t="n"/>
+      <c r="AA26" s="59" t="n"/>
+      <c r="AB26" s="59" t="n"/>
+      <c r="AC26" s="59" t="n"/>
+      <c r="AD26" s="59" t="n"/>
+      <c r="AE26" s="60" t="n"/>
+      <c r="AF26" s="58" t="n"/>
+      <c r="AG26" s="59" t="n"/>
+      <c r="AH26" s="59" t="n"/>
+      <c r="AI26" s="59" t="n"/>
+      <c r="AJ26" s="59" t="n"/>
+      <c r="AK26" s="59" t="n"/>
+      <c r="AL26" s="59" t="n"/>
+      <c r="AM26" s="59" t="n"/>
+      <c r="AN26" s="59" t="n"/>
+      <c r="AO26" s="59" t="n"/>
+      <c r="AP26" s="59" t="n"/>
+      <c r="AQ26" s="59" t="n"/>
+      <c r="AR26" s="59" t="n"/>
+      <c r="AS26" s="60" t="n"/>
+      <c r="AT26" s="58" t="n"/>
+      <c r="AU26" s="59" t="n"/>
+      <c r="AV26" s="59" t="n"/>
+      <c r="AW26" s="59" t="n"/>
+      <c r="AX26" s="59" t="n"/>
+      <c r="AY26" s="59" t="n"/>
+      <c r="AZ26" s="59" t="n"/>
+      <c r="BA26" s="59" t="n"/>
+      <c r="BB26" s="59" t="n"/>
+      <c r="BC26" s="59" t="n"/>
+      <c r="BD26" s="59" t="n"/>
+      <c r="BE26" s="59" t="n"/>
+      <c r="BF26" s="59" t="n"/>
+      <c r="BG26" s="60" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="G27" s="21" t="n"/>
-      <c r="H27" s="21" t="n"/>
-      <c r="I27" s="21" t="n"/>
-      <c r="J27" s="21" t="n"/>
-      <c r="K27" s="21" t="n"/>
-      <c r="L27" s="21" t="n"/>
-      <c r="M27" s="21" t="n"/>
-      <c r="N27" s="21" t="n"/>
-      <c r="O27" s="21" t="n"/>
+      <c r="A27" s="55" t="n"/>
+      <c r="B27" s="55" t="n"/>
+      <c r="C27" s="55" t="n"/>
+      <c r="D27" s="55" t="n"/>
+      <c r="E27" s="55" t="n"/>
+      <c r="F27" s="55" t="n"/>
+      <c r="G27" s="67" t="n"/>
+      <c r="H27" s="67" t="n"/>
+      <c r="I27" s="67" t="n"/>
+      <c r="J27" s="67" t="n"/>
+      <c r="K27" s="67" t="n"/>
+      <c r="L27" s="67" t="n"/>
+      <c r="M27" s="67" t="n"/>
+      <c r="N27" s="67" t="n"/>
+      <c r="O27" s="67" t="n"/>
       <c r="P27" s="21" t="n"/>
       <c r="Q27" s="21" t="n"/>
       <c r="R27" s="24">
         <f>"Fecha :"&amp;BO3</f>
         <v/>
       </c>
-      <c r="S27" s="44" t="n"/>
-      <c r="T27" s="44" t="n"/>
-      <c r="U27" s="44" t="n"/>
-      <c r="V27" s="44" t="n"/>
-      <c r="W27" s="44" t="n"/>
-      <c r="X27" s="44" t="n"/>
-      <c r="Y27" s="44" t="n"/>
-      <c r="Z27" s="44" t="n"/>
-      <c r="AA27" s="44" t="n"/>
-      <c r="AB27" s="44" t="n"/>
-      <c r="AC27" s="44" t="n"/>
-      <c r="AD27" s="44" t="n"/>
-      <c r="AE27" s="45" t="n"/>
+      <c r="S27" s="48" t="n"/>
+      <c r="T27" s="48" t="n"/>
+      <c r="U27" s="48" t="n"/>
+      <c r="V27" s="48" t="n"/>
+      <c r="W27" s="48" t="n"/>
+      <c r="X27" s="48" t="n"/>
+      <c r="Y27" s="48" t="n"/>
+      <c r="Z27" s="48" t="n"/>
+      <c r="AA27" s="48" t="n"/>
+      <c r="AB27" s="48" t="n"/>
+      <c r="AC27" s="48" t="n"/>
+      <c r="AD27" s="48" t="n"/>
+      <c r="AE27" s="49" t="n"/>
       <c r="AF27" s="24">
         <f>"Fecha :"&amp;CC1</f>
         <v/>
       </c>
-      <c r="AG27" s="44" t="n"/>
-      <c r="AH27" s="44" t="n"/>
-      <c r="AI27" s="44" t="n"/>
-      <c r="AJ27" s="44" t="n"/>
-      <c r="AK27" s="44" t="n"/>
-      <c r="AL27" s="44" t="n"/>
-      <c r="AM27" s="44" t="n"/>
-      <c r="AN27" s="44" t="n"/>
-      <c r="AO27" s="44" t="n"/>
-      <c r="AP27" s="44" t="n"/>
-      <c r="AQ27" s="44" t="n"/>
-      <c r="AR27" s="44" t="n"/>
-      <c r="AS27" s="45" t="n"/>
+      <c r="AG27" s="48" t="n"/>
+      <c r="AH27" s="48" t="n"/>
+      <c r="AI27" s="48" t="n"/>
+      <c r="AJ27" s="48" t="n"/>
+      <c r="AK27" s="48" t="n"/>
+      <c r="AL27" s="48" t="n"/>
+      <c r="AM27" s="48" t="n"/>
+      <c r="AN27" s="48" t="n"/>
+      <c r="AO27" s="48" t="n"/>
+      <c r="AP27" s="48" t="n"/>
+      <c r="AQ27" s="48" t="n"/>
+      <c r="AR27" s="48" t="n"/>
+      <c r="AS27" s="49" t="n"/>
       <c r="AT27" s="24">
         <f>"Fecha :"&amp;CC2</f>
         <v/>
       </c>
-      <c r="AU27" s="44" t="n"/>
-      <c r="AV27" s="44" t="n"/>
-      <c r="AW27" s="44" t="n"/>
-      <c r="AX27" s="44" t="n"/>
-      <c r="AY27" s="44" t="n"/>
-      <c r="AZ27" s="44" t="n"/>
-      <c r="BA27" s="44" t="n"/>
-      <c r="BB27" s="44" t="n"/>
-      <c r="BC27" s="44" t="n"/>
-      <c r="BD27" s="44" t="n"/>
-      <c r="BE27" s="44" t="n"/>
-      <c r="BF27" s="44" t="n"/>
-      <c r="BG27" s="45" t="n"/>
+      <c r="AU27" s="48" t="n"/>
+      <c r="AV27" s="48" t="n"/>
+      <c r="AW27" s="48" t="n"/>
+      <c r="AX27" s="48" t="n"/>
+      <c r="AY27" s="48" t="n"/>
+      <c r="AZ27" s="48" t="n"/>
+      <c r="BA27" s="48" t="n"/>
+      <c r="BB27" s="48" t="n"/>
+      <c r="BC27" s="48" t="n"/>
+      <c r="BD27" s="48" t="n"/>
+      <c r="BE27" s="48" t="n"/>
+      <c r="BF27" s="48" t="n"/>
+      <c r="BG27" s="49" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="21" t="n"/>
-      <c r="I28" s="21" t="n"/>
-      <c r="J28" s="21" t="n"/>
-      <c r="K28" s="21" t="n"/>
-      <c r="L28" s="21" t="n"/>
-      <c r="M28" s="21" t="n"/>
-      <c r="N28" s="21" t="n"/>
-      <c r="O28" s="21" t="n"/>
+      <c r="A28" s="55" t="n"/>
+      <c r="B28" s="55" t="n"/>
+      <c r="C28" s="55" t="n"/>
+      <c r="D28" s="55" t="n"/>
+      <c r="E28" s="55" t="n"/>
+      <c r="F28" s="55" t="n"/>
+      <c r="G28" s="67" t="n"/>
+      <c r="H28" s="67" t="n"/>
+      <c r="I28" s="67" t="n"/>
+      <c r="J28" s="67" t="n"/>
+      <c r="K28" s="67" t="n"/>
+      <c r="L28" s="67" t="n"/>
+      <c r="M28" s="67" t="n"/>
+      <c r="N28" s="67" t="n"/>
+      <c r="O28" s="67" t="n"/>
       <c r="P28" s="21" t="n"/>
       <c r="Q28" s="21" t="n"/>
-      <c r="R28" s="50" t="n"/>
-      <c r="AE28" s="51" t="n"/>
-      <c r="AF28" s="50" t="n"/>
-      <c r="AS28" s="51" t="n"/>
-      <c r="AT28" s="50" t="n"/>
-      <c r="BG28" s="51" t="n"/>
+      <c r="R28" s="68" t="n"/>
+      <c r="AE28" s="57" t="n"/>
+      <c r="AF28" s="68" t="n"/>
+      <c r="AS28" s="57" t="n"/>
+      <c r="AT28" s="68" t="n"/>
+      <c r="BG28" s="57" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="G29" s="21" t="n"/>
-      <c r="H29" s="21" t="n"/>
-      <c r="I29" s="21" t="n"/>
-      <c r="J29" s="21" t="n"/>
-      <c r="K29" s="21" t="n"/>
-      <c r="L29" s="21" t="n"/>
-      <c r="M29" s="21" t="n"/>
-      <c r="N29" s="21" t="n"/>
-      <c r="O29" s="21" t="n"/>
+      <c r="A29" s="55" t="n"/>
+      <c r="B29" s="55" t="n"/>
+      <c r="C29" s="55" t="n"/>
+      <c r="D29" s="55" t="n"/>
+      <c r="E29" s="55" t="n"/>
+      <c r="F29" s="55" t="n"/>
+      <c r="G29" s="67" t="n"/>
+      <c r="H29" s="67" t="n"/>
+      <c r="I29" s="67" t="n"/>
+      <c r="J29" s="67" t="n"/>
+      <c r="K29" s="67" t="n"/>
+      <c r="L29" s="67" t="n"/>
+      <c r="M29" s="67" t="n"/>
+      <c r="N29" s="67" t="n"/>
+      <c r="O29" s="67" t="n"/>
       <c r="P29" s="21" t="n"/>
       <c r="Q29" s="21" t="n"/>
-      <c r="R29" s="52" t="n"/>
-      <c r="S29" s="53" t="n"/>
-      <c r="T29" s="53" t="n"/>
-      <c r="U29" s="53" t="n"/>
-      <c r="V29" s="53" t="n"/>
-      <c r="W29" s="53" t="n"/>
-      <c r="X29" s="53" t="n"/>
-      <c r="Y29" s="53" t="n"/>
-      <c r="Z29" s="53" t="n"/>
-      <c r="AA29" s="53" t="n"/>
-      <c r="AB29" s="53" t="n"/>
-      <c r="AC29" s="53" t="n"/>
-      <c r="AD29" s="53" t="n"/>
-      <c r="AE29" s="54" t="n"/>
-      <c r="AF29" s="52" t="n"/>
-      <c r="AG29" s="53" t="n"/>
-      <c r="AH29" s="53" t="n"/>
-      <c r="AI29" s="53" t="n"/>
-      <c r="AJ29" s="53" t="n"/>
-      <c r="AK29" s="53" t="n"/>
-      <c r="AL29" s="53" t="n"/>
-      <c r="AM29" s="53" t="n"/>
-      <c r="AN29" s="53" t="n"/>
-      <c r="AO29" s="53" t="n"/>
-      <c r="AP29" s="53" t="n"/>
-      <c r="AQ29" s="53" t="n"/>
-      <c r="AR29" s="53" t="n"/>
-      <c r="AS29" s="54" t="n"/>
-      <c r="AT29" s="52" t="n"/>
-      <c r="AU29" s="53" t="n"/>
-      <c r="AV29" s="53" t="n"/>
-      <c r="AW29" s="53" t="n"/>
-      <c r="AX29" s="53" t="n"/>
-      <c r="AY29" s="53" t="n"/>
-      <c r="AZ29" s="53" t="n"/>
-      <c r="BA29" s="53" t="n"/>
-      <c r="BB29" s="53" t="n"/>
-      <c r="BC29" s="53" t="n"/>
-      <c r="BD29" s="53" t="n"/>
-      <c r="BE29" s="53" t="n"/>
-      <c r="BF29" s="53" t="n"/>
-      <c r="BG29" s="54" t="n"/>
+      <c r="R29" s="58" t="n"/>
+      <c r="S29" s="59" t="n"/>
+      <c r="T29" s="59" t="n"/>
+      <c r="U29" s="59" t="n"/>
+      <c r="V29" s="59" t="n"/>
+      <c r="W29" s="59" t="n"/>
+      <c r="X29" s="59" t="n"/>
+      <c r="Y29" s="59" t="n"/>
+      <c r="Z29" s="59" t="n"/>
+      <c r="AA29" s="59" t="n"/>
+      <c r="AB29" s="59" t="n"/>
+      <c r="AC29" s="59" t="n"/>
+      <c r="AD29" s="59" t="n"/>
+      <c r="AE29" s="60" t="n"/>
+      <c r="AF29" s="58" t="n"/>
+      <c r="AG29" s="59" t="n"/>
+      <c r="AH29" s="59" t="n"/>
+      <c r="AI29" s="59" t="n"/>
+      <c r="AJ29" s="59" t="n"/>
+      <c r="AK29" s="59" t="n"/>
+      <c r="AL29" s="59" t="n"/>
+      <c r="AM29" s="59" t="n"/>
+      <c r="AN29" s="59" t="n"/>
+      <c r="AO29" s="59" t="n"/>
+      <c r="AP29" s="59" t="n"/>
+      <c r="AQ29" s="59" t="n"/>
+      <c r="AR29" s="59" t="n"/>
+      <c r="AS29" s="60" t="n"/>
+      <c r="AT29" s="58" t="n"/>
+      <c r="AU29" s="59" t="n"/>
+      <c r="AV29" s="59" t="n"/>
+      <c r="AW29" s="59" t="n"/>
+      <c r="AX29" s="59" t="n"/>
+      <c r="AY29" s="59" t="n"/>
+      <c r="AZ29" s="59" t="n"/>
+      <c r="BA29" s="59" t="n"/>
+      <c r="BB29" s="59" t="n"/>
+      <c r="BC29" s="59" t="n"/>
+      <c r="BD29" s="59" t="n"/>
+      <c r="BE29" s="59" t="n"/>
+      <c r="BF29" s="59" t="n"/>
+      <c r="BG29" s="60" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="G30" s="21" t="n"/>
-      <c r="H30" s="21" t="n"/>
-      <c r="I30" s="21" t="n"/>
-      <c r="J30" s="21" t="n"/>
-      <c r="K30" s="21" t="n"/>
-      <c r="L30" s="21" t="n"/>
-      <c r="M30" s="21" t="n"/>
-      <c r="N30" s="21" t="n"/>
-      <c r="O30" s="21" t="n"/>
+      <c r="A30" s="55" t="n"/>
+      <c r="B30" s="55" t="n"/>
+      <c r="C30" s="55" t="n"/>
+      <c r="D30" s="55" t="n"/>
+      <c r="E30" s="55" t="n"/>
+      <c r="F30" s="55" t="n"/>
+      <c r="G30" s="67" t="n"/>
+      <c r="H30" s="67" t="n"/>
+      <c r="I30" s="67" t="n"/>
+      <c r="J30" s="67" t="n"/>
+      <c r="K30" s="67" t="n"/>
+      <c r="L30" s="67" t="n"/>
+      <c r="M30" s="67" t="n"/>
+      <c r="N30" s="67" t="n"/>
+      <c r="O30" s="67" t="n"/>
       <c r="P30" s="21" t="n"/>
       <c r="Q30" s="21" t="n"/>
       <c r="R30" s="21" t="n"/>
@@ -2424,15 +2712,21 @@
       <c r="AF30" s="21" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="G31" s="21" t="n"/>
-      <c r="H31" s="21" t="n"/>
-      <c r="I31" s="21" t="n"/>
-      <c r="J31" s="21" t="n"/>
-      <c r="K31" s="21" t="n"/>
-      <c r="L31" s="21" t="n"/>
-      <c r="M31" s="21" t="n"/>
-      <c r="N31" s="21" t="n"/>
-      <c r="O31" s="21" t="n"/>
+      <c r="A31" s="55" t="n"/>
+      <c r="B31" s="55" t="n"/>
+      <c r="C31" s="55" t="n"/>
+      <c r="D31" s="55" t="n"/>
+      <c r="E31" s="55" t="n"/>
+      <c r="F31" s="55" t="n"/>
+      <c r="G31" s="67" t="n"/>
+      <c r="H31" s="67" t="n"/>
+      <c r="I31" s="67" t="n"/>
+      <c r="J31" s="67" t="n"/>
+      <c r="K31" s="67" t="n"/>
+      <c r="L31" s="67" t="n"/>
+      <c r="M31" s="67" t="n"/>
+      <c r="N31" s="67" t="n"/>
+      <c r="O31" s="67" t="n"/>
       <c r="P31" s="21" t="n"/>
       <c r="Q31" s="21" t="n"/>
       <c r="R31" s="21" t="n"/>
@@ -2452,15 +2746,21 @@
       <c r="AF31" s="21" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="G32" s="21" t="n"/>
-      <c r="H32" s="21" t="n"/>
-      <c r="I32" s="21" t="n"/>
-      <c r="J32" s="21" t="n"/>
-      <c r="K32" s="21" t="n"/>
-      <c r="L32" s="21" t="n"/>
-      <c r="M32" s="21" t="n"/>
-      <c r="N32" s="21" t="n"/>
-      <c r="O32" s="21" t="n"/>
+      <c r="A32" s="55" t="n"/>
+      <c r="B32" s="55" t="n"/>
+      <c r="C32" s="55" t="n"/>
+      <c r="D32" s="55" t="n"/>
+      <c r="E32" s="55" t="n"/>
+      <c r="F32" s="55" t="n"/>
+      <c r="G32" s="67" t="n"/>
+      <c r="H32" s="67" t="n"/>
+      <c r="I32" s="67" t="n"/>
+      <c r="J32" s="67" t="n"/>
+      <c r="K32" s="67" t="n"/>
+      <c r="L32" s="67" t="n"/>
+      <c r="M32" s="67" t="n"/>
+      <c r="N32" s="67" t="n"/>
+      <c r="O32" s="67" t="n"/>
       <c r="P32" s="21" t="n"/>
       <c r="Q32" s="21" t="n"/>
       <c r="R32" s="21" t="n"/>
@@ -2480,15 +2780,21 @@
       <c r="AF32" s="21" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-      <c r="I33" s="21" t="n"/>
-      <c r="J33" s="21" t="n"/>
-      <c r="K33" s="21" t="n"/>
-      <c r="L33" s="21" t="n"/>
-      <c r="M33" s="21" t="n"/>
-      <c r="N33" s="21" t="n"/>
-      <c r="O33" s="21" t="n"/>
+      <c r="A33" s="55" t="n"/>
+      <c r="B33" s="55" t="n"/>
+      <c r="C33" s="55" t="n"/>
+      <c r="D33" s="55" t="n"/>
+      <c r="E33" s="55" t="n"/>
+      <c r="F33" s="55" t="n"/>
+      <c r="G33" s="67" t="n"/>
+      <c r="H33" s="67" t="n"/>
+      <c r="I33" s="67" t="n"/>
+      <c r="J33" s="67" t="n"/>
+      <c r="K33" s="67" t="n"/>
+      <c r="L33" s="67" t="n"/>
+      <c r="M33" s="67" t="n"/>
+      <c r="N33" s="67" t="n"/>
+      <c r="O33" s="67" t="n"/>
       <c r="P33" s="21" t="n"/>
       <c r="Q33" s="21" t="n"/>
       <c r="R33" s="21" t="n"/>
@@ -2508,15 +2814,21 @@
       <c r="AF33" s="21" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="21" t="n"/>
-      <c r="I34" s="21" t="n"/>
-      <c r="J34" s="21" t="n"/>
-      <c r="K34" s="21" t="n"/>
-      <c r="L34" s="21" t="n"/>
-      <c r="M34" s="21" t="n"/>
-      <c r="N34" s="21" t="n"/>
-      <c r="O34" s="21" t="n"/>
+      <c r="A34" s="55" t="n"/>
+      <c r="B34" s="55" t="n"/>
+      <c r="C34" s="55" t="n"/>
+      <c r="D34" s="55" t="n"/>
+      <c r="E34" s="55" t="n"/>
+      <c r="F34" s="55" t="n"/>
+      <c r="G34" s="67" t="n"/>
+      <c r="H34" s="67" t="n"/>
+      <c r="I34" s="67" t="n"/>
+      <c r="J34" s="67" t="n"/>
+      <c r="K34" s="67" t="n"/>
+      <c r="L34" s="67" t="n"/>
+      <c r="M34" s="67" t="n"/>
+      <c r="N34" s="67" t="n"/>
+      <c r="O34" s="67" t="n"/>
       <c r="P34" s="21" t="n"/>
       <c r="Q34" s="21" t="n"/>
       <c r="R34" s="21" t="n"/>
@@ -2536,15 +2848,21 @@
       <c r="AF34" s="21" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="G35" s="21" t="n"/>
-      <c r="H35" s="21" t="n"/>
-      <c r="I35" s="21" t="n"/>
-      <c r="J35" s="21" t="n"/>
-      <c r="K35" s="21" t="n"/>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="21" t="n"/>
-      <c r="N35" s="21" t="n"/>
-      <c r="O35" s="21" t="n"/>
+      <c r="A35" s="55" t="n"/>
+      <c r="B35" s="55" t="n"/>
+      <c r="C35" s="55" t="n"/>
+      <c r="D35" s="55" t="n"/>
+      <c r="E35" s="55" t="n"/>
+      <c r="F35" s="55" t="n"/>
+      <c r="G35" s="67" t="n"/>
+      <c r="H35" s="67" t="n"/>
+      <c r="I35" s="67" t="n"/>
+      <c r="J35" s="67" t="n"/>
+      <c r="K35" s="67" t="n"/>
+      <c r="L35" s="67" t="n"/>
+      <c r="M35" s="67" t="n"/>
+      <c r="N35" s="67" t="n"/>
+      <c r="O35" s="67" t="n"/>
       <c r="P35" s="21" t="n"/>
       <c r="Q35" s="21" t="n"/>
       <c r="R35" s="21" t="n"/>
@@ -2564,15 +2882,21 @@
       <c r="AF35" s="21" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="G36" s="21" t="n"/>
-      <c r="H36" s="21" t="n"/>
-      <c r="I36" s="21" t="n"/>
-      <c r="J36" s="21" t="n"/>
-      <c r="K36" s="21" t="n"/>
-      <c r="L36" s="21" t="n"/>
-      <c r="M36" s="21" t="n"/>
-      <c r="N36" s="21" t="n"/>
-      <c r="O36" s="21" t="n"/>
+      <c r="A36" s="55" t="n"/>
+      <c r="B36" s="55" t="n"/>
+      <c r="C36" s="55" t="n"/>
+      <c r="D36" s="55" t="n"/>
+      <c r="E36" s="55" t="n"/>
+      <c r="F36" s="55" t="n"/>
+      <c r="G36" s="67" t="n"/>
+      <c r="H36" s="67" t="n"/>
+      <c r="I36" s="67" t="n"/>
+      <c r="J36" s="67" t="n"/>
+      <c r="K36" s="67" t="n"/>
+      <c r="L36" s="67" t="n"/>
+      <c r="M36" s="67" t="n"/>
+      <c r="N36" s="67" t="n"/>
+      <c r="O36" s="67" t="n"/>
       <c r="P36" s="21" t="n"/>
       <c r="Q36" s="21" t="n"/>
       <c r="R36" s="21" t="n"/>
@@ -2593,15 +2917,21 @@
       <c r="BK36" s="21" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="G37" s="21" t="n"/>
-      <c r="H37" s="21" t="n"/>
-      <c r="I37" s="21" t="n"/>
-      <c r="J37" s="21" t="n"/>
-      <c r="K37" s="21" t="n"/>
-      <c r="L37" s="21" t="n"/>
-      <c r="M37" s="21" t="n"/>
-      <c r="N37" s="21" t="n"/>
-      <c r="O37" s="21" t="n"/>
+      <c r="A37" s="55" t="n"/>
+      <c r="B37" s="55" t="n"/>
+      <c r="C37" s="55" t="n"/>
+      <c r="D37" s="55" t="n"/>
+      <c r="E37" s="55" t="n"/>
+      <c r="F37" s="55" t="n"/>
+      <c r="G37" s="67" t="n"/>
+      <c r="H37" s="67" t="n"/>
+      <c r="I37" s="67" t="n"/>
+      <c r="J37" s="67" t="n"/>
+      <c r="K37" s="67" t="n"/>
+      <c r="L37" s="67" t="n"/>
+      <c r="M37" s="67" t="n"/>
+      <c r="N37" s="67" t="n"/>
+      <c r="O37" s="67" t="n"/>
       <c r="P37" s="21" t="n"/>
       <c r="Q37" s="21" t="n"/>
       <c r="R37" s="21" t="n"/>
@@ -2621,15 +2951,21 @@
       <c r="AF37" s="21" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="G38" s="21" t="n"/>
-      <c r="H38" s="21" t="n"/>
-      <c r="I38" s="21" t="n"/>
-      <c r="J38" s="21" t="n"/>
-      <c r="K38" s="21" t="n"/>
-      <c r="L38" s="21" t="n"/>
-      <c r="M38" s="21" t="n"/>
-      <c r="N38" s="21" t="n"/>
-      <c r="O38" s="21" t="n"/>
+      <c r="A38" s="55" t="n"/>
+      <c r="B38" s="55" t="n"/>
+      <c r="C38" s="55" t="n"/>
+      <c r="D38" s="55" t="n"/>
+      <c r="E38" s="55" t="n"/>
+      <c r="F38" s="55" t="n"/>
+      <c r="G38" s="67" t="n"/>
+      <c r="H38" s="67" t="n"/>
+      <c r="I38" s="67" t="n"/>
+      <c r="J38" s="67" t="n"/>
+      <c r="K38" s="67" t="n"/>
+      <c r="L38" s="67" t="n"/>
+      <c r="M38" s="67" t="n"/>
+      <c r="N38" s="67" t="n"/>
+      <c r="O38" s="67" t="n"/>
       <c r="P38" s="21" t="n"/>
       <c r="Q38" s="21" t="n"/>
       <c r="R38" s="21" t="n"/>
@@ -2649,476 +2985,608 @@
       <c r="AF38" s="21" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
-      <c r="I39" s="21" t="n"/>
-      <c r="J39" s="21" t="n"/>
-      <c r="K39" s="21" t="n"/>
-      <c r="L39" s="21" t="n"/>
-      <c r="M39" s="21" t="n"/>
-      <c r="N39" s="21" t="n"/>
-      <c r="O39" s="42" t="inlineStr">
+      <c r="A39" s="55" t="n"/>
+      <c r="B39" s="55" t="n"/>
+      <c r="C39" s="55" t="n"/>
+      <c r="D39" s="55" t="n"/>
+      <c r="E39" s="55" t="n"/>
+      <c r="F39" s="55" t="n"/>
+      <c r="G39" s="67" t="n"/>
+      <c r="H39" s="67" t="n"/>
+      <c r="I39" s="67" t="n"/>
+      <c r="J39" s="67" t="n"/>
+      <c r="K39" s="67" t="n"/>
+      <c r="L39" s="67" t="n"/>
+      <c r="M39" s="67" t="n"/>
+      <c r="N39" s="67" t="n"/>
+      <c r="O39" s="69" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="P39" s="44" t="n"/>
-      <c r="Q39" s="44" t="n"/>
-      <c r="R39" s="44" t="n"/>
-      <c r="S39" s="44" t="n"/>
-      <c r="T39" s="44" t="n"/>
-      <c r="U39" s="45" t="n"/>
+      <c r="P39" s="48" t="n"/>
+      <c r="Q39" s="48" t="n"/>
+      <c r="R39" s="48" t="n"/>
+      <c r="S39" s="48" t="n"/>
+      <c r="T39" s="48" t="n"/>
+      <c r="U39" s="49" t="n"/>
       <c r="V39" s="42" t="inlineStr">
         <is>
           <t>Autor</t>
         </is>
       </c>
-      <c r="W39" s="44" t="n"/>
-      <c r="X39" s="44" t="n"/>
-      <c r="Y39" s="44" t="n"/>
-      <c r="Z39" s="44" t="n"/>
-      <c r="AA39" s="44" t="n"/>
-      <c r="AB39" s="45" t="n"/>
+      <c r="W39" s="48" t="n"/>
+      <c r="X39" s="48" t="n"/>
+      <c r="Y39" s="48" t="n"/>
+      <c r="Z39" s="48" t="n"/>
+      <c r="AA39" s="48" t="n"/>
+      <c r="AB39" s="49" t="n"/>
       <c r="AC39" s="43" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="AD39" s="44" t="n"/>
-      <c r="AE39" s="44" t="n"/>
-      <c r="AF39" s="44" t="n"/>
-      <c r="AG39" s="44" t="n"/>
-      <c r="AH39" s="44" t="n"/>
-      <c r="AI39" s="44" t="n"/>
-      <c r="AJ39" s="44" t="n"/>
-      <c r="AK39" s="44" t="n"/>
-      <c r="AL39" s="44" t="n"/>
-      <c r="AM39" s="44" t="n"/>
-      <c r="AN39" s="44" t="n"/>
-      <c r="AO39" s="45" t="n"/>
+      <c r="AD39" s="48" t="n"/>
+      <c r="AE39" s="48" t="n"/>
+      <c r="AF39" s="48" t="n"/>
+      <c r="AG39" s="48" t="n"/>
+      <c r="AH39" s="48" t="n"/>
+      <c r="AI39" s="48" t="n"/>
+      <c r="AJ39" s="48" t="n"/>
+      <c r="AK39" s="48" t="n"/>
+      <c r="AL39" s="48" t="n"/>
+      <c r="AM39" s="48" t="n"/>
+      <c r="AN39" s="48" t="n"/>
+      <c r="AO39" s="49" t="n"/>
       <c r="AP39" s="42" t="inlineStr">
         <is>
           <t>Fecha de elaboración</t>
         </is>
       </c>
-      <c r="AQ39" s="44" t="n"/>
-      <c r="AR39" s="44" t="n"/>
-      <c r="AS39" s="44" t="n"/>
-      <c r="AT39" s="44" t="n"/>
-      <c r="AU39" s="44" t="n"/>
-      <c r="AV39" s="45" t="n"/>
+      <c r="AQ39" s="48" t="n"/>
+      <c r="AR39" s="48" t="n"/>
+      <c r="AS39" s="48" t="n"/>
+      <c r="AT39" s="48" t="n"/>
+      <c r="AU39" s="48" t="n"/>
+      <c r="AV39" s="49" t="n"/>
       <c r="AW39" s="42" t="inlineStr">
         <is>
           <t>Fecha de revisión</t>
         </is>
       </c>
-      <c r="AX39" s="44" t="n"/>
-      <c r="AY39" s="44" t="n"/>
-      <c r="AZ39" s="44" t="n"/>
-      <c r="BA39" s="44" t="n"/>
-      <c r="BB39" s="44" t="n"/>
-      <c r="BC39" s="45" t="n"/>
+      <c r="AX39" s="48" t="n"/>
+      <c r="AY39" s="48" t="n"/>
+      <c r="AZ39" s="48" t="n"/>
+      <c r="BA39" s="48" t="n"/>
+      <c r="BB39" s="48" t="n"/>
+      <c r="BC39" s="49" t="n"/>
       <c r="BD39" s="42" t="inlineStr">
         <is>
           <t>Revisado por</t>
         </is>
       </c>
-      <c r="BE39" s="44" t="n"/>
-      <c r="BF39" s="44" t="n"/>
-      <c r="BG39" s="44" t="n"/>
-      <c r="BH39" s="44" t="n"/>
-      <c r="BI39" s="44" t="n"/>
-      <c r="BJ39" s="45" t="n"/>
+      <c r="BE39" s="48" t="n"/>
+      <c r="BF39" s="48" t="n"/>
+      <c r="BG39" s="48" t="n"/>
+      <c r="BH39" s="48" t="n"/>
+      <c r="BI39" s="48" t="n"/>
+      <c r="BJ39" s="49" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="21" t="n"/>
-      <c r="I40" s="21" t="n"/>
-      <c r="J40" s="21" t="n"/>
-      <c r="K40" s="21" t="n"/>
-      <c r="L40" s="21" t="n"/>
-      <c r="M40" s="21" t="n"/>
-      <c r="N40" s="21" t="n"/>
-      <c r="O40" s="50" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="50" t="n"/>
-      <c r="AB40" s="51" t="n"/>
-      <c r="AC40" s="50" t="n"/>
-      <c r="AO40" s="51" t="n"/>
-      <c r="AP40" s="50" t="n"/>
-      <c r="AV40" s="51" t="n"/>
-      <c r="AW40" s="50" t="n"/>
-      <c r="BC40" s="51" t="n"/>
-      <c r="BD40" s="50" t="n"/>
-      <c r="BJ40" s="51" t="n"/>
+      <c r="A40" s="55" t="n"/>
+      <c r="B40" s="55" t="n"/>
+      <c r="C40" s="55" t="n"/>
+      <c r="D40" s="55" t="n"/>
+      <c r="E40" s="55" t="n"/>
+      <c r="F40" s="55" t="n"/>
+      <c r="G40" s="67" t="n"/>
+      <c r="H40" s="67" t="n"/>
+      <c r="I40" s="67" t="n"/>
+      <c r="J40" s="67" t="n"/>
+      <c r="K40" s="67" t="n"/>
+      <c r="L40" s="67" t="n"/>
+      <c r="M40" s="67" t="n"/>
+      <c r="N40" s="67" t="n"/>
+      <c r="O40" s="54" t="n"/>
+      <c r="U40" s="57" t="n"/>
+      <c r="V40" s="68" t="n"/>
+      <c r="AB40" s="57" t="n"/>
+      <c r="AC40" s="68" t="n"/>
+      <c r="AO40" s="57" t="n"/>
+      <c r="AP40" s="68" t="n"/>
+      <c r="AV40" s="57" t="n"/>
+      <c r="AW40" s="68" t="n"/>
+      <c r="BC40" s="57" t="n"/>
+      <c r="BD40" s="68" t="n"/>
+      <c r="BJ40" s="57" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="21" t="n"/>
-      <c r="I41" s="21" t="n"/>
-      <c r="J41" s="21" t="n"/>
-      <c r="K41" s="21" t="n"/>
-      <c r="L41" s="21" t="n"/>
-      <c r="M41" s="21" t="n"/>
-      <c r="N41" s="21" t="n"/>
-      <c r="O41" s="52" t="n"/>
-      <c r="P41" s="53" t="n"/>
-      <c r="Q41" s="53" t="n"/>
-      <c r="R41" s="53" t="n"/>
-      <c r="S41" s="53" t="n"/>
-      <c r="T41" s="53" t="n"/>
-      <c r="U41" s="54" t="n"/>
-      <c r="V41" s="52" t="n"/>
-      <c r="W41" s="53" t="n"/>
-      <c r="X41" s="53" t="n"/>
-      <c r="Y41" s="53" t="n"/>
-      <c r="Z41" s="53" t="n"/>
-      <c r="AA41" s="53" t="n"/>
-      <c r="AB41" s="54" t="n"/>
-      <c r="AC41" s="52" t="n"/>
-      <c r="AD41" s="53" t="n"/>
-      <c r="AE41" s="53" t="n"/>
-      <c r="AF41" s="53" t="n"/>
-      <c r="AG41" s="53" t="n"/>
-      <c r="AH41" s="53" t="n"/>
-      <c r="AI41" s="53" t="n"/>
-      <c r="AJ41" s="53" t="n"/>
-      <c r="AK41" s="53" t="n"/>
-      <c r="AL41" s="53" t="n"/>
-      <c r="AM41" s="53" t="n"/>
-      <c r="AN41" s="53" t="n"/>
-      <c r="AO41" s="54" t="n"/>
-      <c r="AP41" s="52" t="n"/>
-      <c r="AQ41" s="53" t="n"/>
-      <c r="AR41" s="53" t="n"/>
-      <c r="AS41" s="53" t="n"/>
-      <c r="AT41" s="53" t="n"/>
-      <c r="AU41" s="53" t="n"/>
-      <c r="AV41" s="54" t="n"/>
-      <c r="AW41" s="52" t="n"/>
-      <c r="AX41" s="53" t="n"/>
-      <c r="AY41" s="53" t="n"/>
-      <c r="AZ41" s="53" t="n"/>
-      <c r="BA41" s="53" t="n"/>
-      <c r="BB41" s="53" t="n"/>
-      <c r="BC41" s="54" t="n"/>
-      <c r="BD41" s="52" t="n"/>
-      <c r="BE41" s="53" t="n"/>
-      <c r="BF41" s="53" t="n"/>
-      <c r="BG41" s="53" t="n"/>
-      <c r="BH41" s="53" t="n"/>
-      <c r="BI41" s="53" t="n"/>
-      <c r="BJ41" s="54" t="n"/>
+      <c r="A41" s="55" t="n"/>
+      <c r="B41" s="55" t="n"/>
+      <c r="C41" s="55" t="n"/>
+      <c r="D41" s="55" t="n"/>
+      <c r="E41" s="55" t="n"/>
+      <c r="F41" s="55" t="n"/>
+      <c r="G41" s="67" t="n"/>
+      <c r="H41" s="67" t="n"/>
+      <c r="I41" s="67" t="n"/>
+      <c r="J41" s="67" t="n"/>
+      <c r="K41" s="67" t="n"/>
+      <c r="L41" s="67" t="n"/>
+      <c r="M41" s="67" t="n"/>
+      <c r="N41" s="67" t="n"/>
+      <c r="O41" s="61" t="n"/>
+      <c r="P41" s="59" t="n"/>
+      <c r="Q41" s="59" t="n"/>
+      <c r="R41" s="59" t="n"/>
+      <c r="S41" s="59" t="n"/>
+      <c r="T41" s="59" t="n"/>
+      <c r="U41" s="60" t="n"/>
+      <c r="V41" s="58" t="n"/>
+      <c r="W41" s="59" t="n"/>
+      <c r="X41" s="59" t="n"/>
+      <c r="Y41" s="59" t="n"/>
+      <c r="Z41" s="59" t="n"/>
+      <c r="AA41" s="59" t="n"/>
+      <c r="AB41" s="60" t="n"/>
+      <c r="AC41" s="58" t="n"/>
+      <c r="AD41" s="59" t="n"/>
+      <c r="AE41" s="59" t="n"/>
+      <c r="AF41" s="59" t="n"/>
+      <c r="AG41" s="59" t="n"/>
+      <c r="AH41" s="59" t="n"/>
+      <c r="AI41" s="59" t="n"/>
+      <c r="AJ41" s="59" t="n"/>
+      <c r="AK41" s="59" t="n"/>
+      <c r="AL41" s="59" t="n"/>
+      <c r="AM41" s="59" t="n"/>
+      <c r="AN41" s="59" t="n"/>
+      <c r="AO41" s="60" t="n"/>
+      <c r="AP41" s="58" t="n"/>
+      <c r="AQ41" s="59" t="n"/>
+      <c r="AR41" s="59" t="n"/>
+      <c r="AS41" s="59" t="n"/>
+      <c r="AT41" s="59" t="n"/>
+      <c r="AU41" s="59" t="n"/>
+      <c r="AV41" s="60" t="n"/>
+      <c r="AW41" s="58" t="n"/>
+      <c r="AX41" s="59" t="n"/>
+      <c r="AY41" s="59" t="n"/>
+      <c r="AZ41" s="59" t="n"/>
+      <c r="BA41" s="59" t="n"/>
+      <c r="BB41" s="59" t="n"/>
+      <c r="BC41" s="60" t="n"/>
+      <c r="BD41" s="58" t="n"/>
+      <c r="BE41" s="59" t="n"/>
+      <c r="BF41" s="59" t="n"/>
+      <c r="BG41" s="59" t="n"/>
+      <c r="BH41" s="59" t="n"/>
+      <c r="BI41" s="59" t="n"/>
+      <c r="BJ41" s="60" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="21" t="n"/>
-      <c r="I42" s="21" t="n"/>
-      <c r="J42" s="21" t="n"/>
-      <c r="K42" s="21" t="n"/>
-      <c r="L42" s="21" t="n"/>
-      <c r="M42" s="21" t="n"/>
-      <c r="N42" s="21" t="n"/>
-      <c r="O42" s="37" t="inlineStr">
+      <c r="A42" s="55" t="n"/>
+      <c r="B42" s="55" t="n"/>
+      <c r="C42" s="55" t="n"/>
+      <c r="D42" s="55" t="n"/>
+      <c r="E42" s="55" t="n"/>
+      <c r="F42" s="55" t="n"/>
+      <c r="G42" s="67" t="n"/>
+      <c r="H42" s="67" t="n"/>
+      <c r="I42" s="67" t="n"/>
+      <c r="J42" s="67" t="n"/>
+      <c r="K42" s="67" t="n"/>
+      <c r="L42" s="67" t="n"/>
+      <c r="M42" s="67" t="n"/>
+      <c r="N42" s="67" t="n"/>
+      <c r="O42" s="70" t="inlineStr">
         <is>
           <t>CERO (0)</t>
         </is>
       </c>
-      <c r="P42" s="44" t="n"/>
-      <c r="Q42" s="44" t="n"/>
-      <c r="R42" s="44" t="n"/>
-      <c r="S42" s="44" t="n"/>
-      <c r="T42" s="44" t="n"/>
-      <c r="U42" s="45" t="n"/>
+      <c r="P42" s="48" t="n"/>
+      <c r="Q42" s="48" t="n"/>
+      <c r="R42" s="48" t="n"/>
+      <c r="S42" s="48" t="n"/>
+      <c r="T42" s="48" t="n"/>
+      <c r="U42" s="49" t="n"/>
       <c r="V42" s="37" t="inlineStr">
         <is>
           <t>J.ARBOLEDA</t>
         </is>
       </c>
-      <c r="W42" s="44" t="n"/>
-      <c r="X42" s="44" t="n"/>
-      <c r="Y42" s="44" t="n"/>
-      <c r="Z42" s="44" t="n"/>
-      <c r="AA42" s="44" t="n"/>
-      <c r="AB42" s="45" t="n"/>
+      <c r="W42" s="48" t="n"/>
+      <c r="X42" s="48" t="n"/>
+      <c r="Y42" s="48" t="n"/>
+      <c r="Z42" s="48" t="n"/>
+      <c r="AA42" s="48" t="n"/>
+      <c r="AB42" s="49" t="n"/>
       <c r="AC42" s="38" t="inlineStr">
         <is>
           <t>Emitido para cotizacion</t>
         </is>
       </c>
-      <c r="AD42" s="44" t="n"/>
-      <c r="AE42" s="44" t="n"/>
-      <c r="AF42" s="44" t="n"/>
-      <c r="AG42" s="44" t="n"/>
-      <c r="AH42" s="44" t="n"/>
-      <c r="AI42" s="44" t="n"/>
-      <c r="AJ42" s="44" t="n"/>
-      <c r="AK42" s="44" t="n"/>
-      <c r="AL42" s="44" t="n"/>
-      <c r="AM42" s="44" t="n"/>
-      <c r="AN42" s="44" t="n"/>
-      <c r="AO42" s="45" t="n"/>
+      <c r="AD42" s="48" t="n"/>
+      <c r="AE42" s="48" t="n"/>
+      <c r="AF42" s="48" t="n"/>
+      <c r="AG42" s="48" t="n"/>
+      <c r="AH42" s="48" t="n"/>
+      <c r="AI42" s="48" t="n"/>
+      <c r="AJ42" s="48" t="n"/>
+      <c r="AK42" s="48" t="n"/>
+      <c r="AL42" s="48" t="n"/>
+      <c r="AM42" s="48" t="n"/>
+      <c r="AN42" s="48" t="n"/>
+      <c r="AO42" s="49" t="n"/>
       <c r="AP42" s="39">
         <f>BO3</f>
         <v/>
       </c>
-      <c r="AQ42" s="44" t="n"/>
-      <c r="AR42" s="44" t="n"/>
-      <c r="AS42" s="44" t="n"/>
-      <c r="AT42" s="44" t="n"/>
-      <c r="AU42" s="44" t="n"/>
-      <c r="AV42" s="45" t="n"/>
+      <c r="AQ42" s="48" t="n"/>
+      <c r="AR42" s="48" t="n"/>
+      <c r="AS42" s="48" t="n"/>
+      <c r="AT42" s="48" t="n"/>
+      <c r="AU42" s="48" t="n"/>
+      <c r="AV42" s="49" t="n"/>
       <c r="AW42" s="39">
         <f>AT27</f>
         <v/>
       </c>
-      <c r="AX42" s="44" t="n"/>
-      <c r="AY42" s="44" t="n"/>
-      <c r="AZ42" s="44" t="n"/>
-      <c r="BA42" s="44" t="n"/>
-      <c r="BB42" s="44" t="n"/>
-      <c r="BC42" s="45" t="n"/>
+      <c r="AX42" s="48" t="n"/>
+      <c r="AY42" s="48" t="n"/>
+      <c r="AZ42" s="48" t="n"/>
+      <c r="BA42" s="48" t="n"/>
+      <c r="BB42" s="48" t="n"/>
+      <c r="BC42" s="49" t="n"/>
       <c r="BD42" s="40">
         <f>BO5</f>
         <v/>
       </c>
-      <c r="BE42" s="44" t="n"/>
-      <c r="BF42" s="44" t="n"/>
-      <c r="BG42" s="44" t="n"/>
-      <c r="BH42" s="44" t="n"/>
-      <c r="BI42" s="44" t="n"/>
-      <c r="BJ42" s="45" t="n"/>
+      <c r="BE42" s="48" t="n"/>
+      <c r="BF42" s="48" t="n"/>
+      <c r="BG42" s="48" t="n"/>
+      <c r="BH42" s="48" t="n"/>
+      <c r="BI42" s="48" t="n"/>
+      <c r="BJ42" s="49" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="G43" s="21" t="n"/>
-      <c r="H43" s="21" t="n"/>
-      <c r="I43" s="21" t="n"/>
-      <c r="J43" s="21" t="n"/>
-      <c r="K43" s="21" t="n"/>
-      <c r="L43" s="21" t="n"/>
-      <c r="M43" s="21" t="n"/>
-      <c r="N43" s="21" t="n"/>
-      <c r="O43" s="50" t="n"/>
-      <c r="U43" s="51" t="n"/>
-      <c r="V43" s="50" t="n"/>
-      <c r="AB43" s="51" t="n"/>
-      <c r="AC43" s="50" t="n"/>
-      <c r="AO43" s="51" t="n"/>
-      <c r="AP43" s="50" t="n"/>
-      <c r="AV43" s="51" t="n"/>
-      <c r="AW43" s="50" t="n"/>
-      <c r="BC43" s="51" t="n"/>
-      <c r="BD43" s="50" t="n"/>
-      <c r="BJ43" s="51" t="n"/>
+      <c r="A43" s="55" t="n"/>
+      <c r="B43" s="55" t="n"/>
+      <c r="C43" s="55" t="n"/>
+      <c r="D43" s="55" t="n"/>
+      <c r="E43" s="55" t="n"/>
+      <c r="F43" s="55" t="n"/>
+      <c r="G43" s="67" t="n"/>
+      <c r="H43" s="67" t="n"/>
+      <c r="I43" s="67" t="n"/>
+      <c r="J43" s="67" t="n"/>
+      <c r="K43" s="67" t="n"/>
+      <c r="L43" s="67" t="n"/>
+      <c r="M43" s="67" t="n"/>
+      <c r="N43" s="67" t="n"/>
+      <c r="O43" s="54" t="n"/>
+      <c r="U43" s="57" t="n"/>
+      <c r="V43" s="68" t="n"/>
+      <c r="AB43" s="57" t="n"/>
+      <c r="AC43" s="68" t="n"/>
+      <c r="AO43" s="57" t="n"/>
+      <c r="AP43" s="68" t="n"/>
+      <c r="AV43" s="57" t="n"/>
+      <c r="AW43" s="68" t="n"/>
+      <c r="BC43" s="57" t="n"/>
+      <c r="BD43" s="68" t="n"/>
+      <c r="BJ43" s="57" t="n"/>
       <c r="BP43" s="21" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="G44" s="21" t="n"/>
-      <c r="H44" s="21" t="n"/>
-      <c r="I44" s="21" t="n"/>
-      <c r="J44" s="21" t="n"/>
-      <c r="K44" s="21" t="n"/>
-      <c r="L44" s="21" t="n"/>
-      <c r="M44" s="21" t="n"/>
-      <c r="N44" s="21" t="n"/>
-      <c r="O44" s="52" t="n"/>
-      <c r="P44" s="53" t="n"/>
-      <c r="Q44" s="53" t="n"/>
-      <c r="R44" s="53" t="n"/>
-      <c r="S44" s="53" t="n"/>
-      <c r="T44" s="53" t="n"/>
-      <c r="U44" s="54" t="n"/>
-      <c r="V44" s="52" t="n"/>
-      <c r="W44" s="53" t="n"/>
-      <c r="X44" s="53" t="n"/>
-      <c r="Y44" s="53" t="n"/>
-      <c r="Z44" s="53" t="n"/>
-      <c r="AA44" s="53" t="n"/>
-      <c r="AB44" s="54" t="n"/>
-      <c r="AC44" s="52" t="n"/>
-      <c r="AD44" s="53" t="n"/>
-      <c r="AE44" s="53" t="n"/>
-      <c r="AF44" s="53" t="n"/>
-      <c r="AG44" s="53" t="n"/>
-      <c r="AH44" s="53" t="n"/>
-      <c r="AI44" s="53" t="n"/>
-      <c r="AJ44" s="53" t="n"/>
-      <c r="AK44" s="53" t="n"/>
-      <c r="AL44" s="53" t="n"/>
-      <c r="AM44" s="53" t="n"/>
-      <c r="AN44" s="53" t="n"/>
-      <c r="AO44" s="54" t="n"/>
-      <c r="AP44" s="52" t="n"/>
-      <c r="AQ44" s="53" t="n"/>
-      <c r="AR44" s="53" t="n"/>
-      <c r="AS44" s="53" t="n"/>
-      <c r="AT44" s="53" t="n"/>
-      <c r="AU44" s="53" t="n"/>
-      <c r="AV44" s="54" t="n"/>
-      <c r="AW44" s="52" t="n"/>
-      <c r="AX44" s="53" t="n"/>
-      <c r="AY44" s="53" t="n"/>
-      <c r="AZ44" s="53" t="n"/>
-      <c r="BA44" s="53" t="n"/>
-      <c r="BB44" s="53" t="n"/>
-      <c r="BC44" s="54" t="n"/>
-      <c r="BD44" s="52" t="n"/>
-      <c r="BE44" s="53" t="n"/>
-      <c r="BF44" s="53" t="n"/>
-      <c r="BG44" s="53" t="n"/>
-      <c r="BH44" s="53" t="n"/>
-      <c r="BI44" s="53" t="n"/>
-      <c r="BJ44" s="54" t="n"/>
+      <c r="A44" s="55" t="n"/>
+      <c r="B44" s="55" t="n"/>
+      <c r="C44" s="55" t="n"/>
+      <c r="D44" s="55" t="n"/>
+      <c r="E44" s="55" t="n"/>
+      <c r="F44" s="55" t="n"/>
+      <c r="G44" s="67" t="n"/>
+      <c r="H44" s="67" t="n"/>
+      <c r="I44" s="67" t="n"/>
+      <c r="J44" s="67" t="n"/>
+      <c r="K44" s="67" t="n"/>
+      <c r="L44" s="67" t="n"/>
+      <c r="M44" s="67" t="n"/>
+      <c r="N44" s="67" t="n"/>
+      <c r="O44" s="61" t="n"/>
+      <c r="P44" s="59" t="n"/>
+      <c r="Q44" s="59" t="n"/>
+      <c r="R44" s="59" t="n"/>
+      <c r="S44" s="59" t="n"/>
+      <c r="T44" s="59" t="n"/>
+      <c r="U44" s="60" t="n"/>
+      <c r="V44" s="58" t="n"/>
+      <c r="W44" s="59" t="n"/>
+      <c r="X44" s="59" t="n"/>
+      <c r="Y44" s="59" t="n"/>
+      <c r="Z44" s="59" t="n"/>
+      <c r="AA44" s="59" t="n"/>
+      <c r="AB44" s="60" t="n"/>
+      <c r="AC44" s="58" t="n"/>
+      <c r="AD44" s="59" t="n"/>
+      <c r="AE44" s="59" t="n"/>
+      <c r="AF44" s="59" t="n"/>
+      <c r="AG44" s="59" t="n"/>
+      <c r="AH44" s="59" t="n"/>
+      <c r="AI44" s="59" t="n"/>
+      <c r="AJ44" s="59" t="n"/>
+      <c r="AK44" s="59" t="n"/>
+      <c r="AL44" s="59" t="n"/>
+      <c r="AM44" s="59" t="n"/>
+      <c r="AN44" s="59" t="n"/>
+      <c r="AO44" s="60" t="n"/>
+      <c r="AP44" s="58" t="n"/>
+      <c r="AQ44" s="59" t="n"/>
+      <c r="AR44" s="59" t="n"/>
+      <c r="AS44" s="59" t="n"/>
+      <c r="AT44" s="59" t="n"/>
+      <c r="AU44" s="59" t="n"/>
+      <c r="AV44" s="60" t="n"/>
+      <c r="AW44" s="58" t="n"/>
+      <c r="AX44" s="59" t="n"/>
+      <c r="AY44" s="59" t="n"/>
+      <c r="AZ44" s="59" t="n"/>
+      <c r="BA44" s="59" t="n"/>
+      <c r="BB44" s="59" t="n"/>
+      <c r="BC44" s="60" t="n"/>
+      <c r="BD44" s="58" t="n"/>
+      <c r="BE44" s="59" t="n"/>
+      <c r="BF44" s="59" t="n"/>
+      <c r="BG44" s="59" t="n"/>
+      <c r="BH44" s="59" t="n"/>
+      <c r="BI44" s="59" t="n"/>
+      <c r="BJ44" s="60" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="21" t="n"/>
-      <c r="I45" s="21" t="n"/>
-      <c r="J45" s="21" t="n"/>
-      <c r="K45" s="21" t="n"/>
-      <c r="L45" s="21" t="n"/>
-      <c r="M45" s="21" t="n"/>
-      <c r="N45" s="21" t="n"/>
-      <c r="O45" s="20" t="n"/>
-      <c r="P45" s="44" t="n"/>
-      <c r="Q45" s="44" t="n"/>
-      <c r="R45" s="44" t="n"/>
-      <c r="S45" s="44" t="n"/>
-      <c r="T45" s="44" t="n"/>
-      <c r="U45" s="45" t="n"/>
+      <c r="A45" s="55" t="n"/>
+      <c r="B45" s="55" t="n"/>
+      <c r="C45" s="55" t="n"/>
+      <c r="D45" s="55" t="n"/>
+      <c r="E45" s="55" t="n"/>
+      <c r="F45" s="55" t="n"/>
+      <c r="G45" s="67" t="n"/>
+      <c r="H45" s="67" t="n"/>
+      <c r="I45" s="67" t="n"/>
+      <c r="J45" s="67" t="n"/>
+      <c r="K45" s="67" t="n"/>
+      <c r="L45" s="67" t="n"/>
+      <c r="M45" s="67" t="n"/>
+      <c r="N45" s="67" t="n"/>
+      <c r="O45" s="71" t="n"/>
+      <c r="P45" s="48" t="n"/>
+      <c r="Q45" s="48" t="n"/>
+      <c r="R45" s="48" t="n"/>
+      <c r="S45" s="48" t="n"/>
+      <c r="T45" s="48" t="n"/>
+      <c r="U45" s="49" t="n"/>
       <c r="V45" s="20" t="n"/>
-      <c r="W45" s="44" t="n"/>
-      <c r="X45" s="44" t="n"/>
-      <c r="Y45" s="44" t="n"/>
-      <c r="Z45" s="44" t="n"/>
-      <c r="AA45" s="44" t="n"/>
-      <c r="AB45" s="45" t="n"/>
+      <c r="W45" s="48" t="n"/>
+      <c r="X45" s="48" t="n"/>
+      <c r="Y45" s="48" t="n"/>
+      <c r="Z45" s="48" t="n"/>
+      <c r="AA45" s="48" t="n"/>
+      <c r="AB45" s="49" t="n"/>
       <c r="AC45" s="22" t="n"/>
-      <c r="AD45" s="44" t="n"/>
-      <c r="AE45" s="44" t="n"/>
-      <c r="AF45" s="44" t="n"/>
-      <c r="AG45" s="44" t="n"/>
-      <c r="AH45" s="44" t="n"/>
-      <c r="AI45" s="44" t="n"/>
-      <c r="AJ45" s="44" t="n"/>
-      <c r="AK45" s="44" t="n"/>
-      <c r="AL45" s="44" t="n"/>
-      <c r="AM45" s="44" t="n"/>
-      <c r="AN45" s="44" t="n"/>
-      <c r="AO45" s="45" t="n"/>
+      <c r="AD45" s="48" t="n"/>
+      <c r="AE45" s="48" t="n"/>
+      <c r="AF45" s="48" t="n"/>
+      <c r="AG45" s="48" t="n"/>
+      <c r="AH45" s="48" t="n"/>
+      <c r="AI45" s="48" t="n"/>
+      <c r="AJ45" s="48" t="n"/>
+      <c r="AK45" s="48" t="n"/>
+      <c r="AL45" s="48" t="n"/>
+      <c r="AM45" s="48" t="n"/>
+      <c r="AN45" s="48" t="n"/>
+      <c r="AO45" s="49" t="n"/>
       <c r="AP45" s="20" t="n"/>
-      <c r="AQ45" s="44" t="n"/>
-      <c r="AR45" s="44" t="n"/>
-      <c r="AS45" s="44" t="n"/>
-      <c r="AT45" s="44" t="n"/>
-      <c r="AU45" s="44" t="n"/>
-      <c r="AV45" s="45" t="n"/>
+      <c r="AQ45" s="48" t="n"/>
+      <c r="AR45" s="48" t="n"/>
+      <c r="AS45" s="48" t="n"/>
+      <c r="AT45" s="48" t="n"/>
+      <c r="AU45" s="48" t="n"/>
+      <c r="AV45" s="49" t="n"/>
       <c r="AW45" s="20" t="n"/>
-      <c r="AX45" s="44" t="n"/>
-      <c r="AY45" s="44" t="n"/>
-      <c r="AZ45" s="44" t="n"/>
-      <c r="BA45" s="44" t="n"/>
-      <c r="BB45" s="44" t="n"/>
-      <c r="BC45" s="45" t="n"/>
+      <c r="AX45" s="48" t="n"/>
+      <c r="AY45" s="48" t="n"/>
+      <c r="AZ45" s="48" t="n"/>
+      <c r="BA45" s="48" t="n"/>
+      <c r="BB45" s="48" t="n"/>
+      <c r="BC45" s="49" t="n"/>
       <c r="BD45" s="20" t="n"/>
-      <c r="BE45" s="44" t="n"/>
-      <c r="BF45" s="44" t="n"/>
-      <c r="BG45" s="44" t="n"/>
-      <c r="BH45" s="44" t="n"/>
-      <c r="BI45" s="44" t="n"/>
-      <c r="BJ45" s="45" t="n"/>
+      <c r="BE45" s="48" t="n"/>
+      <c r="BF45" s="48" t="n"/>
+      <c r="BG45" s="48" t="n"/>
+      <c r="BH45" s="48" t="n"/>
+      <c r="BI45" s="48" t="n"/>
+      <c r="BJ45" s="49" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="G46" s="21" t="n"/>
-      <c r="H46" s="21" t="n"/>
-      <c r="I46" s="21" t="n"/>
-      <c r="J46" s="21" t="n"/>
-      <c r="K46" s="21" t="n"/>
-      <c r="L46" s="21" t="n"/>
-      <c r="M46" s="21" t="n"/>
-      <c r="N46" s="21" t="n"/>
-      <c r="O46" s="50" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="50" t="n"/>
-      <c r="AB46" s="51" t="n"/>
-      <c r="AC46" s="50" t="n"/>
-      <c r="AO46" s="51" t="n"/>
-      <c r="AP46" s="50" t="n"/>
-      <c r="AV46" s="51" t="n"/>
-      <c r="AW46" s="50" t="n"/>
-      <c r="BC46" s="51" t="n"/>
-      <c r="BD46" s="50" t="n"/>
-      <c r="BJ46" s="51" t="n"/>
+      <c r="A46" s="55" t="n"/>
+      <c r="B46" s="55" t="n"/>
+      <c r="C46" s="55" t="n"/>
+      <c r="D46" s="55" t="n"/>
+      <c r="E46" s="55" t="n"/>
+      <c r="F46" s="55" t="n"/>
+      <c r="G46" s="67" t="n"/>
+      <c r="H46" s="67" t="n"/>
+      <c r="I46" s="67" t="n"/>
+      <c r="J46" s="67" t="n"/>
+      <c r="K46" s="67" t="n"/>
+      <c r="L46" s="67" t="n"/>
+      <c r="M46" s="67" t="n"/>
+      <c r="N46" s="67" t="n"/>
+      <c r="O46" s="54" t="n"/>
+      <c r="U46" s="57" t="n"/>
+      <c r="V46" s="68" t="n"/>
+      <c r="AB46" s="57" t="n"/>
+      <c r="AC46" s="68" t="n"/>
+      <c r="AO46" s="57" t="n"/>
+      <c r="AP46" s="68" t="n"/>
+      <c r="AV46" s="57" t="n"/>
+      <c r="AW46" s="68" t="n"/>
+      <c r="BC46" s="57" t="n"/>
+      <c r="BD46" s="68" t="n"/>
+      <c r="BJ46" s="57" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="G47" s="21" t="n"/>
-      <c r="H47" s="21" t="n"/>
-      <c r="I47" s="21" t="n"/>
-      <c r="J47" s="21" t="n"/>
-      <c r="K47" s="21" t="n"/>
-      <c r="L47" s="21" t="n"/>
-      <c r="M47" s="21" t="n"/>
-      <c r="N47" s="21" t="n"/>
-      <c r="O47" s="52" t="n"/>
-      <c r="P47" s="53" t="n"/>
-      <c r="Q47" s="53" t="n"/>
-      <c r="R47" s="53" t="n"/>
-      <c r="S47" s="53" t="n"/>
-      <c r="T47" s="53" t="n"/>
-      <c r="U47" s="54" t="n"/>
-      <c r="V47" s="52" t="n"/>
-      <c r="W47" s="53" t="n"/>
-      <c r="X47" s="53" t="n"/>
-      <c r="Y47" s="53" t="n"/>
-      <c r="Z47" s="53" t="n"/>
-      <c r="AA47" s="53" t="n"/>
-      <c r="AB47" s="54" t="n"/>
-      <c r="AC47" s="52" t="n"/>
-      <c r="AD47" s="53" t="n"/>
-      <c r="AE47" s="53" t="n"/>
-      <c r="AF47" s="53" t="n"/>
-      <c r="AG47" s="53" t="n"/>
-      <c r="AH47" s="53" t="n"/>
-      <c r="AI47" s="53" t="n"/>
-      <c r="AJ47" s="53" t="n"/>
-      <c r="AK47" s="53" t="n"/>
-      <c r="AL47" s="53" t="n"/>
-      <c r="AM47" s="53" t="n"/>
-      <c r="AN47" s="53" t="n"/>
-      <c r="AO47" s="54" t="n"/>
-      <c r="AP47" s="52" t="n"/>
-      <c r="AQ47" s="53" t="n"/>
-      <c r="AR47" s="53" t="n"/>
-      <c r="AS47" s="53" t="n"/>
-      <c r="AT47" s="53" t="n"/>
-      <c r="AU47" s="53" t="n"/>
-      <c r="AV47" s="54" t="n"/>
-      <c r="AW47" s="52" t="n"/>
-      <c r="AX47" s="53" t="n"/>
-      <c r="AY47" s="53" t="n"/>
-      <c r="AZ47" s="53" t="n"/>
-      <c r="BA47" s="53" t="n"/>
-      <c r="BB47" s="53" t="n"/>
-      <c r="BC47" s="54" t="n"/>
-      <c r="BD47" s="52" t="n"/>
-      <c r="BE47" s="53" t="n"/>
-      <c r="BF47" s="53" t="n"/>
-      <c r="BG47" s="53" t="n"/>
-      <c r="BH47" s="53" t="n"/>
-      <c r="BI47" s="53" t="n"/>
-      <c r="BJ47" s="54" t="n"/>
+      <c r="A47" s="55" t="n"/>
+      <c r="B47" s="55" t="n"/>
+      <c r="C47" s="55" t="n"/>
+      <c r="D47" s="55" t="n"/>
+      <c r="E47" s="55" t="n"/>
+      <c r="F47" s="55" t="n"/>
+      <c r="G47" s="67" t="n"/>
+      <c r="H47" s="67" t="n"/>
+      <c r="I47" s="67" t="n"/>
+      <c r="J47" s="67" t="n"/>
+      <c r="K47" s="67" t="n"/>
+      <c r="L47" s="67" t="n"/>
+      <c r="M47" s="67" t="n"/>
+      <c r="N47" s="67" t="n"/>
+      <c r="O47" s="61" t="n"/>
+      <c r="P47" s="59" t="n"/>
+      <c r="Q47" s="59" t="n"/>
+      <c r="R47" s="59" t="n"/>
+      <c r="S47" s="59" t="n"/>
+      <c r="T47" s="59" t="n"/>
+      <c r="U47" s="60" t="n"/>
+      <c r="V47" s="58" t="n"/>
+      <c r="W47" s="59" t="n"/>
+      <c r="X47" s="59" t="n"/>
+      <c r="Y47" s="59" t="n"/>
+      <c r="Z47" s="59" t="n"/>
+      <c r="AA47" s="59" t="n"/>
+      <c r="AB47" s="60" t="n"/>
+      <c r="AC47" s="58" t="n"/>
+      <c r="AD47" s="59" t="n"/>
+      <c r="AE47" s="59" t="n"/>
+      <c r="AF47" s="59" t="n"/>
+      <c r="AG47" s="59" t="n"/>
+      <c r="AH47" s="59" t="n"/>
+      <c r="AI47" s="59" t="n"/>
+      <c r="AJ47" s="59" t="n"/>
+      <c r="AK47" s="59" t="n"/>
+      <c r="AL47" s="59" t="n"/>
+      <c r="AM47" s="59" t="n"/>
+      <c r="AN47" s="59" t="n"/>
+      <c r="AO47" s="60" t="n"/>
+      <c r="AP47" s="58" t="n"/>
+      <c r="AQ47" s="59" t="n"/>
+      <c r="AR47" s="59" t="n"/>
+      <c r="AS47" s="59" t="n"/>
+      <c r="AT47" s="59" t="n"/>
+      <c r="AU47" s="59" t="n"/>
+      <c r="AV47" s="60" t="n"/>
+      <c r="AW47" s="58" t="n"/>
+      <c r="AX47" s="59" t="n"/>
+      <c r="AY47" s="59" t="n"/>
+      <c r="AZ47" s="59" t="n"/>
+      <c r="BA47" s="59" t="n"/>
+      <c r="BB47" s="59" t="n"/>
+      <c r="BC47" s="60" t="n"/>
+      <c r="BD47" s="58" t="n"/>
+      <c r="BE47" s="59" t="n"/>
+      <c r="BF47" s="59" t="n"/>
+      <c r="BG47" s="59" t="n"/>
+      <c r="BH47" s="59" t="n"/>
+      <c r="BI47" s="59" t="n"/>
+      <c r="BJ47" s="60" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="O48" s="19" t="n"/>
+      <c r="A48" s="55" t="n"/>
+      <c r="B48" s="55" t="n"/>
+      <c r="C48" s="55" t="n"/>
+      <c r="D48" s="55" t="n"/>
+      <c r="E48" s="55" t="n"/>
+      <c r="F48" s="55" t="n"/>
+      <c r="G48" s="55" t="n"/>
+      <c r="H48" s="55" t="n"/>
+      <c r="I48" s="55" t="n"/>
+      <c r="J48" s="55" t="n"/>
+      <c r="K48" s="55" t="n"/>
+      <c r="L48" s="55" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="72" t="n"/>
       <c r="V48" s="19" t="n"/>
       <c r="AC48" s="19" t="n"/>
       <c r="AP48" s="19" t="n"/>
       <c r="AW48" s="19" t="n"/>
       <c r="BD48" s="19" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1"/>
-    <row r="50" ht="15" customHeight="1"/>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="55" t="n"/>
+      <c r="B49" s="55" t="n"/>
+      <c r="C49" s="55" t="n"/>
+      <c r="D49" s="55" t="n"/>
+      <c r="E49" s="55" t="n"/>
+      <c r="F49" s="55" t="n"/>
+      <c r="G49" s="55" t="n"/>
+      <c r="H49" s="55" t="n"/>
+      <c r="I49" s="55" t="n"/>
+      <c r="J49" s="55" t="n"/>
+      <c r="K49" s="55" t="n"/>
+      <c r="L49" s="55" t="n"/>
+      <c r="M49" s="55" t="n"/>
+      <c r="N49" s="55" t="n"/>
+      <c r="O49" s="55" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="55" t="n"/>
+      <c r="B50" s="55" t="n"/>
+      <c r="C50" s="55" t="n"/>
+      <c r="D50" s="55" t="n"/>
+      <c r="E50" s="55" t="n"/>
+      <c r="F50" s="55" t="n"/>
+      <c r="G50" s="55" t="n"/>
+      <c r="H50" s="55" t="n"/>
+      <c r="I50" s="55" t="n"/>
+      <c r="J50" s="55" t="n"/>
+      <c r="K50" s="55" t="n"/>
+      <c r="L50" s="55" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="55" t="n"/>
+      <c r="B51" s="55" t="n"/>
+      <c r="C51" s="55" t="n"/>
+      <c r="D51" s="55" t="n"/>
+      <c r="E51" s="55" t="n"/>
+      <c r="F51" s="55" t="n"/>
+      <c r="G51" s="55" t="n"/>
+      <c r="H51" s="55" t="n"/>
+      <c r="I51" s="55" t="n"/>
+      <c r="J51" s="55" t="n"/>
+      <c r="K51" s="55" t="n"/>
+      <c r="L51" s="55" t="n"/>
+      <c r="M51" s="55" t="n"/>
+      <c r="N51" s="55" t="n"/>
+      <c r="O51" s="55" t="n"/>
+    </row>
     <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="55" t="n"/>
+      <c r="B52" s="55" t="n"/>
+      <c r="C52" s="55" t="n"/>
+      <c r="D52" s="55" t="n"/>
+      <c r="E52" s="55" t="n"/>
+      <c r="F52" s="55" t="n"/>
+      <c r="G52" s="55" t="n"/>
+      <c r="H52" s="55" t="n"/>
+      <c r="I52" s="55" t="n"/>
+      <c r="J52" s="55" t="n"/>
+      <c r="K52" s="55" t="n"/>
+      <c r="L52" s="55" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
       <c r="BH52" s="8" t="n"/>
       <c r="BI52" s="8" t="n"/>
       <c r="BJ52" s="8" t="n"/>
@@ -3131,22 +3599,54 @@
       <c r="BQ52" s="9" t="n"/>
       <c r="BR52" s="9" t="n"/>
     </row>
+    <row r="53">
+      <c r="A53" s="55" t="n"/>
+      <c r="B53" s="55" t="n"/>
+      <c r="C53" s="55" t="n"/>
+      <c r="D53" s="55" t="n"/>
+      <c r="E53" s="55" t="n"/>
+      <c r="F53" s="55" t="n"/>
+      <c r="G53" s="55" t="n"/>
+      <c r="H53" s="55" t="n"/>
+      <c r="I53" s="55" t="n"/>
+      <c r="J53" s="55" t="n"/>
+      <c r="K53" s="55" t="n"/>
+      <c r="L53" s="55" t="n"/>
+      <c r="M53" s="55" t="n"/>
+      <c r="N53" s="55" t="n"/>
+      <c r="O53" s="55" t="n"/>
+    </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="AA54" s="55" t="n"/>
-      <c r="AB54" s="55" t="n"/>
-      <c r="AC54" s="55" t="n"/>
-      <c r="AD54" s="55" t="n"/>
-      <c r="AE54" s="55" t="n"/>
-      <c r="AF54" s="55" t="n"/>
-      <c r="AG54" s="55" t="n"/>
-      <c r="AH54" s="55" t="n"/>
-      <c r="AI54" s="55" t="n"/>
-      <c r="AJ54" s="55" t="n"/>
-      <c r="AK54" s="55" t="n"/>
-      <c r="AL54" s="55" t="n"/>
-      <c r="AM54" s="55" t="n"/>
-      <c r="AN54" s="55" t="n"/>
-      <c r="AO54" s="55" t="n"/>
+      <c r="A54" s="55" t="n"/>
+      <c r="B54" s="55" t="n"/>
+      <c r="C54" s="55" t="n"/>
+      <c r="D54" s="55" t="n"/>
+      <c r="E54" s="55" t="n"/>
+      <c r="F54" s="55" t="n"/>
+      <c r="G54" s="55" t="n"/>
+      <c r="H54" s="55" t="n"/>
+      <c r="I54" s="55" t="n"/>
+      <c r="J54" s="55" t="n"/>
+      <c r="K54" s="55" t="n"/>
+      <c r="L54" s="55" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="AA54" s="73" t="n"/>
+      <c r="AB54" s="73" t="n"/>
+      <c r="AC54" s="73" t="n"/>
+      <c r="AD54" s="73" t="n"/>
+      <c r="AE54" s="73" t="n"/>
+      <c r="AF54" s="73" t="n"/>
+      <c r="AG54" s="73" t="n"/>
+      <c r="AH54" s="73" t="n"/>
+      <c r="AI54" s="73" t="n"/>
+      <c r="AJ54" s="73" t="n"/>
+      <c r="AK54" s="73" t="n"/>
+      <c r="AL54" s="73" t="n"/>
+      <c r="AM54" s="73" t="n"/>
+      <c r="AN54" s="73" t="n"/>
+      <c r="AO54" s="73" t="n"/>
       <c r="AP54" s="11" t="n"/>
       <c r="AQ54" s="11" t="n"/>
       <c r="AR54" s="11" t="n"/>
@@ -3226,1443 +3726,1575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.61328125" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="30.6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="13" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="13" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="52" max="52"/>
+    <col width="13" customWidth="1" min="53" max="53"/>
+    <col width="13" customWidth="1" min="54" max="54"/>
+    <col width="13" customWidth="1" min="55" max="55"/>
+    <col width="13" customWidth="1" min="56" max="56"/>
+    <col width="13" customWidth="1" min="57" max="57"/>
+    <col width="13" customWidth="1" min="58" max="58"/>
+    <col width="13" customWidth="1" min="59" max="59"/>
+    <col width="13" customWidth="1" min="60" max="60"/>
+    <col width="13" customWidth="1" min="61" max="61"/>
+    <col width="13" customWidth="1" min="62" max="62"/>
+    <col width="13" customWidth="1" min="63" max="63"/>
+    <col width="13" customWidth="1" min="64" max="64"/>
+    <col width="13" customWidth="1" min="66" max="66"/>
+    <col width="13" customWidth="1" min="68" max="68"/>
+    <col width="13" customWidth="1" min="69" max="69"/>
+    <col width="13" customWidth="1" min="70" max="70"/>
+    <col width="13" customWidth="1" min="71" max="71"/>
+    <col width="13" customWidth="1" min="72" max="72"/>
+    <col width="13" customWidth="1" min="73" max="73"/>
+    <col width="13" customWidth="1" min="74" max="74"/>
+    <col width="13" customWidth="1" min="75" max="75"/>
+    <col width="13" customWidth="1" min="78" max="78"/>
+    <col width="13" customWidth="1" min="79" max="79"/>
+    <col width="13" customWidth="1" min="80" max="80"/>
+    <col width="13" customWidth="1" min="81" max="81"/>
+    <col width="13" customWidth="1" min="82" max="82"/>
+    <col width="13" customWidth="1" min="83" max="83"/>
+    <col width="13" customWidth="1" min="84" max="84"/>
+    <col width="13" customWidth="1" min="85" max="85"/>
+    <col width="13" customWidth="1" min="87" max="87"/>
+    <col width="13" customWidth="1" min="88" max="88"/>
+    <col width="13" customWidth="1" min="89" max="89"/>
+    <col width="13" customWidth="1" min="90" max="90"/>
+    <col width="13" customWidth="1" min="91" max="91"/>
+    <col width="13" customWidth="1" min="92" max="92"/>
+    <col width="13" customWidth="1" min="93" max="93"/>
+    <col width="13" customWidth="1" min="96" max="96"/>
+    <col width="13" customWidth="1" min="97" max="97"/>
+    <col width="13" customWidth="1" min="98" max="98"/>
+    <col width="13" customWidth="1" min="99" max="99"/>
+    <col width="13" customWidth="1" min="100" max="100"/>
+    <col width="13" customWidth="1" min="101" max="101"/>
+    <col width="13" customWidth="1" min="102" max="102"/>
+    <col width="13" customWidth="1" min="103" max="103"/>
+    <col width="13" customWidth="1" min="104" max="104"/>
+    <col width="13" customWidth="1" min="105" max="105"/>
+    <col width="13" customWidth="1" min="106" max="106"/>
+    <col width="13" customWidth="1" min="107" max="107"/>
+    <col width="13" customWidth="1" min="108" max="108"/>
+    <col width="13" customWidth="1" min="110" max="110"/>
+    <col width="13" customWidth="1" min="111" max="111"/>
+    <col width="13" customWidth="1" min="112" max="112"/>
+    <col width="13" customWidth="1" min="113" max="113"/>
+    <col width="13" customWidth="1" min="114" max="114"/>
+    <col width="13" customWidth="1" min="115" max="115"/>
+    <col width="13" customWidth="1" min="116" max="116"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
-      <c r="A1" s="35" t="n"/>
-      <c r="B1" s="36" t="n"/>
-      <c r="C1" s="35">
+      <c r="A1" s="74" t="n"/>
+      <c r="B1" s="75" t="n"/>
+      <c r="C1" s="74">
         <f>PORTADA!Z1</f>
         <v/>
       </c>
-      <c r="D1" s="46" t="n"/>
-      <c r="E1" s="46" t="n"/>
-      <c r="F1" s="46" t="n"/>
-      <c r="G1" s="46" t="n"/>
-      <c r="H1" s="46" t="n"/>
-      <c r="I1" s="46" t="n"/>
-      <c r="J1" s="46" t="n"/>
-      <c r="K1" s="46" t="n"/>
-      <c r="L1" s="47" t="n"/>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="D1" s="65" t="n"/>
+      <c r="E1" s="65" t="n"/>
+      <c r="F1" s="65" t="n"/>
+      <c r="G1" s="65" t="n"/>
+      <c r="H1" s="65" t="n"/>
+      <c r="I1" s="65" t="n"/>
+      <c r="J1" s="65" t="n"/>
+      <c r="K1" s="65" t="n"/>
+      <c r="L1" s="66" t="n"/>
+      <c r="M1" s="76" t="inlineStr">
         <is>
           <t>CODIGO:</t>
         </is>
       </c>
-      <c r="N1" s="32">
+      <c r="N1" s="77">
         <f>PORTADA!BO1</f>
         <v/>
       </c>
-      <c r="O1" s="47" t="n"/>
+      <c r="O1" s="66" t="n"/>
     </row>
     <row r="2" ht="29.25" customHeight="1">
-      <c r="A2" s="56" t="n"/>
-      <c r="B2" s="56" t="n"/>
-      <c r="C2" s="35">
+      <c r="A2" s="78" t="n"/>
+      <c r="B2" s="78" t="n"/>
+      <c r="C2" s="74">
         <f>PORTADA!Z3</f>
         <v/>
       </c>
-      <c r="D2" s="44" t="n"/>
-      <c r="E2" s="44" t="n"/>
-      <c r="F2" s="44" t="n"/>
-      <c r="G2" s="44" t="n"/>
-      <c r="H2" s="44" t="n"/>
-      <c r="I2" s="44" t="n"/>
-      <c r="J2" s="44" t="n"/>
-      <c r="K2" s="44" t="n"/>
-      <c r="L2" s="45" t="n"/>
-      <c r="M2" s="12" t="inlineStr">
+      <c r="D2" s="45" t="n"/>
+      <c r="E2" s="45" t="n"/>
+      <c r="F2" s="45" t="n"/>
+      <c r="G2" s="45" t="n"/>
+      <c r="H2" s="45" t="n"/>
+      <c r="I2" s="45" t="n"/>
+      <c r="J2" s="45" t="n"/>
+      <c r="K2" s="45" t="n"/>
+      <c r="L2" s="46" t="n"/>
+      <c r="M2" s="76" t="inlineStr">
         <is>
           <t>REVISION:</t>
         </is>
       </c>
-      <c r="N2" s="32">
+      <c r="N2" s="77">
         <f>PORTADA!BO2</f>
         <v/>
       </c>
-      <c r="O2" s="47" t="n"/>
+      <c r="O2" s="66" t="n"/>
     </row>
     <row r="3" ht="29.25" customHeight="1">
-      <c r="A3" s="56" t="n"/>
-      <c r="B3" s="56" t="n"/>
-      <c r="C3" s="52" t="n"/>
-      <c r="D3" s="53" t="n"/>
-      <c r="E3" s="53" t="n"/>
-      <c r="F3" s="53" t="n"/>
-      <c r="G3" s="53" t="n"/>
-      <c r="H3" s="53" t="n"/>
-      <c r="I3" s="53" t="n"/>
-      <c r="J3" s="53" t="n"/>
-      <c r="K3" s="53" t="n"/>
-      <c r="L3" s="54" t="n"/>
-      <c r="M3" s="12" t="inlineStr">
+      <c r="A3" s="78" t="n"/>
+      <c r="B3" s="78" t="n"/>
+      <c r="C3" s="61" t="n"/>
+      <c r="D3" s="62" t="n"/>
+      <c r="E3" s="62" t="n"/>
+      <c r="F3" s="62" t="n"/>
+      <c r="G3" s="62" t="n"/>
+      <c r="H3" s="62" t="n"/>
+      <c r="I3" s="62" t="n"/>
+      <c r="J3" s="62" t="n"/>
+      <c r="K3" s="62" t="n"/>
+      <c r="L3" s="63" t="n"/>
+      <c r="M3" s="76" t="inlineStr">
         <is>
           <t>FECHA:</t>
         </is>
       </c>
-      <c r="N3" s="32">
+      <c r="N3" s="77">
         <f>PORTADA!BO3</f>
         <v/>
       </c>
-      <c r="O3" s="47" t="n"/>
+      <c r="O3" s="66" t="n"/>
     </row>
     <row r="4" ht="29.25" customHeight="1">
-      <c r="A4" s="56" t="n"/>
-      <c r="B4" s="56" t="n"/>
-      <c r="C4" s="35">
+      <c r="A4" s="78" t="n"/>
+      <c r="B4" s="78" t="n"/>
+      <c r="C4" s="74">
         <f>PORTADA!Z5</f>
         <v/>
       </c>
-      <c r="D4" s="44" t="n"/>
-      <c r="E4" s="44" t="n"/>
-      <c r="F4" s="44" t="n"/>
-      <c r="G4" s="44" t="n"/>
-      <c r="H4" s="44" t="n"/>
-      <c r="I4" s="44" t="n"/>
-      <c r="J4" s="44" t="n"/>
-      <c r="K4" s="44" t="n"/>
-      <c r="L4" s="45" t="n"/>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="45" t="n"/>
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="45" t="n"/>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="45" t="n"/>
+      <c r="K4" s="45" t="n"/>
+      <c r="L4" s="46" t="n"/>
+      <c r="M4" s="76" t="inlineStr">
         <is>
           <t>ELABORO:</t>
         </is>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="77">
         <f>PORTADA!BO4</f>
         <v/>
       </c>
-      <c r="O4" s="47" t="n"/>
+      <c r="O4" s="66" t="n"/>
     </row>
     <row r="5" ht="29.25" customHeight="1">
-      <c r="A5" s="57" t="n"/>
-      <c r="B5" s="57" t="n"/>
-      <c r="C5" s="50" t="n"/>
-      <c r="L5" s="51" t="n"/>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="A5" s="79" t="n"/>
+      <c r="B5" s="79" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="55" t="n"/>
+      <c r="E5" s="55" t="n"/>
+      <c r="F5" s="55" t="n"/>
+      <c r="G5" s="55" t="n"/>
+      <c r="H5" s="55" t="n"/>
+      <c r="I5" s="55" t="n"/>
+      <c r="J5" s="55" t="n"/>
+      <c r="K5" s="55" t="n"/>
+      <c r="L5" s="56" t="n"/>
+      <c r="M5" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">REVISO:      </t>
         </is>
       </c>
-      <c r="N5" s="32">
+      <c r="N5" s="77">
         <f>PORTADA!BO5</f>
         <v/>
       </c>
-      <c r="O5" s="47" t="n"/>
+      <c r="O5" s="66" t="n"/>
     </row>
     <row r="6" ht="29.25" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>PROYECTO:</t>
         </is>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="74">
         <f>PORTADA!N6</f>
         <v/>
       </c>
-      <c r="C6" s="52" t="n"/>
-      <c r="D6" s="53" t="n"/>
-      <c r="E6" s="53" t="n"/>
-      <c r="F6" s="53" t="n"/>
-      <c r="G6" s="53" t="n"/>
-      <c r="H6" s="53" t="n"/>
-      <c r="I6" s="53" t="n"/>
-      <c r="J6" s="53" t="n"/>
-      <c r="K6" s="53" t="n"/>
-      <c r="L6" s="54" t="n"/>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="62" t="n"/>
+      <c r="E6" s="62" t="n"/>
+      <c r="F6" s="62" t="n"/>
+      <c r="G6" s="62" t="n"/>
+      <c r="H6" s="62" t="n"/>
+      <c r="I6" s="62" t="n"/>
+      <c r="J6" s="62" t="n"/>
+      <c r="K6" s="62" t="n"/>
+      <c r="L6" s="63" t="n"/>
+      <c r="M6" s="76" t="inlineStr">
         <is>
           <t>APROBO:</t>
         </is>
       </c>
-      <c r="N6" s="32">
+      <c r="N6" s="77">
         <f>PORTADA!BO6</f>
         <v/>
       </c>
-      <c r="O6" s="47" t="n"/>
+      <c r="O6" s="66" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="80" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="80" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="80" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="80" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="80" t="n">
         <v>8</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="80" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="80" t="n">
         <v>10</v>
       </c>
-      <c r="K7" s="18" t="n">
+      <c r="K7" s="80" t="n">
         <v>11</v>
       </c>
-      <c r="L7" s="18" t="n">
+      <c r="L7" s="80" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="18" t="n">
+      <c r="M7" s="80" t="n">
         <v>13</v>
       </c>
-      <c r="N7" s="18" t="n">
+      <c r="N7" s="80" t="n">
         <v>14</v>
       </c>
-      <c r="O7" s="18" t="n">
+      <c r="O7" s="80" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="58" t="inlineStr">
+    <row r="9" ht="465" customHeight="1">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Hoja de datos: etapa de filtración (prefiltro MERV 8 + filtro final MERV 13-14)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="59" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="82" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B10" s="59" t="n"/>
-      <c r="C10" s="59" t="n"/>
-      <c r="D10" s="59" t="n"/>
-      <c r="E10" s="59" t="n"/>
-      <c r="F10" s="59" t="n"/>
-      <c r="G10" s="59" t="n"/>
-      <c r="H10" s="59" t="n"/>
-      <c r="I10" s="59" t="inlineStr">
+      <c r="B10" s="82" t="n"/>
+      <c r="C10" s="82" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="82" t="n"/>
+      <c r="F10" s="82" t="n"/>
+      <c r="G10" s="82" t="n"/>
+      <c r="H10" s="82" t="n"/>
+      <c r="I10" s="82" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="J10" s="59" t="n"/>
-      <c r="K10" s="59" t="n"/>
-      <c r="L10" s="59" t="n"/>
-      <c r="M10" s="59" t="n"/>
-      <c r="N10" s="59" t="n"/>
-      <c r="O10" s="59" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="J10" s="82" t="n"/>
+      <c r="K10" s="82" t="n"/>
+      <c r="L10" s="82" t="n"/>
+      <c r="M10" s="82" t="n"/>
+      <c r="N10" s="82" t="n"/>
+      <c r="O10" s="82" t="n"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B11" s="61" t="n"/>
-      <c r="C11" s="61" t="n"/>
-      <c r="D11" s="61" t="n"/>
-      <c r="E11" s="61" t="n"/>
-      <c r="F11" s="61" t="n"/>
-      <c r="G11" s="61" t="n"/>
-      <c r="H11" s="61" t="n"/>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="B11" s="84" t="n"/>
+      <c r="C11" s="84" t="n"/>
+      <c r="D11" s="84" t="n"/>
+      <c r="E11" s="84" t="n"/>
+      <c r="F11" s="84" t="n"/>
+      <c r="G11" s="84" t="n"/>
+      <c r="H11" s="84" t="n"/>
+      <c r="I11" s="83" t="inlineStr">
         <is>
           <t>HD-FILT-001</t>
         </is>
       </c>
-      <c r="J11" s="61" t="n"/>
-      <c r="K11" s="61" t="n"/>
-      <c r="L11" s="61" t="n"/>
-      <c r="M11" s="61" t="n"/>
-      <c r="N11" s="61" t="n"/>
-      <c r="O11" s="61" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="J11" s="84" t="n"/>
+      <c r="K11" s="84" t="n"/>
+      <c r="L11" s="84" t="n"/>
+      <c r="M11" s="84" t="n"/>
+      <c r="N11" s="84" t="n"/>
+      <c r="O11" s="84" t="n"/>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Revisión</t>
         </is>
       </c>
-      <c r="B12" s="61" t="n"/>
-      <c r="C12" s="61" t="n"/>
-      <c r="D12" s="61" t="n"/>
-      <c r="E12" s="61" t="n"/>
-      <c r="F12" s="61" t="n"/>
-      <c r="G12" s="61" t="n"/>
-      <c r="H12" s="61" t="n"/>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="B12" s="84" t="n"/>
+      <c r="C12" s="84" t="n"/>
+      <c r="D12" s="84" t="n"/>
+      <c r="E12" s="84" t="n"/>
+      <c r="F12" s="84" t="n"/>
+      <c r="G12" s="84" t="n"/>
+      <c r="H12" s="84" t="n"/>
+      <c r="I12" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J12" s="61" t="n"/>
-      <c r="K12" s="61" t="n"/>
-      <c r="L12" s="61" t="n"/>
-      <c r="M12" s="61" t="n"/>
-      <c r="N12" s="61" t="n"/>
-      <c r="O12" s="61" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="J12" s="84" t="n"/>
+      <c r="K12" s="84" t="n"/>
+      <c r="L12" s="84" t="n"/>
+      <c r="M12" s="84" t="n"/>
+      <c r="N12" s="84" t="n"/>
+      <c r="O12" s="84" t="n"/>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B13" s="61" t="n"/>
-      <c r="C13" s="61" t="n"/>
-      <c r="D13" s="61" t="n"/>
-      <c r="E13" s="61" t="n"/>
-      <c r="F13" s="61" t="n"/>
-      <c r="G13" s="61" t="n"/>
-      <c r="H13" s="61" t="n"/>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="B13" s="84" t="n"/>
+      <c r="C13" s="84" t="n"/>
+      <c r="D13" s="84" t="n"/>
+      <c r="E13" s="84" t="n"/>
+      <c r="F13" s="84" t="n"/>
+      <c r="G13" s="84" t="n"/>
+      <c r="H13" s="84" t="n"/>
+      <c r="I13" s="83" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="J13" s="61" t="n"/>
-      <c r="K13" s="61" t="n"/>
-      <c r="L13" s="61" t="n"/>
-      <c r="M13" s="61" t="n"/>
-      <c r="N13" s="61" t="n"/>
-      <c r="O13" s="61" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="J13" s="84" t="n"/>
+      <c r="K13" s="84" t="n"/>
+      <c r="L13" s="84" t="n"/>
+      <c r="M13" s="84" t="n"/>
+      <c r="N13" s="84" t="n"/>
+      <c r="O13" s="84" t="n"/>
+    </row>
+    <row r="14" ht="240" customHeight="1">
+      <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B14" s="61" t="n"/>
-      <c r="C14" s="61" t="n"/>
-      <c r="D14" s="61" t="n"/>
-      <c r="E14" s="61" t="n"/>
-      <c r="F14" s="61" t="n"/>
-      <c r="G14" s="61" t="n"/>
-      <c r="H14" s="61" t="n"/>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="B14" s="84" t="n"/>
+      <c r="C14" s="84" t="n"/>
+      <c r="D14" s="84" t="n"/>
+      <c r="E14" s="84" t="n"/>
+      <c r="F14" s="84" t="n"/>
+      <c r="G14" s="84" t="n"/>
+      <c r="H14" s="84" t="n"/>
+      <c r="I14" s="83" t="inlineStr">
         <is>
           <t>P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá</t>
         </is>
       </c>
-      <c r="J14" s="61" t="n"/>
-      <c r="K14" s="61" t="n"/>
-      <c r="L14" s="61" t="n"/>
-      <c r="M14" s="61" t="n"/>
-      <c r="N14" s="61" t="n"/>
-      <c r="O14" s="61" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="J14" s="84" t="n"/>
+      <c r="K14" s="84" t="n"/>
+      <c r="L14" s="84" t="n"/>
+      <c r="M14" s="84" t="n"/>
+      <c r="N14" s="84" t="n"/>
+      <c r="O14" s="84" t="n"/>
+    </row>
+    <row r="15" ht="165" customHeight="1">
+      <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Etiqueta de equipo</t>
         </is>
       </c>
-      <c r="B15" s="61" t="n"/>
-      <c r="C15" s="61" t="n"/>
-      <c r="D15" s="61" t="n"/>
-      <c r="E15" s="61" t="n"/>
-      <c r="F15" s="61" t="n"/>
-      <c r="G15" s="61" t="n"/>
-      <c r="H15" s="61" t="n"/>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="B15" s="84" t="n"/>
+      <c r="C15" s="84" t="n"/>
+      <c r="D15" s="84" t="n"/>
+      <c r="E15" s="84" t="n"/>
+      <c r="F15" s="84" t="n"/>
+      <c r="G15" s="84" t="n"/>
+      <c r="H15" s="84" t="n"/>
+      <c r="I15" s="83" t="inlineStr">
         <is>
           <t>FILT-001 (banco de filtración de la impulsión)</t>
         </is>
       </c>
-      <c r="J15" s="61" t="n"/>
-      <c r="K15" s="61" t="n"/>
-      <c r="L15" s="61" t="n"/>
-      <c r="M15" s="61" t="n"/>
-      <c r="N15" s="61" t="n"/>
-      <c r="O15" s="61" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="62" t="inlineStr">
+      <c r="J15" s="84" t="n"/>
+      <c r="K15" s="84" t="n"/>
+      <c r="L15" s="84" t="n"/>
+      <c r="M15" s="84" t="n"/>
+      <c r="N15" s="84" t="n"/>
+      <c r="O15" s="84" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1"/>
+    <row r="17" ht="15" customHeight="1"/>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="85" t="inlineStr">
         <is>
           <t>1. Servicio</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="63" t="inlineStr">
+    <row r="19" ht="165" customHeight="1">
+      <c r="A19" s="86" t="inlineStr">
         <is>
           <t>1.1. Filtración del aire exterior de impulsión (3 840 m³/h) para exclusión de polvo, insectos y objetos extraños, aguas arriba del laboratorio. No es un servicio de biocontención: no se requiere HEPA. Ambiente exterior corrosivo (atmósfera clorada de planta de hipoclorito de calcio, HR media 84 %).</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="23">
-      <c r="A23" s="62" t="inlineStr">
+    <row r="20" ht="15" customHeight="1"/>
+    <row r="21" ht="15" customHeight="1"/>
+    <row r="22" ht="15" customHeight="1"/>
+    <row r="23" ht="15" customHeight="1"/>
+    <row r="24" ht="15" customHeight="1"/>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="85" t="inlineStr">
         <is>
           <t>2. Especificación de eficiencia</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="64" t="inlineStr">
+    <row r="26" ht="75" customHeight="1">
+      <c r="A26" s="87" t="inlineStr">
         <is>
           <t>Tabla 1. Clases de eficiencia exigidas (consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="59" t="inlineStr">
+    <row r="27" ht="75" customHeight="1">
+      <c r="A27" s="82" t="inlineStr">
         <is>
           <t>Etapa</t>
         </is>
       </c>
-      <c r="B25" s="59" t="n"/>
-      <c r="C25" s="59" t="n"/>
-      <c r="D25" s="59" t="inlineStr">
+      <c r="B27" s="82" t="n"/>
+      <c r="C27" s="82" t="n"/>
+      <c r="D27" s="82" t="inlineStr">
         <is>
           <t>ASHRAE 52.2</t>
         </is>
       </c>
-      <c r="E25" s="59" t="n"/>
-      <c r="F25" s="59" t="n"/>
-      <c r="G25" s="59" t="inlineStr">
+      <c r="E27" s="82" t="n"/>
+      <c r="F27" s="82" t="n"/>
+      <c r="G27" s="82" t="inlineStr">
         <is>
           <t>ISO 16890</t>
         </is>
       </c>
-      <c r="H25" s="59" t="n"/>
-      <c r="I25" s="59" t="n"/>
-      <c r="J25" s="59" t="inlineStr">
+      <c r="H27" s="82" t="n"/>
+      <c r="I27" s="82" t="n"/>
+      <c r="J27" s="82" t="inlineStr">
         <is>
           <t>EN 779:2012 (referencia)</t>
         </is>
       </c>
-      <c r="K25" s="59" t="n"/>
-      <c r="L25" s="59" t="n"/>
-      <c r="M25" s="59" t="inlineStr">
+      <c r="K27" s="82" t="n"/>
+      <c r="L27" s="82" t="n"/>
+      <c r="M27" s="82" t="inlineStr">
         <is>
           <t>Eficiencia mínima por rango</t>
         </is>
       </c>
-      <c r="N25" s="59" t="n"/>
-      <c r="O25" s="59" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="60" t="inlineStr">
+      <c r="N27" s="82" t="n"/>
+      <c r="O27" s="82" t="n"/>
+    </row>
+    <row r="28" ht="135" customHeight="1">
+      <c r="A28" s="83" t="inlineStr">
         <is>
           <t>Etapa 1 (prefiltro)</t>
         </is>
       </c>
-      <c r="B26" s="61" t="n"/>
-      <c r="C26" s="61" t="n"/>
-      <c r="D26" s="60" t="inlineStr">
+      <c r="B28" s="84" t="n"/>
+      <c r="C28" s="84" t="n"/>
+      <c r="D28" s="83" t="inlineStr">
         <is>
           <t>MERV 8</t>
         </is>
       </c>
-      <c r="E26" s="61" t="n"/>
-      <c r="F26" s="61" t="n"/>
-      <c r="G26" s="60" t="inlineStr">
+      <c r="E28" s="84" t="n"/>
+      <c r="F28" s="84" t="n"/>
+      <c r="G28" s="83" t="inlineStr">
         <is>
           <t>ISO Coarse / ePM10 (dato típico de equivalencia)</t>
         </is>
       </c>
-      <c r="H26" s="61" t="n"/>
-      <c r="I26" s="61" t="n"/>
-      <c r="J26" s="60" t="inlineStr">
+      <c r="H28" s="84" t="n"/>
+      <c r="I28" s="84" t="n"/>
+      <c r="J28" s="83" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="K26" s="61" t="n"/>
-      <c r="L26" s="61" t="n"/>
-      <c r="M26" s="60" t="inlineStr">
+      <c r="K28" s="84" t="n"/>
+      <c r="L28" s="84" t="n"/>
+      <c r="M28" s="83" t="inlineStr">
         <is>
           <t>Fracción gruesa: polvo, fibras, insectos</t>
         </is>
       </c>
-      <c r="N26" s="61" t="n"/>
-      <c r="O26" s="61" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="60" t="inlineStr">
+      <c r="N28" s="84" t="n"/>
+      <c r="O28" s="84" t="n"/>
+    </row>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="83" t="inlineStr">
         <is>
           <t>Etapa 2 (filtro final)</t>
         </is>
       </c>
-      <c r="B27" s="61" t="n"/>
-      <c r="C27" s="61" t="n"/>
-      <c r="D27" s="60" t="inlineStr">
+      <c r="B29" s="84" t="n"/>
+      <c r="C29" s="84" t="n"/>
+      <c r="D29" s="83" t="inlineStr">
         <is>
           <t>MERV 13-14</t>
         </is>
       </c>
-      <c r="E27" s="61" t="n"/>
-      <c r="F27" s="61" t="n"/>
-      <c r="G27" s="60" t="inlineStr">
+      <c r="E29" s="84" t="n"/>
+      <c r="F29" s="84" t="n"/>
+      <c r="G29" s="83" t="inlineStr">
         <is>
           <t>ePM1 50-70 %</t>
         </is>
       </c>
-      <c r="H27" s="61" t="n"/>
-      <c r="I27" s="61" t="n"/>
-      <c r="J27" s="60" t="inlineStr">
+      <c r="H29" s="84" t="n"/>
+      <c r="I29" s="84" t="n"/>
+      <c r="J29" s="83" t="inlineStr">
         <is>
           <t>F7-F8</t>
         </is>
       </c>
-      <c r="K27" s="61" t="n"/>
-      <c r="L27" s="61" t="n"/>
-      <c r="M27" s="60" t="inlineStr">
+      <c r="K29" s="84" t="n"/>
+      <c r="L29" s="84" t="n"/>
+      <c r="M29" s="83" t="inlineStr">
         <is>
           <t>MERV 13: E2 ≥ 90 %, E3 ≥ 90 %; MERV 14 añade E1 ≥ 75 %</t>
         </is>
       </c>
-      <c r="N27" s="61" t="n"/>
-      <c r="O27" s="61" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="65" t="inlineStr">
+      <c r="N29" s="84" t="n"/>
+      <c r="O29" s="84" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1"/>
+    <row r="31" ht="150" customHeight="1">
+      <c r="A31" s="88" t="inlineStr">
         <is>
           <t>Fuentes: ANSI/ASHRAE 52.2-2017 (PDF) (https://www.ashrae.org/File%20Library/Technical%20Resources/COVID-19/52_2_2017_COVID-19_20200401.pdf); equivalencias MERV ↔ ePM1 confirmadas en la ficha del fabricante (Camfil Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf): MERV 13 → ePM1 60 %, MERV 14 → ePM1 70 %). Se exige informe de ensayo según la norma citada.</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="63" t="inlineStr">
+    <row r="32" ht="15" customHeight="1"/>
+    <row r="33" ht="15" customHeight="1"/>
+    <row r="34" ht="15" customHeight="1"/>
+    <row r="35" ht="15" customHeight="1"/>
+    <row r="36" ht="15" customHeight="1"/>
+    <row r="37" ht="15" customHeight="1"/>
+    <row r="38" ht="180" customHeight="1">
+      <c r="A38" s="86" t="inlineStr">
         <is>
           <t>2.1. Justificación de la clase: MERV 13-14 garantiza E3 ≥ 90 % (polen, polvo grueso, esporas) y E2 ≥ 90 % (polvo fino), con amplio margen sobre el objetivo funcional. MERV 14 se prefiere sobre MERV 13 por la carga de polvo de la planta de hipoclorito.</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="37">
-      <c r="A37" s="62" t="inlineStr">
+    <row r="39" ht="15" customHeight="1"/>
+    <row r="40" ht="15" customHeight="1"/>
+    <row r="41" ht="15" customHeight="1"/>
+    <row r="42" ht="15" customHeight="1"/>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="85" t="inlineStr">
         <is>
           <t>3. Caídas de presión de diseño</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="64" t="inlineStr">
+    <row r="44" ht="120" customHeight="1">
+      <c r="A44" s="87" t="inlineStr">
         <is>
           <t>Tabla 2. ΔP de la etapa final MERV 13-14 (valores congelados de la memoria de cálculo).</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="59" t="inlineStr">
+    <row r="45" ht="15" customHeight="1"/>
+    <row r="46" ht="105" customHeight="1">
+      <c r="A46" s="82" t="inlineStr">
         <is>
           <t>Condición</t>
         </is>
       </c>
-      <c r="B39" s="59" t="n"/>
-      <c r="C39" s="59" t="n"/>
-      <c r="D39" s="59" t="n"/>
-      <c r="E39" s="59" t="n"/>
-      <c r="F39" s="59" t="inlineStr">
+      <c r="B46" s="82" t="n"/>
+      <c r="C46" s="82" t="n"/>
+      <c r="D46" s="82" t="n"/>
+      <c r="E46" s="82" t="n"/>
+      <c r="F46" s="82" t="inlineStr">
         <is>
           <t>Estándar de catálogo (ρ = 1.2 kg/m³)</t>
         </is>
       </c>
-      <c r="G39" s="59" t="n"/>
-      <c r="H39" s="59" t="n"/>
-      <c r="I39" s="59" t="n"/>
-      <c r="J39" s="59" t="n"/>
-      <c r="K39" s="59" t="inlineStr">
+      <c r="G46" s="82" t="n"/>
+      <c r="H46" s="82" t="n"/>
+      <c r="I46" s="82" t="n"/>
+      <c r="J46" s="82" t="n"/>
+      <c r="K46" s="82" t="inlineStr">
         <is>
           <t>En el sitio (ρ = 0.88 kg/m³, k = 0.733)</t>
         </is>
       </c>
-      <c r="L39" s="59" t="n"/>
-      <c r="M39" s="59" t="n"/>
-      <c r="N39" s="59" t="n"/>
-      <c r="O39" s="59" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="60" t="inlineStr">
+      <c r="L46" s="82" t="n"/>
+      <c r="M46" s="82" t="n"/>
+      <c r="N46" s="82" t="n"/>
+      <c r="O46" s="82" t="n"/>
+    </row>
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" s="83" t="inlineStr">
         <is>
           <t>Filtro limpio</t>
         </is>
       </c>
-      <c r="B40" s="61" t="n"/>
-      <c r="C40" s="61" t="n"/>
-      <c r="D40" s="61" t="n"/>
-      <c r="E40" s="61" t="n"/>
-      <c r="F40" s="60" t="inlineStr">
+      <c r="B47" s="84" t="n"/>
+      <c r="C47" s="84" t="n"/>
+      <c r="D47" s="84" t="n"/>
+      <c r="E47" s="84" t="n"/>
+      <c r="F47" s="83" t="inlineStr">
         <is>
           <t>80 Pa</t>
         </is>
       </c>
-      <c r="G40" s="61" t="n"/>
-      <c r="H40" s="61" t="n"/>
-      <c r="I40" s="61" t="n"/>
-      <c r="J40" s="61" t="n"/>
-      <c r="K40" s="60" t="inlineStr">
+      <c r="G47" s="84" t="n"/>
+      <c r="H47" s="84" t="n"/>
+      <c r="I47" s="84" t="n"/>
+      <c r="J47" s="84" t="n"/>
+      <c r="K47" s="83" t="inlineStr">
         <is>
           <t>59 Pa</t>
         </is>
       </c>
-      <c r="L40" s="61" t="n"/>
-      <c r="M40" s="61" t="n"/>
-      <c r="N40" s="61" t="n"/>
-      <c r="O40" s="61" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="60" t="inlineStr">
+      <c r="L47" s="84" t="n"/>
+      <c r="M47" s="84" t="n"/>
+      <c r="N47" s="84" t="n"/>
+      <c r="O47" s="84" t="n"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="83" t="inlineStr">
         <is>
           <t>Filtro cargado (final de diseño)</t>
         </is>
       </c>
-      <c r="B41" s="61" t="n"/>
-      <c r="C41" s="61" t="n"/>
-      <c r="D41" s="61" t="n"/>
-      <c r="E41" s="61" t="n"/>
-      <c r="F41" s="60" t="inlineStr">
+      <c r="B48" s="84" t="n"/>
+      <c r="C48" s="84" t="n"/>
+      <c r="D48" s="84" t="n"/>
+      <c r="E48" s="84" t="n"/>
+      <c r="F48" s="83" t="inlineStr">
         <is>
           <t>210 Pa</t>
         </is>
       </c>
-      <c r="G41" s="61" t="n"/>
-      <c r="H41" s="61" t="n"/>
-      <c r="I41" s="61" t="n"/>
-      <c r="J41" s="61" t="n"/>
-      <c r="K41" s="60" t="inlineStr">
+      <c r="G48" s="84" t="n"/>
+      <c r="H48" s="84" t="n"/>
+      <c r="I48" s="84" t="n"/>
+      <c r="J48" s="84" t="n"/>
+      <c r="K48" s="83" t="inlineStr">
         <is>
           <t>154 Pa</t>
         </is>
       </c>
-      <c r="L41" s="61" t="n"/>
-      <c r="M41" s="61" t="n"/>
-      <c r="N41" s="61" t="n"/>
-      <c r="O41" s="61" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="63" t="inlineStr">
+      <c r="L48" s="84" t="n"/>
+      <c r="M48" s="84" t="n"/>
+      <c r="N48" s="84" t="n"/>
+      <c r="O48" s="84" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1"/>
+    <row r="50" ht="165" customHeight="1">
+      <c r="A50" s="86" t="inlineStr">
         <is>
           <t>3.1. El ΔP final de diseño de 210 Pa estándar es conservador frente a los límites de catálogo (Camfil: 375 Pa máx. con criterio «cambiar al duplicar ΔP inicial»; AAF: 500 Pa máx.; clase F de EN 779: 450 Pa recomendados — fuentes en Tabla 4), lo que alarga la vida útil real del elemento. El prefiltro MERV 8 aporta 50-75 Pa limpio y 250 Pa final (catálogo; Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf), consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="63" t="inlineStr">
+    <row r="51" ht="15" customHeight="1"/>
+    <row r="52" ht="15" customHeight="1"/>
+    <row r="53" ht="15" customHeight="1"/>
+    <row r="54" ht="15" customHeight="1"/>
+    <row r="55" ht="15" customHeight="1"/>
+    <row r="56" ht="15" customHeight="1"/>
+    <row r="57" ht="15" customHeight="1"/>
+    <row r="58" ht="150" customHeight="1">
+      <c r="A58" s="86" t="inlineStr">
         <is>
           <t>3.2. Velocidad frontal: con un módulo 24×24 in (610×610 mm) a 3 840 m³/h resulta ≈2.87 m/s (565 fpm), ligeramente superior al punto de catálogo de 500 fpm (2.54 m/s); el ΔP real será ~13-15 % superior al tabulado (dato típico, escalado aproximadamente cuadrático), efecto parcialmente compensado por la corrección de densidad del sitio. Verificar con la curva del fabricante seleccionado.</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="52">
-      <c r="A52" s="62" t="inlineStr">
+    <row r="59" ht="15" customHeight="1"/>
+    <row r="60" ht="15" customHeight="1"/>
+    <row r="61" ht="15" customHeight="1"/>
+    <row r="62" ht="15" customHeight="1"/>
+    <row r="63" ht="15" customHeight="1"/>
+    <row r="64" ht="15" customHeight="1"/>
+    <row r="65" ht="15" customHeight="1"/>
+    <row r="66" ht="90" customHeight="1">
+      <c r="A66" s="85" t="inlineStr">
         <is>
           <t>4. Dimensiones y construcción</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="64" t="inlineStr">
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="87" t="inlineStr">
         <is>
           <t>Tabla 3. Requisitos de construcción.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="59" t="inlineStr">
+    <row r="68" ht="45" customHeight="1">
+      <c r="A68" s="82" t="inlineStr">
         <is>
           <t>Característica</t>
         </is>
       </c>
-      <c r="B54" s="59" t="n"/>
-      <c r="C54" s="59" t="n"/>
-      <c r="D54" s="59" t="n"/>
-      <c r="E54" s="59" t="n"/>
-      <c r="F54" s="59" t="n"/>
-      <c r="G54" s="59" t="n"/>
-      <c r="H54" s="59" t="n"/>
-      <c r="I54" s="59" t="inlineStr">
+      <c r="B68" s="82" t="n"/>
+      <c r="C68" s="82" t="n"/>
+      <c r="D68" s="82" t="n"/>
+      <c r="E68" s="82" t="n"/>
+      <c r="F68" s="82" t="n"/>
+      <c r="G68" s="82" t="n"/>
+      <c r="H68" s="82" t="n"/>
+      <c r="I68" s="82" t="inlineStr">
         <is>
           <t>Especificación</t>
         </is>
       </c>
-      <c r="J54" s="59" t="n"/>
-      <c r="K54" s="59" t="n"/>
-      <c r="L54" s="59" t="n"/>
-      <c r="M54" s="59" t="n"/>
-      <c r="N54" s="59" t="n"/>
-      <c r="O54" s="59" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="60" t="inlineStr">
+      <c r="J68" s="82" t="n"/>
+      <c r="K68" s="82" t="n"/>
+      <c r="L68" s="82" t="n"/>
+      <c r="M68" s="82" t="n"/>
+      <c r="N68" s="82" t="n"/>
+      <c r="O68" s="82" t="n"/>
+    </row>
+    <row r="69" ht="240" customHeight="1">
+      <c r="A69" s="83" t="inlineStr">
         <is>
           <t>Dimensiones</t>
         </is>
       </c>
-      <c r="B55" s="61" t="n"/>
-      <c r="C55" s="61" t="n"/>
-      <c r="D55" s="61" t="n"/>
-      <c r="E55" s="61" t="n"/>
-      <c r="F55" s="61" t="n"/>
-      <c r="G55" s="61" t="n"/>
-      <c r="H55" s="61" t="n"/>
-      <c r="I55" s="60" t="inlineStr">
+      <c r="B69" s="84" t="n"/>
+      <c r="C69" s="84" t="n"/>
+      <c r="D69" s="84" t="n"/>
+      <c r="E69" s="84" t="n"/>
+      <c r="F69" s="84" t="n"/>
+      <c r="G69" s="84" t="n"/>
+      <c r="H69" s="84" t="n"/>
+      <c r="I69" s="83" t="inlineStr">
         <is>
           <t>Módulo pleno 24×24 in (610×610 mm); profundidad según línea V-bank (292 mm dato típico)</t>
         </is>
       </c>
-      <c r="J55" s="61" t="n"/>
-      <c r="K55" s="61" t="n"/>
-      <c r="L55" s="61" t="n"/>
-      <c r="M55" s="61" t="n"/>
-      <c r="N55" s="61" t="n"/>
-      <c r="O55" s="61" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="60" t="inlineStr">
+      <c r="J69" s="84" t="n"/>
+      <c r="K69" s="84" t="n"/>
+      <c r="L69" s="84" t="n"/>
+      <c r="M69" s="84" t="n"/>
+      <c r="N69" s="84" t="n"/>
+      <c r="O69" s="84" t="n"/>
+    </row>
+    <row r="70" ht="105" customHeight="1">
+      <c r="A70" s="83" t="inlineStr">
         <is>
           <t>Tipo etapa final</t>
         </is>
       </c>
-      <c r="B56" s="61" t="n"/>
-      <c r="C56" s="61" t="n"/>
-      <c r="D56" s="61" t="n"/>
-      <c r="E56" s="61" t="n"/>
-      <c r="F56" s="61" t="n"/>
-      <c r="G56" s="61" t="n"/>
-      <c r="H56" s="61" t="n"/>
-      <c r="I56" s="60" t="inlineStr">
+      <c r="B70" s="84" t="n"/>
+      <c r="C70" s="84" t="n"/>
+      <c r="D70" s="84" t="n"/>
+      <c r="E70" s="84" t="n"/>
+      <c r="F70" s="84" t="n"/>
+      <c r="G70" s="84" t="n"/>
+      <c r="H70" s="84" t="n"/>
+      <c r="I70" s="83" t="inlineStr">
         <is>
           <t>V-bank / casete compacto de minipleat</t>
         </is>
       </c>
-      <c r="J56" s="61" t="n"/>
-      <c r="K56" s="61" t="n"/>
-      <c r="L56" s="61" t="n"/>
-      <c r="M56" s="61" t="n"/>
-      <c r="N56" s="61" t="n"/>
-      <c r="O56" s="61" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="60" t="inlineStr">
+      <c r="J70" s="84" t="n"/>
+      <c r="K70" s="84" t="n"/>
+      <c r="L70" s="84" t="n"/>
+      <c r="M70" s="84" t="n"/>
+      <c r="N70" s="84" t="n"/>
+      <c r="O70" s="84" t="n"/>
+    </row>
+    <row r="71" ht="270" customHeight="1">
+      <c r="A71" s="83" t="inlineStr">
         <is>
           <t>Marco del filtro</t>
         </is>
       </c>
-      <c r="B57" s="61" t="n"/>
-      <c r="C57" s="61" t="n"/>
-      <c r="D57" s="61" t="n"/>
-      <c r="E57" s="61" t="n"/>
-      <c r="F57" s="61" t="n"/>
-      <c r="G57" s="61" t="n"/>
-      <c r="H57" s="61" t="n"/>
-      <c r="I57" s="60" t="inlineStr">
+      <c r="B71" s="84" t="n"/>
+      <c r="C71" s="84" t="n"/>
+      <c r="D71" s="84" t="n"/>
+      <c r="E71" s="84" t="n"/>
+      <c r="F71" s="84" t="n"/>
+      <c r="G71" s="84" t="n"/>
+      <c r="H71" s="84" t="n"/>
+      <c r="I71" s="83" t="inlineStr">
         <is>
           <t>100 % plástico (ABS/poliestireno/HIPS), sin componentes metálicos; paquete sellado con poliuretano</t>
         </is>
       </c>
-      <c r="J57" s="61" t="n"/>
-      <c r="K57" s="61" t="n"/>
-      <c r="L57" s="61" t="n"/>
-      <c r="M57" s="61" t="n"/>
-      <c r="N57" s="61" t="n"/>
-      <c r="O57" s="61" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="60" t="inlineStr">
+      <c r="J71" s="84" t="n"/>
+      <c r="K71" s="84" t="n"/>
+      <c r="L71" s="84" t="n"/>
+      <c r="M71" s="84" t="n"/>
+      <c r="N71" s="84" t="n"/>
+      <c r="O71" s="84" t="n"/>
+    </row>
+    <row r="72" ht="105" customHeight="1">
+      <c r="A72" s="83" t="inlineStr">
         <is>
           <t>Junta</t>
         </is>
       </c>
-      <c r="B58" s="61" t="n"/>
-      <c r="C58" s="61" t="n"/>
-      <c r="D58" s="61" t="n"/>
-      <c r="E58" s="61" t="n"/>
-      <c r="F58" s="61" t="n"/>
-      <c r="G58" s="61" t="n"/>
-      <c r="H58" s="61" t="n"/>
-      <c r="I58" s="60" t="inlineStr">
+      <c r="B72" s="84" t="n"/>
+      <c r="C72" s="84" t="n"/>
+      <c r="D72" s="84" t="n"/>
+      <c r="E72" s="84" t="n"/>
+      <c r="F72" s="84" t="n"/>
+      <c r="G72" s="84" t="n"/>
+      <c r="H72" s="84" t="n"/>
+      <c r="I72" s="83" t="inlineStr">
         <is>
           <t>Poliuretano o EPDM continua, en cabezal</t>
         </is>
       </c>
-      <c r="J58" s="61" t="n"/>
-      <c r="K58" s="61" t="n"/>
-      <c r="L58" s="61" t="n"/>
-      <c r="M58" s="61" t="n"/>
-      <c r="N58" s="61" t="n"/>
-      <c r="O58" s="61" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="60" t="inlineStr">
+      <c r="J72" s="84" t="n"/>
+      <c r="K72" s="84" t="n"/>
+      <c r="L72" s="84" t="n"/>
+      <c r="M72" s="84" t="n"/>
+      <c r="N72" s="84" t="n"/>
+      <c r="O72" s="84" t="n"/>
+    </row>
+    <row r="73" ht="255" customHeight="1">
+      <c r="A73" s="83" t="inlineStr">
         <is>
           <t>Portafiltros (holding frames)</t>
         </is>
       </c>
-      <c r="B59" s="61" t="n"/>
-      <c r="C59" s="61" t="n"/>
-      <c r="D59" s="61" t="n"/>
-      <c r="E59" s="61" t="n"/>
-      <c r="F59" s="61" t="n"/>
-      <c r="G59" s="61" t="n"/>
-      <c r="H59" s="61" t="n"/>
-      <c r="I59" s="60" t="inlineStr">
+      <c r="B73" s="84" t="n"/>
+      <c r="C73" s="84" t="n"/>
+      <c r="D73" s="84" t="n"/>
+      <c r="E73" s="84" t="n"/>
+      <c r="F73" s="84" t="n"/>
+      <c r="G73" s="84" t="n"/>
+      <c r="H73" s="84" t="n"/>
+      <c r="I73" s="83" t="inlineStr">
         <is>
           <t>Inox 304/316 con junta continua de poliuretano; galvanizado descartado por el ambiente clorado</t>
         </is>
       </c>
-      <c r="J59" s="61" t="n"/>
-      <c r="K59" s="61" t="n"/>
-      <c r="L59" s="61" t="n"/>
-      <c r="M59" s="61" t="n"/>
-      <c r="N59" s="61" t="n"/>
-      <c r="O59" s="61" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="60" t="inlineStr">
+      <c r="J73" s="84" t="n"/>
+      <c r="K73" s="84" t="n"/>
+      <c r="L73" s="84" t="n"/>
+      <c r="M73" s="84" t="n"/>
+      <c r="N73" s="84" t="n"/>
+      <c r="O73" s="84" t="n"/>
+    </row>
+    <row r="74" ht="255" customHeight="1">
+      <c r="A74" s="83" t="inlineStr">
         <is>
           <t>Fijación prefiltro</t>
         </is>
       </c>
-      <c r="B60" s="61" t="n"/>
-      <c r="C60" s="61" t="n"/>
-      <c r="D60" s="61" t="n"/>
-      <c r="E60" s="61" t="n"/>
-      <c r="F60" s="61" t="n"/>
-      <c r="G60" s="61" t="n"/>
-      <c r="H60" s="61" t="n"/>
-      <c r="I60" s="60" t="inlineStr">
+      <c r="B74" s="84" t="n"/>
+      <c r="C74" s="84" t="n"/>
+      <c r="D74" s="84" t="n"/>
+      <c r="E74" s="84" t="n"/>
+      <c r="F74" s="84" t="n"/>
+      <c r="G74" s="84" t="n"/>
+      <c r="H74" s="84" t="n"/>
+      <c r="I74" s="83" t="inlineStr">
         <is>
           <t>Espaciador/clip frontal integrado al filtro final (configuración estándar de los candidatos)</t>
         </is>
       </c>
-      <c r="J60" s="61" t="n"/>
-      <c r="K60" s="61" t="n"/>
-      <c r="L60" s="61" t="n"/>
-      <c r="M60" s="61" t="n"/>
-      <c r="N60" s="61" t="n"/>
-      <c r="O60" s="61" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="60" t="inlineStr">
+      <c r="J74" s="84" t="n"/>
+      <c r="K74" s="84" t="n"/>
+      <c r="L74" s="84" t="n"/>
+      <c r="M74" s="84" t="n"/>
+      <c r="N74" s="84" t="n"/>
+      <c r="O74" s="84" t="n"/>
+    </row>
+    <row r="75" ht="315" customHeight="1">
+      <c r="A75" s="83" t="inlineStr">
         <is>
           <t>Marco del prefiltro</t>
         </is>
       </c>
-      <c r="B61" s="61" t="n"/>
-      <c r="C61" s="61" t="n"/>
-      <c r="D61" s="61" t="n"/>
-      <c r="E61" s="61" t="n"/>
-      <c r="F61" s="61" t="n"/>
-      <c r="G61" s="61" t="n"/>
-      <c r="H61" s="61" t="n"/>
-      <c r="I61" s="60" t="inlineStr">
+      <c r="B75" s="84" t="n"/>
+      <c r="C75" s="84" t="n"/>
+      <c r="D75" s="84" t="n"/>
+      <c r="E75" s="84" t="n"/>
+      <c r="F75" s="84" t="n"/>
+      <c r="G75" s="84" t="n"/>
+      <c r="H75" s="84" t="n"/>
+      <c r="I75" s="83" t="inlineStr">
         <is>
           <t>Cartón hidrófugo; la rejilla soporte galvanizada se acepta con inspección de corrosión programada en el primer año</t>
         </is>
       </c>
-      <c r="J61" s="61" t="n"/>
-      <c r="K61" s="61" t="n"/>
-      <c r="L61" s="61" t="n"/>
-      <c r="M61" s="61" t="n"/>
-      <c r="N61" s="61" t="n"/>
-      <c r="O61" s="61" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="62" t="inlineStr">
+      <c r="J75" s="84" t="n"/>
+      <c r="K75" s="84" t="n"/>
+      <c r="L75" s="84" t="n"/>
+      <c r="M75" s="84" t="n"/>
+      <c r="N75" s="84" t="n"/>
+      <c r="O75" s="84" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1"/>
+    <row r="77" ht="15" customHeight="1"/>
+    <row r="78" ht="75" customHeight="1">
+      <c r="A78" s="85" t="inlineStr">
         <is>
           <t>5. Candidatos comerciales</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="64" t="inlineStr">
+    <row r="79" ht="105" customHeight="1">
+      <c r="A79" s="87" t="inlineStr">
         <is>
           <t>Tabla 4. Filtros finales candidatos (500 fpm = 2.54 m/s; consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="59" t="inlineStr">
+    <row r="80" ht="15" customHeight="1"/>
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" s="82" t="inlineStr">
         <is>
           <t>Fabricante / modelo</t>
         </is>
       </c>
-      <c r="B66" s="59" t="n"/>
-      <c r="C66" s="59" t="n"/>
-      <c r="D66" s="59" t="inlineStr">
+      <c r="B81" s="82" t="n"/>
+      <c r="C81" s="82" t="n"/>
+      <c r="D81" s="82" t="inlineStr">
         <is>
           <t>Clase</t>
         </is>
       </c>
-      <c r="E66" s="59" t="n"/>
-      <c r="F66" s="59" t="n"/>
-      <c r="G66" s="59" t="inlineStr">
+      <c r="E81" s="82" t="n"/>
+      <c r="F81" s="82" t="n"/>
+      <c r="G81" s="82" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="H66" s="59" t="n"/>
-      <c r="I66" s="59" t="n"/>
-      <c r="J66" s="59" t="inlineStr">
+      <c r="H81" s="82" t="n"/>
+      <c r="I81" s="82" t="n"/>
+      <c r="J81" s="82" t="inlineStr">
         <is>
           <t>ΔP inicial catálogo</t>
         </is>
       </c>
-      <c r="K66" s="59" t="n"/>
-      <c r="L66" s="59" t="inlineStr">
+      <c r="K81" s="82" t="n"/>
+      <c r="L81" s="82" t="inlineStr">
         <is>
           <t>ΔP final máx.</t>
         </is>
       </c>
-      <c r="M66" s="59" t="n"/>
-      <c r="N66" s="59" t="inlineStr">
+      <c r="M81" s="82" t="n"/>
+      <c r="N81" s="82" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="O66" s="59" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="60" t="inlineStr">
+      <c r="O81" s="82" t="n"/>
+    </row>
+    <row r="82" ht="210" customHeight="1">
+      <c r="A82" s="83" t="inlineStr">
         <is>
           <t>Camfil Durafil ES2 (referencia de diseño)</t>
         </is>
       </c>
-      <c r="B67" s="61" t="n"/>
-      <c r="C67" s="61" t="n"/>
-      <c r="D67" s="60" t="inlineStr">
+      <c r="B82" s="84" t="n"/>
+      <c r="C82" s="84" t="n"/>
+      <c r="D82" s="83" t="inlineStr">
         <is>
           <t>MERV 14 / ePM1 70</t>
         </is>
       </c>
-      <c r="E67" s="61" t="n"/>
-      <c r="F67" s="61" t="n"/>
-      <c r="G67" s="60" t="inlineStr">
+      <c r="E82" s="84" t="n"/>
+      <c r="F82" s="84" t="n"/>
+      <c r="G82" s="83" t="inlineStr">
         <is>
           <t>Plástico ABS/poliestireno</t>
         </is>
       </c>
-      <c r="H67" s="61" t="n"/>
-      <c r="I67" s="61" t="n"/>
-      <c r="J67" s="60" t="inlineStr">
+      <c r="H82" s="84" t="n"/>
+      <c r="I82" s="84" t="n"/>
+      <c r="J82" s="83" t="inlineStr">
         <is>
           <t>≤ 0.32 in c.a. ≈ 80 Pa</t>
         </is>
       </c>
-      <c r="K67" s="61" t="n"/>
-      <c r="L67" s="60" t="inlineStr">
+      <c r="K82" s="84" t="n"/>
+      <c r="L82" s="83" t="inlineStr">
         <is>
           <t>375 Pa</t>
         </is>
       </c>
-      <c r="M67" s="61" t="n"/>
-      <c r="N67" s="60" t="inlineStr">
+      <c r="M82" s="84" t="n"/>
+      <c r="N82" s="83" t="inlineStr">
         <is>
           <t>Ficha (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf)</t>
         </is>
       </c>
-      <c r="O67" s="61" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="60" t="inlineStr">
+      <c r="O82" s="84" t="n"/>
+    </row>
+    <row r="83" ht="465" customHeight="1">
+      <c r="A83" s="83" t="inlineStr">
         <is>
           <t>AAF VariCel VXL</t>
         </is>
       </c>
-      <c r="B68" s="61" t="n"/>
-      <c r="C68" s="61" t="n"/>
-      <c r="D68" s="60" t="inlineStr">
+      <c r="B83" s="84" t="n"/>
+      <c r="C83" s="84" t="n"/>
+      <c r="D83" s="83" t="inlineStr">
         <is>
           <t>MERV 14</t>
         </is>
       </c>
-      <c r="E68" s="61" t="n"/>
-      <c r="F68" s="61" t="n"/>
-      <c r="G68" s="60" t="inlineStr">
+      <c r="E83" s="84" t="n"/>
+      <c r="F83" s="84" t="n"/>
+      <c r="G83" s="83" t="inlineStr">
         <is>
           <t>Plástico HIPS + ABS, sin metal</t>
         </is>
       </c>
-      <c r="H68" s="61" t="n"/>
-      <c r="I68" s="61" t="n"/>
-      <c r="J68" s="60" t="inlineStr">
+      <c r="H83" s="84" t="n"/>
+      <c r="I83" s="84" t="n"/>
+      <c r="J83" s="83" t="inlineStr">
         <is>
           <t>≈ 100-112 Pa (dato típico, de curva)</t>
         </is>
       </c>
-      <c r="K68" s="61" t="n"/>
-      <c r="L68" s="60" t="inlineStr">
+      <c r="K83" s="84" t="n"/>
+      <c r="L83" s="83" t="inlineStr">
         <is>
           <t>500 Pa</t>
         </is>
       </c>
-      <c r="M68" s="61" t="n"/>
-      <c r="N68" s="60" t="inlineStr">
+      <c r="M83" s="84" t="n"/>
+      <c r="N83" s="83" t="inlineStr">
         <is>
           <t>AAF AFP-1-162 (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
         </is>
       </c>
-      <c r="O68" s="61" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="60" t="inlineStr">
+      <c r="O83" s="84" t="n"/>
+    </row>
+    <row r="84" ht="255" customHeight="1">
+      <c r="A84" s="83" t="inlineStr">
         <is>
           <t>Freudenberg Viledon MaxiPleat MX 85</t>
         </is>
       </c>
-      <c r="B69" s="61" t="n"/>
-      <c r="C69" s="61" t="n"/>
-      <c r="D69" s="60" t="inlineStr">
+      <c r="B84" s="84" t="n"/>
+      <c r="C84" s="84" t="n"/>
+      <c r="D84" s="83" t="inlineStr">
         <is>
           <t>F8 / ePM1 65 % (≈ MERV 14)</t>
         </is>
       </c>
-      <c r="E69" s="61" t="n"/>
-      <c r="F69" s="61" t="n"/>
-      <c r="G69" s="60" t="inlineStr">
+      <c r="E84" s="84" t="n"/>
+      <c r="F84" s="84" t="n"/>
+      <c r="G84" s="83" t="inlineStr">
         <is>
           <t>Plástico, paquete fundido estanco</t>
         </is>
       </c>
-      <c r="H69" s="61" t="n"/>
-      <c r="I69" s="61" t="n"/>
-      <c r="J69" s="60" t="inlineStr">
+      <c r="H84" s="84" t="n"/>
+      <c r="I84" s="84" t="n"/>
+      <c r="J84" s="83" t="inlineStr">
         <is>
           <t>135-180 Pa (familia)</t>
         </is>
       </c>
-      <c r="K69" s="61" t="n"/>
-      <c r="L69" s="60" t="inlineStr">
+      <c r="K84" s="84" t="n"/>
+      <c r="L84" s="83" t="inlineStr">
         <is>
           <t>≈ 450 Pa (dato típico)</t>
         </is>
       </c>
-      <c r="M69" s="61" t="n"/>
-      <c r="N69" s="60" t="inlineStr">
+      <c r="M84" s="84" t="n"/>
+      <c r="N84" s="83" t="inlineStr">
         <is>
           <t>Ficha (PDF) (https://menardifilters.se/wp-content/uploads/MaxiPleat_DS_02-CC-038-EN_low.pdf)</t>
         </is>
       </c>
-      <c r="O69" s="61" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="60" t="inlineStr">
+      <c r="O84" s="84" t="n"/>
+    </row>
+    <row r="85" ht="270" customHeight="1">
+      <c r="A85" s="83" t="inlineStr">
         <is>
           <t>Koch Multi-Pleat Green13</t>
         </is>
       </c>
-      <c r="B70" s="61" t="n"/>
-      <c r="C70" s="61" t="n"/>
-      <c r="D70" s="60" t="inlineStr">
+      <c r="B85" s="84" t="n"/>
+      <c r="C85" s="84" t="n"/>
+      <c r="D85" s="83" t="inlineStr">
         <is>
           <t>MERV 13</t>
         </is>
       </c>
-      <c r="E70" s="61" t="n"/>
-      <c r="F70" s="61" t="n"/>
-      <c r="G70" s="60" t="inlineStr">
+      <c r="E85" s="84" t="n"/>
+      <c r="F85" s="84" t="n"/>
+      <c r="G85" s="83" t="inlineStr">
         <is>
           <t>Cartón + rejilla galvanizada</t>
         </is>
       </c>
-      <c r="H70" s="61" t="n"/>
-      <c r="I70" s="61" t="n"/>
-      <c r="J70" s="60" t="inlineStr">
+      <c r="H85" s="84" t="n"/>
+      <c r="I85" s="84" t="n"/>
+      <c r="J85" s="83" t="inlineStr">
         <is>
           <t>≈ 75-100 Pa (dato típico plisados MERV 13)</t>
         </is>
       </c>
-      <c r="K70" s="61" t="n"/>
-      <c r="L70" s="60" t="inlineStr">
+      <c r="K85" s="84" t="n"/>
+      <c r="L85" s="83" t="inlineStr">
         <is>
           <t>≈ 250 Pa (dato típico)</t>
         </is>
       </c>
-      <c r="M70" s="61" t="n"/>
-      <c r="N70" s="60" t="inlineStr">
+      <c r="M85" s="84" t="n"/>
+      <c r="N85" s="83" t="inlineStr">
         <is>
           <t>Ficha (PDF) (https://www.airfilterplus.com/wp-content/uploads/2022/03/Multi-Pleat-Green-13-2021.pdf)</t>
         </is>
       </c>
-      <c r="O70" s="61" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="64" t="inlineStr">
+      <c r="O85" s="84" t="n"/>
+    </row>
+    <row r="86" ht="15" customHeight="1"/>
+    <row r="87" ht="105" customHeight="1">
+      <c r="A87" s="87" t="inlineStr">
         <is>
           <t>Tabla 5. Prefiltros candidatos y portafiltros (consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="59" t="inlineStr">
+    <row r="88" ht="15" customHeight="1"/>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="82" t="inlineStr">
         <is>
           <t>Ítem</t>
         </is>
       </c>
-      <c r="B73" s="59" t="n"/>
-      <c r="C73" s="59" t="n"/>
-      <c r="D73" s="59" t="n"/>
-      <c r="E73" s="59" t="inlineStr">
+      <c r="B89" s="82" t="n"/>
+      <c r="C89" s="82" t="n"/>
+      <c r="D89" s="82" t="n"/>
+      <c r="E89" s="82" t="inlineStr">
         <is>
           <t>Candidato</t>
         </is>
       </c>
-      <c r="F73" s="59" t="n"/>
-      <c r="G73" s="59" t="n"/>
-      <c r="H73" s="59" t="n"/>
-      <c r="I73" s="59" t="inlineStr">
+      <c r="F89" s="82" t="n"/>
+      <c r="G89" s="82" t="n"/>
+      <c r="H89" s="82" t="n"/>
+      <c r="I89" s="82" t="inlineStr">
         <is>
           <t>Dato clave</t>
         </is>
       </c>
-      <c r="J73" s="59" t="n"/>
-      <c r="K73" s="59" t="n"/>
-      <c r="L73" s="59" t="n"/>
-      <c r="M73" s="59" t="inlineStr">
+      <c r="J89" s="82" t="n"/>
+      <c r="K89" s="82" t="n"/>
+      <c r="L89" s="82" t="n"/>
+      <c r="M89" s="82" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N73" s="59" t="n"/>
-      <c r="O73" s="59" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="60" t="inlineStr">
+      <c r="N89" s="82" t="n"/>
+      <c r="O89" s="82" t="n"/>
+    </row>
+    <row r="90" ht="210" customHeight="1">
+      <c r="A90" s="83" t="inlineStr">
         <is>
           <t>Prefiltro MERV 8</t>
         </is>
       </c>
-      <c r="B74" s="61" t="n"/>
-      <c r="C74" s="61" t="n"/>
-      <c r="D74" s="61" t="n"/>
-      <c r="E74" s="60" t="inlineStr">
+      <c r="B90" s="84" t="n"/>
+      <c r="C90" s="84" t="n"/>
+      <c r="D90" s="84" t="n"/>
+      <c r="E90" s="83" t="inlineStr">
         <is>
           <t>Camfil 30/30 / Dual 9</t>
         </is>
       </c>
-      <c r="F74" s="61" t="n"/>
-      <c r="G74" s="61" t="n"/>
-      <c r="H74" s="61" t="n"/>
-      <c r="I74" s="60" t="inlineStr">
+      <c r="F90" s="84" t="n"/>
+      <c r="G90" s="84" t="n"/>
+      <c r="H90" s="84" t="n"/>
+      <c r="I90" s="83" t="inlineStr">
         <is>
           <t>ΔP inicial ≤ 67-75 Pa @ 500 fpm</t>
         </is>
       </c>
-      <c r="J74" s="61" t="n"/>
-      <c r="K74" s="61" t="n"/>
-      <c r="L74" s="61" t="n"/>
-      <c r="M74" s="60" t="inlineStr">
+      <c r="J90" s="84" t="n"/>
+      <c r="K90" s="84" t="n"/>
+      <c r="L90" s="84" t="n"/>
+      <c r="M90" s="83" t="inlineStr">
         <is>
           <t>Ficha (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf)</t>
         </is>
       </c>
-      <c r="N74" s="61" t="n"/>
-      <c r="O74" s="61" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="60" t="inlineStr">
+      <c r="N90" s="84" t="n"/>
+      <c r="O90" s="84" t="n"/>
+    </row>
+    <row r="91" ht="225" customHeight="1">
+      <c r="A91" s="83" t="inlineStr">
         <is>
           <t>Prefiltro MERV 8</t>
         </is>
       </c>
-      <c r="B75" s="61" t="n"/>
-      <c r="C75" s="61" t="n"/>
-      <c r="D75" s="61" t="n"/>
-      <c r="E75" s="60" t="inlineStr">
+      <c r="B91" s="84" t="n"/>
+      <c r="C91" s="84" t="n"/>
+      <c r="D91" s="84" t="n"/>
+      <c r="E91" s="83" t="inlineStr">
         <is>
           <t>Koch Multi-Pleat XL8</t>
         </is>
       </c>
-      <c r="F75" s="61" t="n"/>
-      <c r="G75" s="61" t="n"/>
-      <c r="H75" s="61" t="n"/>
-      <c r="I75" s="60" t="inlineStr">
+      <c r="F91" s="84" t="n"/>
+      <c r="G91" s="84" t="n"/>
+      <c r="H91" s="84" t="n"/>
+      <c r="I91" s="83" t="inlineStr">
         <is>
           <t>ΔP inicial ~50-62 Pa (dato típico, de curva)</t>
         </is>
       </c>
-      <c r="J75" s="61" t="n"/>
-      <c r="K75" s="61" t="n"/>
-      <c r="L75" s="61" t="n"/>
-      <c r="M75" s="60" t="inlineStr">
+      <c r="J91" s="84" t="n"/>
+      <c r="K91" s="84" t="n"/>
+      <c r="L91" s="84" t="n"/>
+      <c r="M91" s="83" t="inlineStr">
         <is>
           <t>Ficha (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
         </is>
       </c>
-      <c r="N75" s="61" t="n"/>
-      <c r="O75" s="61" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="60" t="inlineStr">
+      <c r="N91" s="84" t="n"/>
+      <c r="O91" s="84" t="n"/>
+    </row>
+    <row r="92" ht="405" customHeight="1">
+      <c r="A92" s="83" t="inlineStr">
         <is>
           <t>Portafiltros</t>
         </is>
       </c>
-      <c r="B76" s="61" t="n"/>
-      <c r="C76" s="61" t="n"/>
-      <c r="D76" s="61" t="n"/>
-      <c r="E76" s="60" t="inlineStr">
+      <c r="B92" s="84" t="n"/>
+      <c r="C92" s="84" t="n"/>
+      <c r="D92" s="84" t="n"/>
+      <c r="E92" s="83" t="inlineStr">
         <is>
           <t>Camfil MagnaFrame II</t>
         </is>
       </c>
-      <c r="F76" s="61" t="n"/>
-      <c r="G76" s="61" t="n"/>
-      <c r="H76" s="61" t="n"/>
-      <c r="I76" s="60" t="inlineStr">
+      <c r="F92" s="84" t="n"/>
+      <c r="G92" s="84" t="n"/>
+      <c r="H92" s="84" t="n"/>
+      <c r="I92" s="83" t="inlineStr">
         <is>
           <t>Galvanizado 14 ga, opción inox 304; junta PU</t>
         </is>
       </c>
-      <c r="J76" s="61" t="n"/>
-      <c r="K76" s="61" t="n"/>
-      <c r="L76" s="61" t="n"/>
-      <c r="M76" s="60" t="inlineStr">
+      <c r="J92" s="84" t="n"/>
+      <c r="K92" s="84" t="n"/>
+      <c r="L92" s="84" t="n"/>
+      <c r="M92" s="83" t="inlineStr">
         <is>
           <t>Camfil (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
         </is>
       </c>
-      <c r="N76" s="61" t="n"/>
-      <c r="O76" s="61" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="60" t="inlineStr">
+      <c r="N92" s="84" t="n"/>
+      <c r="O92" s="84" t="n"/>
+    </row>
+    <row r="93" ht="420" customHeight="1">
+      <c r="A93" s="83" t="inlineStr">
         <is>
           <t>Portafiltros</t>
         </is>
       </c>
-      <c r="B77" s="61" t="n"/>
-      <c r="C77" s="61" t="n"/>
-      <c r="D77" s="61" t="n"/>
-      <c r="E77" s="60" t="inlineStr">
+      <c r="B93" s="84" t="n"/>
+      <c r="C93" s="84" t="n"/>
+      <c r="D93" s="84" t="n"/>
+      <c r="E93" s="83" t="inlineStr">
         <is>
           <t>Camfil Universal Holding Frame</t>
         </is>
       </c>
-      <c r="F77" s="61" t="n"/>
-      <c r="G77" s="61" t="n"/>
-      <c r="H77" s="61" t="n"/>
-      <c r="I77" s="60" t="inlineStr">
+      <c r="F93" s="84" t="n"/>
+      <c r="G93" s="84" t="n"/>
+      <c r="H93" s="84" t="n"/>
+      <c r="I93" s="83" t="inlineStr">
         <is>
           <t>Disponible inox o galvanizado; junta PU continua opcional</t>
         </is>
       </c>
-      <c r="J77" s="61" t="n"/>
-      <c r="K77" s="61" t="n"/>
-      <c r="L77" s="61" t="n"/>
-      <c r="M77" s="60" t="inlineStr">
+      <c r="J93" s="84" t="n"/>
+      <c r="K93" s="84" t="n"/>
+      <c r="L93" s="84" t="n"/>
+      <c r="M93" s="83" t="inlineStr">
         <is>
           <t>Camfil (https://www.camfil.com/en-sg/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/universal-filter-holding-frame-_-46512)</t>
         </is>
       </c>
-      <c r="N77" s="61" t="n"/>
-      <c r="O77" s="61" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="62" t="inlineStr">
+      <c r="N93" s="84" t="n"/>
+      <c r="O93" s="84" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1"/>
+    <row r="95" ht="15" customHeight="1"/>
+    <row r="96" ht="105" customHeight="1">
+      <c r="A96" s="85" t="inlineStr">
         <is>
           <t>6. Suministro y repuestos (Colombia)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="63" t="inlineStr">
+    <row r="97" ht="165" customHeight="1">
+      <c r="A97" s="86" t="inlineStr">
         <is>
           <t>6.1. Canales identificados (consulta 2026-07-23): AAF/Flanders vía Filter Tech S.A.S. (https://filtrosdeaireacondicionado.com/) y Air Solutions Colombia (https://www.airsolutionscolombia.com/productos); Camfil vía ITECO (https://www.iteco.com.co/nuestras-marcas/) y RGD Aire (https://rgdaire.com/index.php/servicio-filtros/); reemplazos compatibles de fabricación nacional CARVEL S.A./Workclean (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/).</t>
         </is>
       </c>
     </row>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86">
-      <c r="A86" s="63" t="inlineStr">
+    <row r="98" ht="15" customHeight="1"/>
+    <row r="99" ht="15" customHeight="1"/>
+    <row r="100" ht="15" customHeight="1"/>
+    <row r="101" ht="15" customHeight="1"/>
+    <row r="102" ht="15" customHeight="1"/>
+    <row r="103" ht="15" customHeight="1"/>
+    <row r="104" ht="15" customHeight="1"/>
+    <row r="105" ht="180" customHeight="1">
+      <c r="A105" s="86" t="inlineStr">
         <is>
           <t>6.2. La especificación se congela en términos MERV 13-14 / ePM1 50-70 % + 24×24 in para habilitar segunda fuente. Se incluye en la compra inicial un juego de repuestos (un prefiltro y un filtro final). Cantidades y plazos: por confirmar con proveedor.</t>
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="90">
-      <c r="A90" s="62" t="inlineStr">
+    <row r="106" ht="15" customHeight="1"/>
+    <row r="107" ht="15" customHeight="1"/>
+    <row r="108" ht="15" customHeight="1"/>
+    <row r="109" ht="15" customHeight="1"/>
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" s="85" t="inlineStr">
         <is>
           <t>7. Normas aplicables</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="63" t="inlineStr">
+    <row r="111" ht="165" customHeight="1">
+      <c r="A111" s="86" t="inlineStr">
         <is>
           <t>7.1. ANSI/ASHRAE 52.2-2017 (ensayo y clasificación MERV); ISO 16890 (ePM1, exigible como informe alternativo); EN 779:2012 (referencia heredada F7/F8). El estado de carga del filtro se sigue por programa de mantenimiento basado en la ΔP esperada (59 Pa limpio / 154 Pa cargado en el sitio) y en la carga de polvo observada en operación (dato típico de operación).</t>
         </is>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
+    <row r="112" ht="15" customHeight="1"/>
+    <row r="113" ht="15" customHeight="1"/>
+    <row r="114" ht="15" customHeight="1"/>
+    <row r="115" ht="15" customHeight="1"/>
+    <row r="116" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="129">
-    <mergeCell ref="A39:E39"/>
+  <mergeCells count="132">
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="J82:K82"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="L82:M82"/>
+    <mergeCell ref="A31:O37"/>
+    <mergeCell ref="N85:O85"/>
     <mergeCell ref="J27:L27"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="J25:L25"/>
-    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="A66:O66"/>
+    <mergeCell ref="D28:F28"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="K41:O41"/>
-    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="I69:O69"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="I90:L90"/>
+    <mergeCell ref="A79:O80"/>
+    <mergeCell ref="A75:H75"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="M76:O76"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="I61:O61"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="I57:O57"/>
-    <mergeCell ref="I76:L76"/>
-    <mergeCell ref="I54:O54"/>
-    <mergeCell ref="F39:J39"/>
-    <mergeCell ref="I56:O56"/>
-    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="A96:O96"/>
+    <mergeCell ref="F47:J47"/>
+    <mergeCell ref="I70:O70"/>
+    <mergeCell ref="A87:O88"/>
+    <mergeCell ref="F46:J46"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="I72:O72"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="L81:M81"/>
+    <mergeCell ref="F48:J48"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A69:C69"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A50:O57"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A91:O94"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="G69:I69"/>
-    <mergeCell ref="M75:O75"/>
-    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="E91:H91"/>
     <mergeCell ref="I10:O10"/>
     <mergeCell ref="A18:O18"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="I59:O59"/>
-    <mergeCell ref="I60:O60"/>
+    <mergeCell ref="A97:O104"/>
+    <mergeCell ref="A38:O41"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="M89:O89"/>
+    <mergeCell ref="I74:O74"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="F41:J41"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="L83:M83"/>
+    <mergeCell ref="K46:O46"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="I89:L89"/>
     <mergeCell ref="I11:O11"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="N67:O67"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="L85:M85"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="L84:M84"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="N84:O84"/>
+    <mergeCell ref="A82:C82"/>
     <mergeCell ref="G27:I27"/>
-    <mergeCell ref="A64:O64"/>
-    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A19:O23"/>
+    <mergeCell ref="J28:L28"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="G82:I82"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="N70:O70"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A29:O32"/>
-    <mergeCell ref="A90:O90"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="G68:I68"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="F40:J40"/>
-    <mergeCell ref="A43:O46"/>
-    <mergeCell ref="M77:O77"/>
-    <mergeCell ref="I74:L74"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A33:O35"/>
+    <mergeCell ref="A91:D91"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="I73:O73"/>
+    <mergeCell ref="G83:I83"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="N82:O82"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A47:E47"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
-    <mergeCell ref="J66:K66"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="K39:O39"/>
-    <mergeCell ref="A19:O21"/>
-    <mergeCell ref="G70:I70"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="I75:O75"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="D84:F84"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A70:C70"/>
     <mergeCell ref="I12:O12"/>
-    <mergeCell ref="M73:O73"/>
-    <mergeCell ref="I55:O55"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="I68:O68"/>
+    <mergeCell ref="A58:O64"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="A78:O78"/>
     <mergeCell ref="I14:O14"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="I73:L73"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="A80:O80"/>
+    <mergeCell ref="M90:O90"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A44:O45"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="M74:O74"/>
-    <mergeCell ref="J69:K69"/>
-    <mergeCell ref="A47:O50"/>
+    <mergeCell ref="J84:K84"/>
     <mergeCell ref="I13:O13"/>
-    <mergeCell ref="A86:O88"/>
     <mergeCell ref="M27:O27"/>
-    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="A85:C85"/>
     <mergeCell ref="I15:O15"/>
-    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="M91:O91"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="G25:I25"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="J70:K70"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A52:O52"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G85:I85"/>
+    <mergeCell ref="A43:O43"/>
+    <mergeCell ref="A111:O116"/>
+    <mergeCell ref="M93:O93"/>
+    <mergeCell ref="I91:L91"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I75:L75"/>
-    <mergeCell ref="A81:O85"/>
-    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="M92:O92"/>
+    <mergeCell ref="A105:O108"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="I93:L93"/>
+    <mergeCell ref="I71:O71"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="I58:O58"/>
-    <mergeCell ref="G67:I67"/>
-    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="A110:O110"/>
+    <mergeCell ref="I92:L92"/>
+    <mergeCell ref="N83:O83"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
